--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BH22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -727,6 +727,4080 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>SnapshotTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Swedish Division 1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Pitea</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>FBK Karlstad</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G2" t="n">
+        <v>600</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I2" t="n">
+        <v>870</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K2" t="n">
+        <v>950</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>2026-05-12 02:17:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Swedish Division 1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Tvaakers</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>BK Olympic</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G3" t="n">
+        <v>600</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I3" t="n">
+        <v>870</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K3" t="n">
+        <v>950</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>2026-05-12 02:17:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Swedish Division 1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Vasalunds IF</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Gefle</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K4" t="n">
+        <v>950</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>2026-05-12 02:17:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Bulgarian A League</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>09:15:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Septemvri</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Spartak Varna</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>2026-05-12 02:17:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Swedish Division 1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Assyriska FF</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Umea FC</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G6" t="n">
+        <v>990</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I6" t="n">
+        <v>990</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K6" t="n">
+        <v>950</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>2026-05-12 02:17:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Swedish Division 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Angelholms</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Aatvidabergs Ff</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G7" t="n">
+        <v>600</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I7" t="n">
+        <v>870</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K7" t="n">
+        <v>950</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>2026-05-12 02:17:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Swedish Division 1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Trelleborgs</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Jonkopings Sodra</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G8" t="n">
+        <v>600</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I8" t="n">
+        <v>870</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K8" t="n">
+        <v>950</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>2026-05-12 02:17:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Swedish Division 1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>IF Karlstad</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>IFK Stocksund</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K9" t="n">
+        <v>950</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>2026-05-12 02:17:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Swedish Division 1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>FC Trollhattan</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Ariana FC</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G10" t="n">
+        <v>600</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I10" t="n">
+        <v>870</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K10" t="n">
+        <v>950</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>2026-05-12 02:17:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Swiss Super League</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>11:30:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Thun</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Young Boys</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>2026-05-12 02:17:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Swiss Super League</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>11:30:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>FC Basel</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>St Gallen</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2026-05-12 02:17:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Swiss Super League</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>11:30:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Sion</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Lugano</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>2026-05-12 02:17:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Bulgarian A League</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>11:45:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Botev Vratsa</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Montana</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I14" t="n">
+        <v>870</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>950</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>2026-05-12 02:17:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Swedish Superettan</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Ljungskile</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2026-05-12 02:17:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Spanish La Liga</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>280</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>36</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>30</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-05-12 02:17:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Bulgarian A League</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>14:15:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Lokomotiv Sofia</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Beroe Stara Za</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-05-12 02:17:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Al-Ettifaq</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Al-Ittihad</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-05-12 02:17:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Al-Quadisiya (KSA)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Al-Hazm (KSA)</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="H19" t="n">
+        <v>10</v>
+      </c>
+      <c r="I19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K19" t="n">
+        <v>8</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>55</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>130</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>360</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-05-12 02:17:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Spanish La Liga</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>25</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>34</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-05-12 02:17:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>English Sky Bet League 1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Bradford</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Bolton</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-05-12 02:17:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Spanish La Liga</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Oviedo</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="H22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I22" t="n">
+        <v>14</v>
+      </c>
+      <c r="J22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P22" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>520</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>48</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>25</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>27</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>42</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>110</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>25</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>46</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-05-12 02:17:22</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-14.xlsx
@@ -769,7 +769,7 @@
         <v>870</v>
       </c>
       <c r="J2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K2" t="n">
         <v>950</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -1148,16 +1148,16 @@
         <v>1.04</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H4" t="n">
         <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -1342,16 +1342,16 @@
         <v>1.7</v>
       </c>
       <c r="G5" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="H5" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I5" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K5" t="n">
         <v>4.1</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
         <v>1.04</v>
@@ -1566,7 +1566,7 @@
         <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="R6" t="n">
         <v>1.24</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -2118,16 +2118,16 @@
         <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H9" t="n">
         <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K9" t="n">
         <v>950</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.64</v>
+        <v>2.96</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H13" t="n">
         <v>3.35</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -3088,19 +3088,19 @@
         <v>1.72</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="H14" t="n">
-        <v>2.14</v>
+        <v>5.2</v>
       </c>
       <c r="I14" t="n">
-        <v>870</v>
+        <v>6.8</v>
       </c>
       <c r="J14" t="n">
         <v>3.6</v>
       </c>
       <c r="K14" t="n">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="G15" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="H15" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="I15" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="J15" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K15" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -3479,10 +3479,10 @@
         <v>2.28</v>
       </c>
       <c r="H16" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I16" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J16" t="n">
         <v>3.55</v>
@@ -3503,7 +3503,7 @@
         <v>1.32</v>
       </c>
       <c r="P16" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q16" t="n">
         <v>2.02</v>
@@ -3560,7 +3560,7 @@
         <v>17.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="AJ16" t="n">
         <v>30</v>
@@ -3572,7 +3572,7 @@
         <v>40</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN16" t="n">
         <v>17.5</v>
@@ -3599,7 +3599,7 @@
         <v>7.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW16" t="n">
         <v>24</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
         <v>3.9</v>
       </c>
       <c r="K17" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -3864,10 +3864,10 @@
         <v>3.75</v>
       </c>
       <c r="G18" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H18" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="I18" t="n">
         <v>2.08</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -4055,16 +4055,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="G19" t="n">
         <v>1.31</v>
       </c>
       <c r="H19" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="J19" t="n">
         <v>6.6</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4097,10 +4097,10 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="U19" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -4118,10 +4118,10 @@
         <v>130</v>
       </c>
       <c r="AA19" t="n">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="AB19" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AC19" t="n">
         <v>970</v>
@@ -4130,10 +4130,10 @@
         <v>950</v>
       </c>
       <c r="AE19" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF19" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AG19" t="n">
         <v>970</v>
@@ -4142,7 +4142,7 @@
         <v>30</v>
       </c>
       <c r="AI19" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ19" t="n">
         <v>970</v>
@@ -4160,31 +4160,31 @@
         <v>3.45</v>
       </c>
       <c r="AO19" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP19" t="n">
+        <v>34</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR19" t="n">
         <v>9.4</v>
       </c>
-      <c r="AQ19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR19" t="n">
+      <c r="AS19" t="n">
         <v>10</v>
       </c>
-      <c r="AS19" t="n">
-        <v>6</v>
-      </c>
       <c r="AT19" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU19" t="n">
         <v>15</v>
       </c>
       <c r="AV19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW19" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AX19" t="n">
         <v>10</v>
@@ -4196,7 +4196,7 @@
         <v>22</v>
       </c>
       <c r="BA19" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB19" t="n">
         <v>10</v>
@@ -4205,20 +4205,20 @@
         <v>11.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>23</v>
+        <v>7.4</v>
       </c>
       <c r="BE19" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BG19" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G20" t="n">
         <v>2.16</v>
       </c>
       <c r="H20" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I20" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J20" t="n">
         <v>3.9</v>
@@ -4279,16 +4279,16 @@
         <v>1.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q20" t="n">
         <v>1.76</v>
       </c>
       <c r="R20" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S20" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="T20" t="n">
         <v>1.67</v>
@@ -4306,10 +4306,10 @@
         <v>20</v>
       </c>
       <c r="Y20" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA20" t="n">
         <v>65</v>
@@ -4351,7 +4351,7 @@
         <v>75</v>
       </c>
       <c r="AN20" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO20" t="n">
         <v>32</v>
@@ -4366,7 +4366,7 @@
         <v>23</v>
       </c>
       <c r="AS20" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AT20" t="n">
         <v>10.5</v>
@@ -4378,13 +4378,13 @@
         <v>13.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX20" t="n">
         <v>13</v>
       </c>
       <c r="AY20" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ20" t="n">
         <v>14.5</v>
@@ -4396,23 +4396,23 @@
         <v>22</v>
       </c>
       <c r="BC20" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD20" t="n">
         <v>20</v>
       </c>
       <c r="BE20" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BF20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
         <v>32</v>
       </c>
       <c r="AF21" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG21" t="n">
         <v>13</v>
@@ -4542,7 +4542,7 @@
         <v>38</v>
       </c>
       <c r="AM21" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AN21" t="n">
         <v>22</v>
@@ -4560,7 +4560,7 @@
         <v>17</v>
       </c>
       <c r="AS21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT21" t="n">
         <v>10.5</v>
@@ -4572,7 +4572,7 @@
         <v>11</v>
       </c>
       <c r="AW21" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX21" t="n">
         <v>15.5</v>
@@ -4584,16 +4584,16 @@
         <v>13.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB21" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC21" t="n">
         <v>22</v>
       </c>
       <c r="BD21" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE21" t="n">
         <v>7.6</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
         <v>1.9</v>
       </c>
       <c r="U22" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4745,7 +4745,7 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AQ22" t="n">
         <v>27</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-14.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
         <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="R6" t="n">
         <v>1.24</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
         <v>4.1</v>
       </c>
       <c r="K12" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2730,7 +2730,7 @@
         <v>2.96</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="G13" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H13" t="n">
         <v>3.35</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="J13" t="n">
         <v>3.6</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
         <v>1.73</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v>1.72</v>
       </c>
       <c r="G14" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="H14" t="n">
         <v>5.2</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G16" t="n">
         <v>2.28</v>
@@ -3482,7 +3482,7 @@
         <v>3.55</v>
       </c>
       <c r="I16" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J16" t="n">
         <v>3.55</v>
@@ -3500,10 +3500,10 @@
         <v>3.85</v>
       </c>
       <c r="O16" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P16" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q16" t="n">
         <v>2.02</v>
@@ -3515,7 +3515,7 @@
         <v>3.5</v>
       </c>
       <c r="T16" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U16" t="n">
         <v>2.18</v>
@@ -3560,7 +3560,7 @@
         <v>17.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AJ16" t="n">
         <v>30</v>
@@ -3599,7 +3599,7 @@
         <v>7.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW16" t="n">
         <v>24</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -3670,13 +3670,13 @@
         <v>1.75</v>
       </c>
       <c r="G17" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="H17" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I17" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J17" t="n">
         <v>3.9</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="G18" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="H18" t="n">
         <v>1.88</v>
@@ -3873,7 +3873,7 @@
         <v>2.08</v>
       </c>
       <c r="J18" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K18" t="n">
         <v>4.5</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
         <v>350</v>
       </c>
       <c r="AB19" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AC19" t="n">
         <v>970</v>
@@ -4151,7 +4151,7 @@
         <v>970</v>
       </c>
       <c r="AL19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
@@ -4163,13 +4163,13 @@
         <v>110</v>
       </c>
       <c r="AP19" t="n">
-        <v>34</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR19" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS19" t="n">
         <v>10</v>
@@ -4184,7 +4184,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AW19" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX19" t="n">
         <v>10</v>
@@ -4196,7 +4196,7 @@
         <v>22</v>
       </c>
       <c r="BA19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BB19" t="n">
         <v>10</v>
@@ -4205,20 +4205,20 @@
         <v>11.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE19" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF19" t="n">
         <v>3</v>
       </c>
       <c r="BG19" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G20" t="n">
         <v>2.16</v>
       </c>
       <c r="H20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I20" t="n">
         <v>3.6</v>
-      </c>
-      <c r="I20" t="n">
-        <v>3.65</v>
       </c>
       <c r="J20" t="n">
         <v>3.9</v>
@@ -4285,7 +4285,7 @@
         <v>1.76</v>
       </c>
       <c r="R20" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S20" t="n">
         <v>2.92</v>
@@ -4294,7 +4294,7 @@
         <v>1.67</v>
       </c>
       <c r="U20" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -4366,7 +4366,7 @@
         <v>23</v>
       </c>
       <c r="AS20" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AT20" t="n">
         <v>10.5</v>
@@ -4378,13 +4378,13 @@
         <v>13.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX20" t="n">
         <v>13</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ20" t="n">
         <v>14.5</v>
@@ -4402,17 +4402,17 @@
         <v>20</v>
       </c>
       <c r="BE20" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BF20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG20" t="n">
         <v>26</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -4545,7 +4545,7 @@
         <v>75</v>
       </c>
       <c r="AN21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO21" t="n">
         <v>25</v>
@@ -4560,7 +4560,7 @@
         <v>17</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.2</v>
+        <v>36</v>
       </c>
       <c r="AT21" t="n">
         <v>10.5</v>
@@ -4584,10 +4584,10 @@
         <v>13.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BC21" t="n">
         <v>22</v>
@@ -4596,7 +4596,7 @@
         <v>7</v>
       </c>
       <c r="BE21" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF21" t="n">
         <v>17</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -4643,13 +4643,13 @@
         <v>1.28</v>
       </c>
       <c r="H22" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="I22" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="J22" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="K22" t="n">
         <v>7.8</v>
@@ -4670,19 +4670,19 @@
         <v>3.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="R22" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="S22" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="T22" t="n">
         <v>1.9</v>
       </c>
       <c r="U22" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4700,7 +4700,7 @@
         <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="AB22" t="n">
         <v>13</v>
@@ -4709,13 +4709,13 @@
         <v>17.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AE22" t="n">
         <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AG22" t="n">
         <v>11.5</v>
@@ -4724,7 +4724,7 @@
         <v>30</v>
       </c>
       <c r="AI22" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
         <v>10.5</v>
@@ -4736,7 +4736,7 @@
         <v>32</v>
       </c>
       <c r="AM22" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
         <v>3.55</v>
@@ -4760,7 +4760,7 @@
         <v>11.5</v>
       </c>
       <c r="AU22" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AV22" t="n">
         <v>25</v>
@@ -4775,7 +4775,7 @@
         <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BA22" t="n">
         <v>40</v>
@@ -4793,14 +4793,14 @@
         <v>42</v>
       </c>
       <c r="BF22" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BG22" t="n">
         <v>46</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-14.xlsx
@@ -760,167 +760,167 @@
         <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H2" t="n">
         <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J2" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K2" t="n">
         <v>950</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="P2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="R2" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-12 06:52:21</t>
+          <t>2026-05-12 09:10:40</t>
         </is>
       </c>
     </row>
@@ -954,167 +954,167 @@
         <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
         <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J3" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-12 06:52:21</t>
+          <t>2026-05-12 09:10:40</t>
         </is>
       </c>
     </row>
@@ -1148,167 +1148,167 @@
         <v>1.04</v>
       </c>
       <c r="G4" t="n">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H4" t="n">
         <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J4" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="R4" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-12 06:52:21</t>
+          <t>2026-05-12 09:10:40</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="G5" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="H5" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I5" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J5" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-12 06:52:21</t>
+          <t>2026-05-12 09:10:40</t>
         </is>
       </c>
     </row>
@@ -1557,13 +1557,13 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="O6" t="n">
         <v>1.16</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="Q6" t="n">
         <v>1.15</v>
@@ -1572,7 +1572,7 @@
         <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="T6" t="n">
         <v>1.11</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-12 06:52:21</t>
+          <t>2026-05-12 09:10:40</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-12 06:52:21</t>
+          <t>2026-05-12 09:10:40</t>
         </is>
       </c>
     </row>
@@ -1924,16 +1924,16 @@
         <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>600</v>
+        <v>2.14</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>1.91</v>
       </c>
       <c r="I8" t="n">
         <v>870</v>
       </c>
       <c r="J8" t="n">
-        <v>1.03</v>
+        <v>1.91</v>
       </c>
       <c r="K8" t="n">
         <v>950</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-12 06:52:21</t>
+          <t>2026-05-12 09:10:40</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-12 06:52:21</t>
+          <t>2026-05-12 09:10:40</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-12 06:52:21</t>
+          <t>2026-05-12 09:10:40</t>
         </is>
       </c>
     </row>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-12 06:52:21</t>
+          <t>2026-05-12 09:10:40</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-12 06:52:21</t>
+          <t>2026-05-12 09:10:40</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.08</v>
+        <v>1.38</v>
       </c>
       <c r="G13" t="n">
         <v>2.32</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-12 06:52:21</t>
+          <t>2026-05-12 09:10:40</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
         <v>1.84</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-12 06:52:21</t>
+          <t>2026-05-12 09:10:40</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-12 06:52:21</t>
+          <t>2026-05-12 09:10:40</t>
         </is>
       </c>
     </row>
@@ -3473,13 +3473,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G16" t="n">
         <v>2.28</v>
       </c>
       <c r="H16" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I16" t="n">
         <v>3.6</v>
@@ -3491,28 +3491,28 @@
         <v>3.65</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
         <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O16" t="n">
         <v>1.33</v>
       </c>
       <c r="P16" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
         <v>1.37</v>
       </c>
       <c r="S16" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T16" t="n">
         <v>1.8</v>
@@ -3521,10 +3521,10 @@
         <v>2.18</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="X16" t="n">
         <v>14.5</v>
@@ -3560,7 +3560,7 @@
         <v>17.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AJ16" t="n">
         <v>30</v>
@@ -3575,7 +3575,7 @@
         <v>95</v>
       </c>
       <c r="AN16" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AO16" t="n">
         <v>42</v>
@@ -3584,7 +3584,7 @@
         <v>13</v>
       </c>
       <c r="AQ16" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR16" t="n">
         <v>21</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-12 06:52:21</t>
+          <t>2026-05-12 09:10:40</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-12 06:52:21</t>
+          <t>2026-05-12 09:10:40</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
         <v>4.4</v>
       </c>
       <c r="H18" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="I18" t="n">
         <v>2.08</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-12 06:52:21</t>
+          <t>2026-05-12 09:10:40</t>
         </is>
       </c>
     </row>
@@ -4061,13 +4061,13 @@
         <v>1.31</v>
       </c>
       <c r="H19" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="I19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J19" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="K19" t="n">
         <v>8</v>
@@ -4088,7 +4088,7 @@
         <v>3.55</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4100,7 +4100,7 @@
         <v>1.7</v>
       </c>
       <c r="U19" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -4109,7 +4109,7 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Y19" t="n">
         <v>950</v>
@@ -4121,10 +4121,10 @@
         <v>350</v>
       </c>
       <c r="AB19" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AD19" t="n">
         <v>950</v>
@@ -4133,10 +4133,10 @@
         <v>140</v>
       </c>
       <c r="AF19" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AG19" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AH19" t="n">
         <v>30</v>
@@ -4145,80 +4145,80 @@
         <v>100</v>
       </c>
       <c r="AJ19" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AK19" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AL19" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
       </c>
       <c r="AN19" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="AO19" t="n">
         <v>110</v>
       </c>
       <c r="AP19" t="n">
-        <v>8.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="AR19" t="n">
-        <v>9.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="AS19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC19" t="n">
         <v>10</v>
       </c>
-      <c r="AT19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>15</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BD19" t="n">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="BE19" t="n">
-        <v>9.6</v>
+        <v>5.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="BG19" t="n">
-        <v>9.6</v>
+        <v>5.2</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-12 06:52:21</t>
+          <t>2026-05-12 09:10:40</t>
         </is>
       </c>
     </row>
@@ -4249,25 +4249,25 @@
         </is>
       </c>
       <c r="F20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G20" t="n">
         <v>2.14</v>
       </c>
-      <c r="G20" t="n">
-        <v>2.16</v>
-      </c>
       <c r="H20" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I20" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="J20" t="n">
         <v>3.9</v>
       </c>
       <c r="K20" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
@@ -4291,16 +4291,16 @@
         <v>2.92</v>
       </c>
       <c r="T20" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U20" t="n">
         <v>2.4</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="X20" t="n">
         <v>20</v>
@@ -4315,7 +4315,7 @@
         <v>65</v>
       </c>
       <c r="AB20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC20" t="n">
         <v>8.800000000000001</v>
@@ -4330,7 +4330,7 @@
         <v>15</v>
       </c>
       <c r="AG20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH20" t="n">
         <v>16.5</v>
@@ -4366,7 +4366,7 @@
         <v>23</v>
       </c>
       <c r="AS20" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AT20" t="n">
         <v>10.5</v>
@@ -4378,19 +4378,19 @@
         <v>13.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX20" t="n">
         <v>13</v>
       </c>
       <c r="AY20" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ20" t="n">
         <v>14.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB20" t="n">
         <v>22</v>
@@ -4399,20 +4399,20 @@
         <v>18.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE20" t="n">
         <v>34</v>
       </c>
       <c r="BF20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG20" t="n">
         <v>26</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-12 06:52:21</t>
+          <t>2026-05-12 09:10:40</t>
         </is>
       </c>
     </row>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="G21" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="H21" t="n">
         <v>2.86</v>
@@ -4461,7 +4461,7 @@
         <v>3.7</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M21" t="n">
         <v>1.06</v>
@@ -4470,7 +4470,7 @@
         <v>4.2</v>
       </c>
       <c r="O21" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P21" t="n">
         <v>2.04</v>
@@ -4479,10 +4479,10 @@
         <v>1.89</v>
       </c>
       <c r="R21" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T21" t="n">
         <v>1.67</v>
@@ -4491,10 +4491,10 @@
         <v>2.32</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X21" t="n">
         <v>17.5</v>
@@ -4533,7 +4533,7 @@
         <v>40</v>
       </c>
       <c r="AJ21" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK21" t="n">
         <v>28</v>
@@ -4551,37 +4551,37 @@
         <v>25</v>
       </c>
       <c r="AP21" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT21" t="n">
         <v>11</v>
       </c>
-      <c r="AR21" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AU21" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV21" t="n">
         <v>11</v>
       </c>
       <c r="AW21" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX21" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AY21" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BA21" t="n">
         <v>7.2</v>
@@ -4593,20 +4593,20 @@
         <v>22</v>
       </c>
       <c r="BD21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE21" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BG21" t="n">
         <v>19.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-12 06:52:21</t>
+          <t>2026-05-12 09:10:40</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
         <v>1.26</v>
       </c>
       <c r="G22" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="H22" t="n">
         <v>12</v>
@@ -4649,13 +4649,13 @@
         <v>13.5</v>
       </c>
       <c r="J22" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="K22" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M22" t="n">
         <v>1.02</v>
@@ -4667,16 +4667,16 @@
         <v>1.14</v>
       </c>
       <c r="P22" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="Q22" t="n">
         <v>1.43</v>
       </c>
       <c r="R22" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="S22" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="T22" t="n">
         <v>1.9</v>
@@ -4685,25 +4685,25 @@
         <v>2.02</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="X22" t="n">
         <v>40</v>
       </c>
       <c r="Y22" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Z22" t="n">
         <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="AB22" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC22" t="n">
         <v>17.5</v>
@@ -4715,7 +4715,7 @@
         <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG22" t="n">
         <v>11.5</v>
@@ -4727,7 +4727,7 @@
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AK22" t="n">
         <v>13</v>
@@ -4736,22 +4736,22 @@
         <v>32</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN22" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AO22" t="n">
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR22" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AS22" t="n">
         <v>110</v>
@@ -4763,13 +4763,13 @@
         <v>15</v>
       </c>
       <c r="AV22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW22" t="n">
         <v>44</v>
       </c>
       <c r="AX22" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AY22" t="n">
         <v>10</v>
@@ -4793,14 +4793,14 @@
         <v>42</v>
       </c>
       <c r="BF22" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BG22" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-12 06:52:21</t>
+          <t>2026-05-12 09:10:40</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-14.xlsx
@@ -781,7 +781,7 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O2" t="n">
         <v>1.14</v>
@@ -796,7 +796,7 @@
         <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-12 09:10:40</t>
+          <t>2026-05-12 10:39:24</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H3" t="n">
         <v>1.04</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-12 09:10:40</t>
+          <t>2026-05-12 10:39:24</t>
         </is>
       </c>
     </row>
@@ -1169,13 +1169,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O4" t="n">
         <v>1.16</v>
       </c>
       <c r="P4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q4" t="n">
         <v>1.16</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-12 09:10:40</t>
+          <t>2026-05-12 10:39:24</t>
         </is>
       </c>
     </row>
@@ -1342,31 +1342,31 @@
         <v>1.69</v>
       </c>
       <c r="G5" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="H5" t="n">
         <v>5.4</v>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="K5" t="n">
         <v>4.2</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P5" t="n">
         <v>1.85</v>
@@ -1375,134 +1375,134 @@
         <v>1.98</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-12 09:10:40</t>
+          <t>2026-05-12 10:39:24</t>
         </is>
       </c>
     </row>
@@ -1557,16 +1557,16 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.36</v>
+        <v>1.1</v>
       </c>
       <c r="O6" t="n">
         <v>1.16</v>
       </c>
       <c r="P6" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="R6" t="n">
         <v>1.24</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-12 09:10:40</t>
+          <t>2026-05-12 10:39:24</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-12 09:10:40</t>
+          <t>2026-05-12 10:39:24</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-12 09:10:40</t>
+          <t>2026-05-12 10:39:24</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-12 09:10:40</t>
+          <t>2026-05-12 10:39:24</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-12 09:10:40</t>
+          <t>2026-05-12 10:39:24</t>
         </is>
       </c>
     </row>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-12 09:10:40</t>
+          <t>2026-05-12 10:39:24</t>
         </is>
       </c>
     </row>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-12 09:10:40</t>
+          <t>2026-05-12 10:39:24</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-12 09:10:40</t>
+          <t>2026-05-12 10:39:24</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-12 09:10:40</t>
+          <t>2026-05-12 10:39:24</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-12 09:10:40</t>
+          <t>2026-05-12 10:39:24</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
         <v>1.94</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R16" t="n">
         <v>1.37</v>
@@ -3560,7 +3560,7 @@
         <v>17.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AJ16" t="n">
         <v>30</v>
@@ -3632,11 +3632,11 @@
         <v>15.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-12 09:10:40</t>
+          <t>2026-05-12 10:39:24</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
         <v>2.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-12 09:10:40</t>
+          <t>2026-05-12 10:39:24</t>
         </is>
       </c>
     </row>
@@ -3864,10 +3864,10 @@
         <v>3.7</v>
       </c>
       <c r="G18" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="H18" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="I18" t="n">
         <v>2.08</v>
@@ -3894,7 +3894,7 @@
         <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-12 09:10:40</t>
+          <t>2026-05-12 10:39:24</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
         <v>1.27</v>
       </c>
       <c r="G19" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="H19" t="n">
         <v>10</v>
@@ -4070,7 +4070,7 @@
         <v>6.8</v>
       </c>
       <c r="K19" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4088,7 +4088,7 @@
         <v>3.55</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4097,10 +4097,10 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="U19" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -4109,7 +4109,7 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>60</v>
+        <v>950</v>
       </c>
       <c r="Y19" t="n">
         <v>950</v>
@@ -4121,10 +4121,10 @@
         <v>350</v>
       </c>
       <c r="AB19" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AD19" t="n">
         <v>950</v>
@@ -4148,7 +4148,7 @@
         <v>14</v>
       </c>
       <c r="AK19" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL19" t="n">
         <v>30</v>
@@ -4157,34 +4157,34 @@
         <v>110</v>
       </c>
       <c r="AN19" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AO19" t="n">
         <v>110</v>
       </c>
       <c r="AP19" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="AQ19" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="AR19" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AT19" t="n">
         <v>12</v>
       </c>
       <c r="AU19" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AV19" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AX19" t="n">
         <v>10.5</v>
@@ -4193,10 +4193,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ19" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BB19" t="n">
         <v>10.5</v>
@@ -4208,17 +4208,17 @@
         <v>20</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.74</v>
+        <v>2.98</v>
       </c>
       <c r="BG19" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-12 09:10:40</t>
+          <t>2026-05-12 10:39:24</t>
         </is>
       </c>
     </row>
@@ -4249,25 +4249,25 @@
         </is>
       </c>
       <c r="F20" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G20" t="n">
         <v>2.1</v>
       </c>
-      <c r="G20" t="n">
-        <v>2.14</v>
-      </c>
       <c r="H20" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I20" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J20" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K20" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
@@ -4297,10 +4297,10 @@
         <v>2.4</v>
       </c>
       <c r="V20" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W20" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="X20" t="n">
         <v>20</v>
@@ -4324,10 +4324,10 @@
         <v>15</v>
       </c>
       <c r="AE20" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF20" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG20" t="n">
         <v>10.5</v>
@@ -4354,7 +4354,7 @@
         <v>13</v>
       </c>
       <c r="AO20" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AP20" t="n">
         <v>17</v>
@@ -4399,7 +4399,7 @@
         <v>18.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BE20" t="n">
         <v>34</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-12 09:10:40</t>
+          <t>2026-05-12 10:39:24</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
         <v>3.7</v>
       </c>
       <c r="L21" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="M21" t="n">
         <v>1.06</v>
@@ -4470,7 +4470,7 @@
         <v>4.2</v>
       </c>
       <c r="O21" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P21" t="n">
         <v>2.04</v>
@@ -4581,7 +4581,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BA21" t="n">
         <v>7.2</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-12 09:10:40</t>
+          <t>2026-05-12 10:39:24</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4652,7 @@
         <v>7.2</v>
       </c>
       <c r="K22" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="L22" t="n">
         <v>1.19</v>
@@ -4661,7 +4661,7 @@
         <v>1.02</v>
       </c>
       <c r="N22" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="O22" t="n">
         <v>1.14</v>
@@ -4670,7 +4670,7 @@
         <v>3.05</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R22" t="n">
         <v>1.84</v>
@@ -4709,7 +4709,7 @@
         <v>17.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AE22" t="n">
         <v>1000</v>
@@ -4745,7 +4745,7 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ22" t="n">
         <v>26</v>
@@ -4763,7 +4763,7 @@
         <v>15</v>
       </c>
       <c r="AV22" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AW22" t="n">
         <v>44</v>
@@ -4781,13 +4781,13 @@
         <v>40</v>
       </c>
       <c r="BB22" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BC22" t="n">
         <v>11.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BE22" t="n">
         <v>42</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-12 09:10:40</t>
+          <t>2026-05-12 10:39:24</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-14.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>1.69</v>
       </c>
       <c r="G5" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="H5" t="n">
         <v>5.4</v>
@@ -1360,10 +1360,10 @@
         <v>1.4</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.85</v>
+        <v>3.4</v>
       </c>
       <c r="O5" t="n">
         <v>1.34</v>
@@ -1375,22 +1375,22 @@
         <v>1.98</v>
       </c>
       <c r="R5" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.98</v>
+        <v>3.15</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V5" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W5" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="X5" t="n">
         <v>17</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -1745,152 +1745,152 @@
         <v>950</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R7" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -1939,152 +1939,152 @@
         <v>950</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R8" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -2133,152 +2133,152 @@
         <v>950</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="P9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="R9" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -2327,152 +2327,152 @@
         <v>950</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R10" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.38</v>
+        <v>2.1</v>
       </c>
       <c r="G13" t="n">
         <v>2.32</v>
@@ -2906,7 +2906,7 @@
         <v>3.6</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
         <v>1.94</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R16" t="n">
         <v>1.37</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="G17" t="n">
         <v>1.88</v>
@@ -3676,7 +3676,7 @@
         <v>4.4</v>
       </c>
       <c r="I17" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="J17" t="n">
         <v>3.9</v>
@@ -3700,7 +3700,7 @@
         <v>2.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
         <v>4.7</v>
       </c>
       <c r="H18" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="I18" t="n">
         <v>2.08</v>
@@ -3894,7 +3894,7 @@
         <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -4252,13 +4252,13 @@
         <v>2.06</v>
       </c>
       <c r="G20" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H20" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="I20" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J20" t="n">
         <v>3.95</v>
@@ -4267,7 +4267,7 @@
         <v>4</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
@@ -4294,34 +4294,34 @@
         <v>1.68</v>
       </c>
       <c r="U20" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V20" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W20" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X20" t="n">
         <v>20</v>
       </c>
       <c r="Y20" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z20" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AA20" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AB20" t="n">
         <v>11.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD20" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE20" t="n">
         <v>40</v>
@@ -4336,10 +4336,10 @@
         <v>16.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK20" t="n">
         <v>21</v>
@@ -4351,16 +4351,16 @@
         <v>75</v>
       </c>
       <c r="AN20" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AP20" t="n">
         <v>17</v>
       </c>
       <c r="AQ20" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR20" t="n">
         <v>23</v>
@@ -4369,7 +4369,7 @@
         <v>32</v>
       </c>
       <c r="AT20" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU20" t="n">
         <v>8.199999999999999</v>
@@ -4381,10 +4381,10 @@
         <v>23</v>
       </c>
       <c r="AX20" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ20" t="n">
         <v>14.5</v>
@@ -4393,10 +4393,10 @@
         <v>26</v>
       </c>
       <c r="BB20" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BC20" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD20" t="n">
         <v>20</v>
@@ -4405,14 +4405,14 @@
         <v>34</v>
       </c>
       <c r="BF20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG20" t="n">
         <v>26</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
         <v>2.68</v>
       </c>
       <c r="H21" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="I21" t="n">
         <v>2.96</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -4637,19 +4637,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="G22" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="H22" t="n">
         <v>12</v>
       </c>
       <c r="I22" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="J22" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="K22" t="n">
         <v>7.8</v>
@@ -4676,7 +4676,7 @@
         <v>1.84</v>
       </c>
       <c r="S22" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="T22" t="n">
         <v>1.9</v>
@@ -4688,7 +4688,7 @@
         <v>1.08</v>
       </c>
       <c r="W22" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="X22" t="n">
         <v>40</v>
@@ -4745,7 +4745,7 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AQ22" t="n">
         <v>26</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-14.xlsx
@@ -139,117 +139,117 @@
     <t>Odd_CS_Goleada_A_Lay</t>
   </si>
   <si>
+    <t>Odd_CS_0x0_Back</t>
+  </si>
+  <si>
+    <t>Odd_CS_0x1_Back</t>
+  </si>
+  <si>
+    <t>Odd_CS_0x2_Back</t>
+  </si>
+  <si>
+    <t>Odd_CS_0x3_Back</t>
+  </si>
+  <si>
+    <t>Odd_CS_1x0_Back</t>
+  </si>
+  <si>
+    <t>Odd_CS_1x1_Back</t>
+  </si>
+  <si>
+    <t>Odd_CS_1x2_Back</t>
+  </si>
+  <si>
+    <t>Odd_CS_1x3_Back</t>
+  </si>
+  <si>
+    <t>Odd_CS_2x0_Back</t>
+  </si>
+  <si>
+    <t>Odd_CS_2x1_Back</t>
+  </si>
+  <si>
+    <t>Odd_CS_2x2_Back</t>
+  </si>
+  <si>
+    <t>Odd_CS_2x3_Back</t>
+  </si>
+  <si>
+    <t>Odd_CS_3x0_Back</t>
+  </si>
+  <si>
+    <t>Odd_CS_3x1_Back</t>
+  </si>
+  <si>
+    <t>Odd_CS_3x2_Back</t>
+  </si>
+  <si>
+    <t>Odd_CS_3x3_Back</t>
+  </si>
+  <si>
+    <t>Odd_CS_Goleada_H_Back</t>
+  </si>
+  <si>
+    <t>Odd_CS_Goleada_A_Back</t>
+  </si>
+  <si>
     <t>Odd_HTS_0x0_Lay</t>
   </si>
   <si>
+    <t>Odd_HTS_0x0_Back</t>
+  </si>
+  <si>
     <t>Odd_HTS_1x1_Lay</t>
   </si>
   <si>
+    <t>Odd_HTS_1x1_Back</t>
+  </si>
+  <si>
     <t>Odd_HTS_2x2_Lay</t>
   </si>
   <si>
+    <t>Odd_HTS_2x2_Back</t>
+  </si>
+  <si>
     <t>Odd_HTS_1x0_Lay</t>
   </si>
   <si>
+    <t>Odd_HTS_1x0_Back</t>
+  </si>
+  <si>
     <t>Odd_HTS_2x0_Lay</t>
   </si>
   <si>
+    <t>Odd_HTS_2x0_Back</t>
+  </si>
+  <si>
     <t>Odd_HTS_2x1_Lay</t>
   </si>
   <si>
+    <t>Odd_HTS_2x1_Back</t>
+  </si>
+  <si>
     <t>Odd_HTS_0x1_Lay</t>
   </si>
   <si>
+    <t>Odd_HTS_0x1_Back</t>
+  </si>
+  <si>
     <t>Odd_HTS_0x2_Lay</t>
   </si>
   <si>
+    <t>Odd_HTS_0x2_Back</t>
+  </si>
+  <si>
     <t>Odd_HTS_1x2_Lay</t>
   </si>
   <si>
+    <t>Odd_HTS_1x2_Back</t>
+  </si>
+  <si>
     <t>Odd_HTS_Outros_Lay</t>
   </si>
   <si>
-    <t>Odd_CS_0x0_Back</t>
-  </si>
-  <si>
-    <t>Odd_CS_0x1_Back</t>
-  </si>
-  <si>
-    <t>Odd_CS_0x2_Back</t>
-  </si>
-  <si>
-    <t>Odd_CS_0x3_Back</t>
-  </si>
-  <si>
-    <t>Odd_CS_1x0_Back</t>
-  </si>
-  <si>
-    <t>Odd_CS_1x1_Back</t>
-  </si>
-  <si>
-    <t>Odd_CS_1x2_Back</t>
-  </si>
-  <si>
-    <t>Odd_CS_1x3_Back</t>
-  </si>
-  <si>
-    <t>Odd_CS_2x0_Back</t>
-  </si>
-  <si>
-    <t>Odd_CS_2x1_Back</t>
-  </si>
-  <si>
-    <t>Odd_CS_2x2_Back</t>
-  </si>
-  <si>
-    <t>Odd_CS_2x3_Back</t>
-  </si>
-  <si>
-    <t>Odd_CS_3x0_Back</t>
-  </si>
-  <si>
-    <t>Odd_CS_3x1_Back</t>
-  </si>
-  <si>
-    <t>Odd_CS_3x2_Back</t>
-  </si>
-  <si>
-    <t>Odd_CS_3x3_Back</t>
-  </si>
-  <si>
-    <t>Odd_CS_Goleada_H_Back</t>
-  </si>
-  <si>
-    <t>Odd_CS_Goleada_A_Back</t>
-  </si>
-  <si>
-    <t>Odd_HTS_0x0_Back</t>
-  </si>
-  <si>
-    <t>Odd_HTS_1x1_Back</t>
-  </si>
-  <si>
-    <t>Odd_HTS_2x2_Back</t>
-  </si>
-  <si>
-    <t>Odd_HTS_1x0_Back</t>
-  </si>
-  <si>
-    <t>Odd_HTS_2x0_Back</t>
-  </si>
-  <si>
-    <t>Odd_HTS_2x1_Back</t>
-  </si>
-  <si>
-    <t>Odd_HTS_0x1_Back</t>
-  </si>
-  <si>
-    <t>Odd_HTS_0x2_Back</t>
-  </si>
-  <si>
-    <t>Odd_HTS_1x2_Back</t>
-  </si>
-  <si>
     <t>Odd_HTS_Outros_Back</t>
   </si>
   <si>
@@ -442,7 +442,7 @@
     <t>Oviedo</t>
   </si>
   <si>
-    <t>2026-05-12 12:09:35</t>
+    <t>2026-05-12 12:59:32</t>
   </si>
 </sst>
 </file>
@@ -1170,34 +1170,34 @@
         <v>1000</v>
       </c>
       <c r="AP2">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AR2">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AS2">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AT2">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AU2">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AV2">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AW2">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AX2">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AY2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2">
         <v>1.01</v>
@@ -1224,61 +1224,61 @@
         <v>1.01</v>
       </c>
       <c r="BH2">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL2">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN2">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP2">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR2">
-        <v>1.04</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
         <v>1.04</v>
       </c>
       <c r="BT2">
-        <v>1.04</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
         <v>1.04</v>
       </c>
       <c r="BV2">
-        <v>1.04</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
         <v>1.04</v>
       </c>
       <c r="BX2">
-        <v>1.04</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
         <v>1.04</v>
       </c>
       <c r="BZ2">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CA2">
         <v>0</v>
@@ -1412,34 +1412,34 @@
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AR3">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AS3">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AT3">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AU3">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AV3">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AW3">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AX3">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AY3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3">
         <v>1.01</v>
@@ -1466,61 +1466,61 @@
         <v>1.01</v>
       </c>
       <c r="BH3">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
-        <v>1.04</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
         <v>1.04</v>
       </c>
       <c r="BT3">
-        <v>1.04</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
         <v>1.04</v>
       </c>
       <c r="BV3">
-        <v>1.04</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
         <v>1.04</v>
       </c>
       <c r="BX3">
-        <v>1.04</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
         <v>1.04</v>
       </c>
       <c r="BZ3">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CA3">
         <v>0</v>
@@ -1654,34 +1654,34 @@
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AR4">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AS4">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AT4">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AU4">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AV4">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AW4">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AX4">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AY4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4">
         <v>1.01</v>
@@ -1708,61 +1708,61 @@
         <v>1.01</v>
       </c>
       <c r="BH4">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
-        <v>1.04</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
         <v>1.04</v>
       </c>
       <c r="BT4">
-        <v>1.04</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
         <v>1.04</v>
       </c>
       <c r="BV4">
-        <v>1.04</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
         <v>1.04</v>
       </c>
       <c r="BX4">
-        <v>1.04</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
         <v>1.04</v>
       </c>
       <c r="BZ4">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CA4">
         <v>0</v>
@@ -1896,115 +1896,115 @@
         <v>140</v>
       </c>
       <c r="AP5">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AQ5">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AR5">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="AS5">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="AT5">
-        <v>17.5</v>
+        <v>7</v>
       </c>
       <c r="AU5">
-        <v>44</v>
+        <v>7.6</v>
       </c>
       <c r="AV5">
+        <v>19</v>
+      </c>
+      <c r="AW5">
+        <v>4.1</v>
+      </c>
+      <c r="AX5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ5">
+        <v>18.5</v>
+      </c>
+      <c r="BA5">
+        <v>4.1</v>
+      </c>
+      <c r="BB5">
         <v>13</v>
       </c>
-      <c r="AW5">
-        <v>1000</v>
-      </c>
-      <c r="AX5">
-        <v>1000</v>
-      </c>
-      <c r="AY5">
-        <v>34</v>
-      </c>
-      <c r="AZ5">
-        <v>10</v>
-      </c>
-      <c r="BA5">
-        <v>13</v>
-      </c>
-      <c r="BB5">
-        <v>4</v>
-      </c>
       <c r="BC5">
+        <v>16.5</v>
+      </c>
+      <c r="BD5">
+        <v>3.95</v>
+      </c>
+      <c r="BE5">
         <v>4.2</v>
       </c>
-      <c r="BD5">
-        <v>7</v>
-      </c>
-      <c r="BE5">
-        <v>7.6</v>
-      </c>
       <c r="BF5">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="BG5">
         <v>4.1</v>
       </c>
       <c r="BH5">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>8.800000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="BJ5">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="BK5">
-        <v>4.1</v>
+        <v>1.61</v>
       </c>
       <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>1.8</v>
+      </c>
+      <c r="BN5">
+        <v>5.9</v>
+      </c>
+      <c r="BO5">
+        <v>2.88</v>
+      </c>
+      <c r="BP5">
+        <v>17.5</v>
+      </c>
+      <c r="BQ5">
+        <v>1.63</v>
+      </c>
+      <c r="BR5">
+        <v>44</v>
+      </c>
+      <c r="BS5">
+        <v>1.73</v>
+      </c>
+      <c r="BT5">
         <v>13</v>
       </c>
-      <c r="BM5">
-        <v>16.5</v>
-      </c>
-      <c r="BN5">
-        <v>3.95</v>
-      </c>
-      <c r="BO5">
-        <v>4.2</v>
-      </c>
-      <c r="BP5">
-        <v>9</v>
-      </c>
-      <c r="BQ5">
-        <v>4.1</v>
-      </c>
-      <c r="BR5">
-        <v>1.8</v>
-      </c>
-      <c r="BS5">
-        <v>1.61</v>
-      </c>
-      <c r="BT5">
-        <v>1.8</v>
-      </c>
       <c r="BU5">
-        <v>2.88</v>
+        <v>1.58</v>
       </c>
       <c r="BV5">
-        <v>1.63</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="BX5">
-        <v>1.58</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="BZ5">
-        <v>1.77</v>
+        <v>34</v>
       </c>
       <c r="CA5">
         <v>1.71</v>
@@ -2138,34 +2138,34 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AR6">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AU6">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AV6">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AW6">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="AY6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6">
         <v>1.01</v>
@@ -2192,61 +2192,61 @@
         <v>1.01</v>
       </c>
       <c r="BH6">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL6">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN6">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP6">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR6">
-        <v>1.04</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
         <v>1.04</v>
       </c>
       <c r="BT6">
-        <v>1.04</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
         <v>1.04</v>
       </c>
       <c r="BV6">
-        <v>1.04</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
         <v>1.04</v>
       </c>
       <c r="BX6">
-        <v>1.04</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
         <v>1.04</v>
       </c>
       <c r="BZ6">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CA6">
         <v>0</v>
@@ -2284,7 +2284,7 @@
         <v>990</v>
       </c>
       <c r="J7">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2296,22 +2296,22 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O7">
         <v>1.22</v>
       </c>
       <c r="P7">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q7">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="R7">
         <v>1.24</v>
       </c>
       <c r="S7">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T7">
         <v>1.11</v>
@@ -2380,34 +2380,34 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AR7">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AS7">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AT7">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AU7">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AV7">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AW7">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AX7">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AY7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7">
         <v>1.03</v>
@@ -2428,67 +2428,67 @@
         <v>1.03</v>
       </c>
       <c r="BF7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BH7">
-        <v>1.03</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7">
-        <v>1.03</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BL7">
-        <v>1.03</v>
+        <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>1.03</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BP7">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
         <v>1.01</v>
       </c>
       <c r="BR7">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
         <v>1.01</v>
       </c>
       <c r="BT7">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
         <v>1.01</v>
       </c>
       <c r="BV7">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
         <v>1.01</v>
       </c>
       <c r="BX7">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
         <v>1.01</v>
       </c>
       <c r="BZ7">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CA7">
         <v>0</v>
@@ -2622,52 +2622,52 @@
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AR8">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AS8">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AT8">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AU8">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AV8">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AW8">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AX8">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF8">
         <v>1.01</v>
@@ -2676,61 +2676,61 @@
         <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
         <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
         <v>1.01</v>
       </c>
       <c r="BL8">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
         <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
         <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
         <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
         <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
         <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
         <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
         <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CA8">
         <v>0</v>
@@ -2768,7 +2768,7 @@
         <v>990</v>
       </c>
       <c r="J9">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K9">
         <v>950</v>
@@ -2789,13 +2789,13 @@
         <v>1.25</v>
       </c>
       <c r="Q9">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="R9">
         <v>1.24</v>
       </c>
       <c r="S9">
-        <v>1.05</v>
+        <v>1.31</v>
       </c>
       <c r="T9">
         <v>1.11</v>
@@ -2864,34 +2864,34 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AR9">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AS9">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AT9">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AU9">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AV9">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AW9">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AX9">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9">
         <v>1.03</v>
@@ -2912,67 +2912,67 @@
         <v>1.03</v>
       </c>
       <c r="BF9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BH9">
-        <v>1.03</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9">
-        <v>1.03</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
-        <v>1.03</v>
+        <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>1.03</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
         <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
         <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
         <v>1.01</v>
       </c>
       <c r="BV9">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
         <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
         <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CA9">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>1.04</v>
       </c>
       <c r="G10">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H10">
         <v>1.04</v>
@@ -3010,7 +3010,7 @@
         <v>1000</v>
       </c>
       <c r="J10">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K10">
         <v>950</v>
@@ -3037,7 +3037,7 @@
         <v>1.24</v>
       </c>
       <c r="S10">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="T10">
         <v>1.11</v>
@@ -3106,34 +3106,34 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AR10">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AS10">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AT10">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AU10">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AV10">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AW10">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AX10">
-        <v>1000</v>
+        <v>1.03</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10">
         <v>1.03</v>
@@ -3154,67 +3154,67 @@
         <v>1.03</v>
       </c>
       <c r="BF10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BG10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BH10">
-        <v>1.03</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10">
-        <v>1.03</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BL10">
-        <v>1.03</v>
+        <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>1.03</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BP10">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
         <v>1.01</v>
       </c>
       <c r="BR10">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
         <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
         <v>1.01</v>
       </c>
       <c r="BV10">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
         <v>1.01</v>
       </c>
       <c r="BX10">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
         <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CA10">
         <v>0</v>
@@ -3264,28 +3264,28 @@
         <v>1.02</v>
       </c>
       <c r="N11">
-        <v>2.96</v>
+        <v>6</v>
       </c>
       <c r="O11">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="P11">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="Q11">
         <v>1.4</v>
       </c>
       <c r="R11">
-        <v>1.69</v>
+        <v>1.84</v>
       </c>
       <c r="S11">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="T11">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="U11">
-        <v>2.36</v>
+        <v>2.94</v>
       </c>
       <c r="V11">
         <v>1.4</v>
@@ -3294,7 +3294,7 @@
         <v>1.83</v>
       </c>
       <c r="X11">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="Y11">
         <v>34</v>
@@ -3309,7 +3309,7 @@
         <v>26</v>
       </c>
       <c r="AC11">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AD11">
         <v>22</v>
@@ -3321,7 +3321,7 @@
         <v>28</v>
       </c>
       <c r="AG11">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AH11">
         <v>20</v>
@@ -3339,7 +3339,7 @@
         <v>32</v>
       </c>
       <c r="AM11">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AN11">
         <v>1000</v>
@@ -3348,115 +3348,115 @@
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>1000</v>
+        <v>2.14</v>
       </c>
       <c r="AQ11">
-        <v>1000</v>
+        <v>2.1</v>
       </c>
       <c r="AR11">
-        <v>1000</v>
+        <v>2.14</v>
       </c>
       <c r="AS11">
-        <v>1000</v>
+        <v>2.18</v>
       </c>
       <c r="AT11">
-        <v>1000</v>
+        <v>2.06</v>
       </c>
       <c r="AU11">
-        <v>1000</v>
+        <v>1.95</v>
       </c>
       <c r="AV11">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AW11">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AX11">
-        <v>1000</v>
+        <v>2.08</v>
       </c>
       <c r="AY11">
-        <v>1000</v>
+        <v>1.96</v>
       </c>
       <c r="AZ11">
-        <v>2.06</v>
+        <v>10</v>
       </c>
       <c r="BA11">
-        <v>2.02</v>
+        <v>20</v>
       </c>
       <c r="BB11">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="BC11">
-        <v>2.1</v>
+        <v>13</v>
       </c>
       <c r="BD11">
-        <v>2</v>
+        <v>16.5</v>
       </c>
       <c r="BE11">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="BF11">
-        <v>11</v>
+        <v>2.24</v>
       </c>
       <c r="BG11">
-        <v>20</v>
+        <v>2.24</v>
       </c>
       <c r="BH11">
-        <v>2</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BL11">
-        <v>2.04</v>
+        <v>1000</v>
       </c>
       <c r="BM11">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="BP11">
-        <v>2.16</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
         <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
         <v>1.01</v>
       </c>
       <c r="BV11">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
         <v>1.01</v>
       </c>
       <c r="BX11">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
         <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
         <v>1.01</v>
@@ -3500,7 +3500,7 @@
         <v>4.5</v>
       </c>
       <c r="L12">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M12">
         <v>1.02</v>
@@ -3512,22 +3512,22 @@
         <v>1.15</v>
       </c>
       <c r="P12">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="Q12">
         <v>1.45</v>
       </c>
       <c r="R12">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="S12">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="T12">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="U12">
-        <v>2.56</v>
+        <v>2.96</v>
       </c>
       <c r="V12">
         <v>1.56</v>
@@ -3590,115 +3590,115 @@
         <v>12.5</v>
       </c>
       <c r="AP12">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ12">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR12">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AS12">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AT12">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="AU12">
-        <v>30</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV12">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AW12">
-        <v>25</v>
+        <v>17.5</v>
       </c>
       <c r="AX12">
-        <v>32</v>
+        <v>16.5</v>
       </c>
       <c r="AY12">
-        <v>18.5</v>
+        <v>9.6</v>
       </c>
       <c r="AZ12">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BA12">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
       <c r="BB12">
-        <v>17.5</v>
+        <v>9.4</v>
       </c>
       <c r="BC12">
-        <v>9.6</v>
+        <v>16.5</v>
       </c>
       <c r="BD12">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="BE12">
         <v>9.800000000000001</v>
       </c>
       <c r="BF12">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG12">
-        <v>17.5</v>
+        <v>9</v>
       </c>
       <c r="BH12">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
+        <v>3.35</v>
+      </c>
+      <c r="BJ12">
+        <v>11.5</v>
+      </c>
+      <c r="BK12">
+        <v>5.1</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>21</v>
+      </c>
+      <c r="BN12">
+        <v>9</v>
+      </c>
+      <c r="BO12">
+        <v>4.1</v>
+      </c>
+      <c r="BP12">
+        <v>23</v>
+      </c>
+      <c r="BQ12">
         <v>9.6</v>
       </c>
-      <c r="BJ12">
-        <v>12.5</v>
-      </c>
-      <c r="BK12">
-        <v>19.5</v>
-      </c>
-      <c r="BL12">
-        <v>9.4</v>
-      </c>
-      <c r="BM12">
-        <v>16.5</v>
-      </c>
-      <c r="BN12">
-        <v>19</v>
-      </c>
-      <c r="BO12">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BP12">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BQ12">
-        <v>9</v>
-      </c>
       <c r="BR12">
-        <v>3.35</v>
+        <v>30</v>
       </c>
       <c r="BS12">
-        <v>5.1</v>
+        <v>13</v>
       </c>
       <c r="BT12">
-        <v>21</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU12">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BV12">
-        <v>9.6</v>
+        <v>25</v>
       </c>
       <c r="BW12">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="BX12">
-        <v>4.2</v>
+        <v>32</v>
       </c>
       <c r="BY12">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ12">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="CA12">
         <v>8</v>
@@ -3739,7 +3739,7 @@
         <v>3.35</v>
       </c>
       <c r="K13">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -3763,13 +3763,13 @@
         <v>1.42</v>
       </c>
       <c r="S13">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="T13">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="U13">
-        <v>1.11</v>
+        <v>2.26</v>
       </c>
       <c r="V13">
         <v>1.37</v>
@@ -3781,7 +3781,7 @@
         <v>1000</v>
       </c>
       <c r="Y13">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z13">
         <v>1000</v>
@@ -3796,13 +3796,13 @@
         <v>11</v>
       </c>
       <c r="AD13">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE13">
         <v>1000</v>
       </c>
       <c r="AF13">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG13">
         <v>1000</v>
@@ -3814,13 +3814,13 @@
         <v>1000</v>
       </c>
       <c r="AJ13">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK13">
         <v>1000</v>
       </c>
       <c r="AL13">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM13">
         <v>90</v>
@@ -3832,115 +3832,115 @@
         <v>1000</v>
       </c>
       <c r="AP13">
-        <v>1000</v>
+        <v>1.57</v>
       </c>
       <c r="AQ13">
+        <v>11</v>
+      </c>
+      <c r="AR13">
+        <v>1.57</v>
+      </c>
+      <c r="AS13">
+        <v>1.57</v>
+      </c>
+      <c r="AT13">
+        <v>1.57</v>
+      </c>
+      <c r="AU13">
+        <v>1.37</v>
+      </c>
+      <c r="AV13">
+        <v>10.5</v>
+      </c>
+      <c r="AW13">
+        <v>1.57</v>
+      </c>
+      <c r="AX13">
+        <v>11</v>
+      </c>
+      <c r="AY13">
+        <v>1.57</v>
+      </c>
+      <c r="AZ13">
+        <v>1.46</v>
+      </c>
+      <c r="BA13">
+        <v>1.57</v>
+      </c>
+      <c r="BB13">
+        <v>1.51</v>
+      </c>
+      <c r="BC13">
+        <v>1.57</v>
+      </c>
+      <c r="BD13">
+        <v>1.51</v>
+      </c>
+      <c r="BE13">
+        <v>1.54</v>
+      </c>
+      <c r="BF13">
+        <v>1.57</v>
+      </c>
+      <c r="BG13">
+        <v>1.57</v>
+      </c>
+      <c r="BH13">
+        <v>1000</v>
+      </c>
+      <c r="BI13">
+        <v>1.01</v>
+      </c>
+      <c r="BJ13">
         <v>12.5</v>
       </c>
-      <c r="AR13">
-        <v>1000</v>
-      </c>
-      <c r="AS13">
+      <c r="BK13">
+        <v>5.9</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>21</v>
+      </c>
+      <c r="BN13">
         <v>7</v>
       </c>
-      <c r="AT13">
+      <c r="BO13">
+        <v>3.6</v>
+      </c>
+      <c r="BP13">
         <v>21</v>
       </c>
-      <c r="AU13">
+      <c r="BQ13">
+        <v>9.6</v>
+      </c>
+      <c r="BR13">
         <v>36</v>
       </c>
-      <c r="AV13">
+      <c r="BS13">
+        <v>16.5</v>
+      </c>
+      <c r="BT13">
         <v>9.199999999999999</v>
       </c>
-      <c r="AW13">
-        <v>36</v>
-      </c>
-      <c r="AX13">
-        <v>48</v>
-      </c>
-      <c r="AY13">
-        <v>29</v>
-      </c>
-      <c r="AZ13">
-        <v>1.17</v>
-      </c>
-      <c r="BA13">
-        <v>1.17</v>
-      </c>
-      <c r="BB13">
-        <v>1.17</v>
-      </c>
-      <c r="BC13">
-        <v>1.17</v>
-      </c>
-      <c r="BD13">
-        <v>1.17</v>
-      </c>
-      <c r="BE13">
-        <v>1.06</v>
-      </c>
-      <c r="BF13">
-        <v>1.17</v>
-      </c>
-      <c r="BG13">
-        <v>1.17</v>
-      </c>
-      <c r="BH13">
-        <v>1.17</v>
-      </c>
-      <c r="BI13">
-        <v>1.17</v>
-      </c>
-      <c r="BJ13">
-        <v>1.11</v>
-      </c>
-      <c r="BK13">
-        <v>1.17</v>
-      </c>
-      <c r="BL13">
-        <v>1.17</v>
-      </c>
-      <c r="BM13">
-        <v>1.17</v>
-      </c>
-      <c r="BN13">
-        <v>1.17</v>
-      </c>
-      <c r="BO13">
-        <v>1.16</v>
-      </c>
-      <c r="BP13">
-        <v>1.17</v>
-      </c>
-      <c r="BQ13">
-        <v>1.17</v>
-      </c>
-      <c r="BR13">
-        <v>1.01</v>
-      </c>
-      <c r="BS13">
-        <v>5.9</v>
-      </c>
-      <c r="BT13">
-        <v>21</v>
-      </c>
       <c r="BU13">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="BV13">
-        <v>9.6</v>
+        <v>34</v>
       </c>
       <c r="BW13">
         <v>16.5</v>
       </c>
       <c r="BX13">
-        <v>4.6</v>
+        <v>48</v>
       </c>
       <c r="BY13">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="BZ13">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="CA13">
         <v>13</v>
@@ -3984,208 +3984,208 @@
         <v>4.1</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P14">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q14">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="s">
         <v>142</v>
@@ -4226,16 +4226,16 @@
         <v>4.3</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P15">
         <v>2.12</v>
@@ -4244,184 +4244,184 @@
         <v>1.78</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN15">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AO15">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AP15">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU15">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV15">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AW15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AX15">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AY15">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AZ15">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB15">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BC15">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BD15">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BE15">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BF15">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BG15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BH15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BK15">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BL15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM15">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN15">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BO15">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BP15">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BQ15">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BR15">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BS15">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BT15">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BU15">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BV15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX15">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ15">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>70</v>
       </c>
       <c r="AB16">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC16">
         <v>7.8</v>
@@ -4549,7 +4549,7 @@
         <v>40</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN16">
         <v>18</v>
@@ -4558,115 +4558,115 @@
         <v>42</v>
       </c>
       <c r="AP16">
+        <v>13</v>
+      </c>
+      <c r="AQ16">
+        <v>12</v>
+      </c>
+      <c r="AR16">
+        <v>21</v>
+      </c>
+      <c r="AS16">
+        <v>44</v>
+      </c>
+      <c r="AT16">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU16">
+        <v>7.4</v>
+      </c>
+      <c r="AV16">
+        <v>13.5</v>
+      </c>
+      <c r="AW16">
+        <v>24</v>
+      </c>
+      <c r="AX16">
+        <v>12</v>
+      </c>
+      <c r="AY16">
+        <v>10</v>
+      </c>
+      <c r="AZ16">
+        <v>15.5</v>
+      </c>
+      <c r="BA16">
+        <v>28</v>
+      </c>
+      <c r="BB16">
+        <v>19.5</v>
+      </c>
+      <c r="BC16">
+        <v>21</v>
+      </c>
+      <c r="BD16">
+        <v>23</v>
+      </c>
+      <c r="BE16">
+        <v>36</v>
+      </c>
+      <c r="BF16">
+        <v>15.5</v>
+      </c>
+      <c r="BG16">
+        <v>30</v>
+      </c>
+      <c r="BH16">
         <v>3.55</v>
       </c>
-      <c r="AQ16">
+      <c r="BI16">
+        <v>2.74</v>
+      </c>
+      <c r="BJ16">
         <v>9.800000000000001</v>
       </c>
-      <c r="AR16">
+      <c r="BK16">
+        <v>5.1</v>
+      </c>
+      <c r="BL16">
         <v>120</v>
       </c>
-      <c r="AS16">
+      <c r="BM16">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN16">
         <v>5.3</v>
       </c>
-      <c r="AT16">
+      <c r="BO16">
+        <v>3.9</v>
+      </c>
+      <c r="BP16">
         <v>17</v>
       </c>
-      <c r="AU16">
+      <c r="BQ16">
+        <v>6.6</v>
+      </c>
+      <c r="BR16">
         <v>32</v>
       </c>
-      <c r="AV16">
+      <c r="BS16">
+        <v>8</v>
+      </c>
+      <c r="BT16">
         <v>7</v>
       </c>
-      <c r="AW16">
+      <c r="BU16">
+        <v>5.1</v>
+      </c>
+      <c r="BV16">
         <v>30</v>
       </c>
-      <c r="AX16">
+      <c r="BW16">
+        <v>7.8</v>
+      </c>
+      <c r="BX16">
         <v>42</v>
       </c>
-      <c r="AY16">
+      <c r="BY16">
+        <v>8.6</v>
+      </c>
+      <c r="BZ16">
         <v>27</v>
-      </c>
-      <c r="AZ16">
-        <v>13</v>
-      </c>
-      <c r="BA16">
-        <v>12</v>
-      </c>
-      <c r="BB16">
-        <v>21</v>
-      </c>
-      <c r="BC16">
-        <v>44</v>
-      </c>
-      <c r="BD16">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE16">
-        <v>7.4</v>
-      </c>
-      <c r="BF16">
-        <v>13.5</v>
-      </c>
-      <c r="BG16">
-        <v>24</v>
-      </c>
-      <c r="BH16">
-        <v>12</v>
-      </c>
-      <c r="BI16">
-        <v>10</v>
-      </c>
-      <c r="BJ16">
-        <v>15.5</v>
-      </c>
-      <c r="BK16">
-        <v>28</v>
-      </c>
-      <c r="BL16">
-        <v>19.5</v>
-      </c>
-      <c r="BM16">
-        <v>21</v>
-      </c>
-      <c r="BN16">
-        <v>23</v>
-      </c>
-      <c r="BO16">
-        <v>36</v>
-      </c>
-      <c r="BP16">
-        <v>15.5</v>
-      </c>
-      <c r="BQ16">
-        <v>30</v>
-      </c>
-      <c r="BR16">
-        <v>2.74</v>
-      </c>
-      <c r="BS16">
-        <v>5.1</v>
-      </c>
-      <c r="BT16">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BU16">
-        <v>3.9</v>
-      </c>
-      <c r="BV16">
-        <v>6.6</v>
-      </c>
-      <c r="BW16">
-        <v>8</v>
-      </c>
-      <c r="BX16">
-        <v>5.1</v>
-      </c>
-      <c r="BY16">
-        <v>7.8</v>
-      </c>
-      <c r="BZ16">
-        <v>8.6</v>
       </c>
       <c r="CA16">
         <v>7.6</v>
@@ -4949,7 +4949,7 @@
         <v>3.8</v>
       </c>
       <c r="K18">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -5188,7 +5188,7 @@
         <v>12</v>
       </c>
       <c r="J19">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="K19">
         <v>7.8</v>
@@ -5284,88 +5284,88 @@
         <v>110</v>
       </c>
       <c r="AP19">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AU19">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AV19">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AW19">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AX19">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY19">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ19">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BA19">
-        <v>40</v>
+        <v>5.5</v>
       </c>
       <c r="BB19">
+        <v>10.5</v>
+      </c>
+      <c r="BC19">
+        <v>10</v>
+      </c>
+      <c r="BD19">
+        <v>20</v>
+      </c>
+      <c r="BE19">
         <v>5.6</v>
       </c>
-      <c r="BC19">
-        <v>5.8</v>
-      </c>
-      <c r="BD19">
-        <v>12</v>
-      </c>
-      <c r="BE19">
-        <v>4.6</v>
-      </c>
       <c r="BF19">
-        <v>5.2</v>
+        <v>2.98</v>
       </c>
       <c r="BG19">
         <v>5.6</v>
       </c>
       <c r="BH19">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BI19">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BJ19">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BK19">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BL19">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BM19">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BN19">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BO19">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BP19">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="BQ19">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BR19">
         <v>0</v>
@@ -5418,16 +5418,16 @@
         <v>139</v>
       </c>
       <c r="F20">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G20">
         <v>2.08</v>
       </c>
       <c r="H20">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I20">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J20">
         <v>3.95</v>
@@ -5487,7 +5487,7 @@
         <v>11.5</v>
       </c>
       <c r="AC20">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD20">
         <v>15.5</v>
@@ -5526,115 +5526,115 @@
         <v>36</v>
       </c>
       <c r="AP20">
+        <v>17</v>
+      </c>
+      <c r="AQ20">
+        <v>15</v>
+      </c>
+      <c r="AR20">
+        <v>23</v>
+      </c>
+      <c r="AS20">
+        <v>32</v>
+      </c>
+      <c r="AT20">
+        <v>10</v>
+      </c>
+      <c r="AU20">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV20">
+        <v>13.5</v>
+      </c>
+      <c r="AW20">
+        <v>32</v>
+      </c>
+      <c r="AX20">
+        <v>12.5</v>
+      </c>
+      <c r="AY20">
+        <v>9.6</v>
+      </c>
+      <c r="AZ20">
+        <v>14.5</v>
+      </c>
+      <c r="BA20">
+        <v>36</v>
+      </c>
+      <c r="BB20">
+        <v>17</v>
+      </c>
+      <c r="BC20">
+        <v>18</v>
+      </c>
+      <c r="BD20">
+        <v>20</v>
+      </c>
+      <c r="BE20">
+        <v>34</v>
+      </c>
+      <c r="BF20">
+        <v>11</v>
+      </c>
+      <c r="BG20">
+        <v>29</v>
+      </c>
+      <c r="BH20">
         <v>4</v>
       </c>
-      <c r="AQ20">
+      <c r="BI20">
+        <v>3.15</v>
+      </c>
+      <c r="BJ20">
         <v>9.4</v>
       </c>
-      <c r="AR20">
+      <c r="BK20">
+        <v>4.9</v>
+      </c>
+      <c r="BL20">
         <v>100</v>
       </c>
-      <c r="AS20">
+      <c r="BM20">
+        <v>9.4</v>
+      </c>
+      <c r="BN20">
         <v>5.2</v>
       </c>
-      <c r="AT20">
+      <c r="BO20">
+        <v>4</v>
+      </c>
+      <c r="BP20">
         <v>14.5</v>
       </c>
-      <c r="AU20">
+      <c r="BQ20">
+        <v>6</v>
+      </c>
+      <c r="BR20">
         <v>26</v>
       </c>
-      <c r="AV20">
+      <c r="BS20">
+        <v>7.4</v>
+      </c>
+      <c r="BT20">
         <v>7.6</v>
       </c>
-      <c r="AW20">
+      <c r="BU20">
+        <v>5.7</v>
+      </c>
+      <c r="BV20">
         <v>30</v>
       </c>
-      <c r="AX20">
+      <c r="BW20">
+        <v>7.6</v>
+      </c>
+      <c r="BX20">
         <v>38</v>
       </c>
-      <c r="AY20">
+      <c r="BY20">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ20">
         <v>21</v>
-      </c>
-      <c r="AZ20">
-        <v>17</v>
-      </c>
-      <c r="BA20">
-        <v>15</v>
-      </c>
-      <c r="BB20">
-        <v>23</v>
-      </c>
-      <c r="BC20">
-        <v>32</v>
-      </c>
-      <c r="BD20">
-        <v>10</v>
-      </c>
-      <c r="BE20">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF20">
-        <v>13.5</v>
-      </c>
-      <c r="BG20">
-        <v>32</v>
-      </c>
-      <c r="BH20">
-        <v>12.5</v>
-      </c>
-      <c r="BI20">
-        <v>9.6</v>
-      </c>
-      <c r="BJ20">
-        <v>14.5</v>
-      </c>
-      <c r="BK20">
-        <v>36</v>
-      </c>
-      <c r="BL20">
-        <v>17</v>
-      </c>
-      <c r="BM20">
-        <v>18</v>
-      </c>
-      <c r="BN20">
-        <v>20</v>
-      </c>
-      <c r="BO20">
-        <v>34</v>
-      </c>
-      <c r="BP20">
-        <v>11</v>
-      </c>
-      <c r="BQ20">
-        <v>29</v>
-      </c>
-      <c r="BR20">
-        <v>3.15</v>
-      </c>
-      <c r="BS20">
-        <v>4.9</v>
-      </c>
-      <c r="BT20">
-        <v>9.4</v>
-      </c>
-      <c r="BU20">
-        <v>4</v>
-      </c>
-      <c r="BV20">
-        <v>6</v>
-      </c>
-      <c r="BW20">
-        <v>7.4</v>
-      </c>
-      <c r="BX20">
-        <v>5.7</v>
-      </c>
-      <c r="BY20">
-        <v>7.6</v>
-      </c>
-      <c r="BZ20">
-        <v>8.199999999999999</v>
       </c>
       <c r="CA20">
         <v>7</v>
@@ -5768,115 +5768,115 @@
         <v>25</v>
       </c>
       <c r="AP21">
+        <v>15</v>
+      </c>
+      <c r="AQ21">
+        <v>11.5</v>
+      </c>
+      <c r="AR21">
+        <v>17.5</v>
+      </c>
+      <c r="AS21">
+        <v>7.4</v>
+      </c>
+      <c r="AT21">
+        <v>11</v>
+      </c>
+      <c r="AU21">
+        <v>7.6</v>
+      </c>
+      <c r="AV21">
+        <v>11</v>
+      </c>
+      <c r="AW21">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX21">
+        <v>15</v>
+      </c>
+      <c r="AY21">
+        <v>10.5</v>
+      </c>
+      <c r="AZ21">
+        <v>13.5</v>
+      </c>
+      <c r="BA21">
+        <v>7.2</v>
+      </c>
+      <c r="BB21">
+        <v>7.2</v>
+      </c>
+      <c r="BC21">
+        <v>22</v>
+      </c>
+      <c r="BD21">
+        <v>7.2</v>
+      </c>
+      <c r="BE21">
+        <v>7.8</v>
+      </c>
+      <c r="BF21">
+        <v>16</v>
+      </c>
+      <c r="BG21">
+        <v>19.5</v>
+      </c>
+      <c r="BH21">
         <v>3.85</v>
       </c>
-      <c r="AQ21">
+      <c r="BI21">
+        <v>3.05</v>
+      </c>
+      <c r="BJ21">
         <v>9.4</v>
       </c>
-      <c r="AR21">
-        <v>1000</v>
-      </c>
-      <c r="AS21">
+      <c r="BK21">
+        <v>4.9</v>
+      </c>
+      <c r="BL21">
+        <v>1000</v>
+      </c>
+      <c r="BM21">
+        <v>9.4</v>
+      </c>
+      <c r="BN21">
         <v>5.9</v>
       </c>
-      <c r="AT21">
+      <c r="BO21">
+        <v>4.5</v>
+      </c>
+      <c r="BP21">
         <v>19.5</v>
       </c>
-      <c r="AU21">
+      <c r="BQ21">
+        <v>6.8</v>
+      </c>
+      <c r="BR21">
         <v>30</v>
       </c>
-      <c r="AV21">
+      <c r="BS21">
+        <v>7.6</v>
+      </c>
+      <c r="BT21">
         <v>6.4</v>
       </c>
-      <c r="AW21">
+      <c r="BU21">
+        <v>4.8</v>
+      </c>
+      <c r="BV21">
         <v>22</v>
       </c>
-      <c r="AX21">
+      <c r="BW21">
+        <v>7</v>
+      </c>
+      <c r="BX21">
         <v>32</v>
       </c>
-      <c r="AY21">
-        <v>0</v>
-      </c>
-      <c r="AZ21">
-        <v>15</v>
-      </c>
-      <c r="BA21">
-        <v>11.5</v>
-      </c>
-      <c r="BB21">
-        <v>17.5</v>
-      </c>
-      <c r="BC21">
-        <v>7.4</v>
-      </c>
-      <c r="BD21">
-        <v>11</v>
-      </c>
-      <c r="BE21">
-        <v>7.6</v>
-      </c>
-      <c r="BF21">
-        <v>11</v>
-      </c>
-      <c r="BG21">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BH21">
-        <v>15</v>
-      </c>
-      <c r="BI21">
-        <v>10.5</v>
-      </c>
-      <c r="BJ21">
-        <v>13.5</v>
-      </c>
-      <c r="BK21">
-        <v>7.2</v>
-      </c>
-      <c r="BL21">
-        <v>7.2</v>
-      </c>
-      <c r="BM21">
-        <v>22</v>
-      </c>
-      <c r="BN21">
-        <v>7.2</v>
-      </c>
-      <c r="BO21">
+      <c r="BY21">
         <v>7.8</v>
       </c>
-      <c r="BP21">
-        <v>16</v>
-      </c>
-      <c r="BQ21">
-        <v>19.5</v>
-      </c>
-      <c r="BR21">
-        <v>3.05</v>
-      </c>
-      <c r="BS21">
-        <v>4.9</v>
-      </c>
-      <c r="BT21">
-        <v>9.4</v>
-      </c>
-      <c r="BU21">
-        <v>4.5</v>
-      </c>
-      <c r="BV21">
-        <v>6.8</v>
-      </c>
-      <c r="BW21">
-        <v>7.6</v>
-      </c>
-      <c r="BX21">
-        <v>4.8</v>
-      </c>
-      <c r="BY21">
-        <v>7</v>
-      </c>
       <c r="BZ21">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="CA21">
         <v>0</v>
@@ -6010,115 +6010,115 @@
         <v>1000</v>
       </c>
       <c r="AP22">
+        <v>27</v>
+      </c>
+      <c r="AQ22">
+        <v>27</v>
+      </c>
+      <c r="AR22">
+        <v>42</v>
+      </c>
+      <c r="AS22">
+        <v>110</v>
+      </c>
+      <c r="AT22">
+        <v>11.5</v>
+      </c>
+      <c r="AU22">
+        <v>15</v>
+      </c>
+      <c r="AV22">
+        <v>38</v>
+      </c>
+      <c r="AW22">
+        <v>44</v>
+      </c>
+      <c r="AX22">
+        <v>8.6</v>
+      </c>
+      <c r="AY22">
+        <v>10</v>
+      </c>
+      <c r="AZ22">
+        <v>25</v>
+      </c>
+      <c r="BA22">
+        <v>40</v>
+      </c>
+      <c r="BB22">
+        <v>9.6</v>
+      </c>
+      <c r="BC22">
+        <v>11.5</v>
+      </c>
+      <c r="BD22">
+        <v>20</v>
+      </c>
+      <c r="BE22">
+        <v>42</v>
+      </c>
+      <c r="BF22">
+        <v>3.35</v>
+      </c>
+      <c r="BG22">
+        <v>46</v>
+      </c>
+      <c r="BH22">
         <v>5.2</v>
       </c>
-      <c r="AQ22">
+      <c r="BI22">
+        <v>3.95</v>
+      </c>
+      <c r="BJ22">
         <v>11.5</v>
       </c>
-      <c r="AR22">
+      <c r="BK22">
+        <v>6.6</v>
+      </c>
+      <c r="BL22">
         <v>120</v>
       </c>
-      <c r="AS22">
+      <c r="BM22">
+        <v>14.5</v>
+      </c>
+      <c r="BN22">
         <v>4.1</v>
       </c>
-      <c r="AT22">
+      <c r="BO22">
+        <v>3.25</v>
+      </c>
+      <c r="BP22">
         <v>7</v>
       </c>
-      <c r="AU22">
+      <c r="BQ22">
+        <v>5.3</v>
+      </c>
+      <c r="BR22">
         <v>19.5</v>
       </c>
-      <c r="AV22">
-        <v>14.5</v>
-      </c>
-      <c r="AW22">
-        <v>85</v>
-      </c>
-      <c r="AX22">
-        <v>70</v>
-      </c>
-      <c r="AY22">
-        <v>8.4</v>
-      </c>
-      <c r="AZ22">
-        <v>32</v>
-      </c>
-      <c r="BA22">
-        <v>26</v>
-      </c>
-      <c r="BB22">
-        <v>40</v>
-      </c>
-      <c r="BC22">
-        <v>110</v>
-      </c>
-      <c r="BD22">
-        <v>11.5</v>
-      </c>
-      <c r="BE22">
-        <v>15</v>
-      </c>
-      <c r="BF22">
-        <v>38</v>
-      </c>
-      <c r="BG22">
-        <v>44</v>
-      </c>
-      <c r="BH22">
-        <v>8.6</v>
-      </c>
-      <c r="BI22">
-        <v>10</v>
-      </c>
-      <c r="BJ22">
-        <v>25</v>
-      </c>
-      <c r="BK22">
-        <v>40</v>
-      </c>
-      <c r="BL22">
-        <v>9.6</v>
-      </c>
-      <c r="BM22">
-        <v>11.5</v>
-      </c>
-      <c r="BN22">
-        <v>20</v>
-      </c>
-      <c r="BO22">
-        <v>42</v>
-      </c>
-      <c r="BP22">
-        <v>3.35</v>
-      </c>
-      <c r="BQ22">
-        <v>44</v>
-      </c>
-      <c r="BR22">
-        <v>3.95</v>
-      </c>
       <c r="BS22">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT22">
         <v>14.5</v>
       </c>
       <c r="BU22">
-        <v>3.25</v>
+        <v>7.6</v>
       </c>
       <c r="BV22">
-        <v>5.3</v>
+        <v>85</v>
       </c>
       <c r="BW22">
-        <v>8.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BX22">
-        <v>7.6</v>
+        <v>70</v>
       </c>
       <c r="BY22">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BZ22">
-        <v>13</v>
+        <v>8.4</v>
       </c>
       <c r="CA22">
         <v>5.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-14.xlsx
@@ -881,13 +881,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O2" t="n">
         <v>1.14</v>
       </c>
       <c r="P2" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q2" t="n">
         <v>1.14</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-12 13:38:45</t>
+          <t>2026-05-12 15:58:19</t>
         </is>
       </c>
     </row>
@@ -1135,13 +1135,13 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="O3" t="n">
         <v>1.17</v>
       </c>
       <c r="P3" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q3" t="n">
         <v>1.16</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-12 13:38:45</t>
+          <t>2026-05-12 15:58:19</t>
         </is>
       </c>
     </row>
@@ -1389,13 +1389,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="O4" t="n">
         <v>1.16</v>
       </c>
       <c r="P4" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q4" t="n">
         <v>1.16</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:38:45</t>
+          <t>2026-05-12 15:58:19</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="G5" t="n">
         <v>1.82</v>
@@ -1643,7 +1643,7 @@
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="O5" t="n">
         <v>1.34</v>
@@ -1655,16 +1655,16 @@
         <v>1.98</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S5" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="T5" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="U5" t="n">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="V5" t="n">
         <v>1.19</v>
@@ -1676,7 +1676,7 @@
         <v>17</v>
       </c>
       <c r="Y5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z5" t="n">
         <v>55</v>
@@ -1685,34 +1685,34 @@
         <v>190</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE5" t="n">
         <v>110</v>
       </c>
       <c r="AF5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI5" t="n">
         <v>110</v>
       </c>
       <c r="AJ5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL5" t="n">
         <v>48</v>
@@ -1721,7 +1721,7 @@
         <v>160</v>
       </c>
       <c r="AN5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO5" t="n">
         <v>140</v>
@@ -1733,10 +1733,10 @@
         <v>13</v>
       </c>
       <c r="AR5" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AT5" t="n">
         <v>7</v>
@@ -1748,7 +1748,7 @@
         <v>19</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AX5" t="n">
         <v>8.800000000000001</v>
@@ -1760,7 +1760,7 @@
         <v>18.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BB5" t="n">
         <v>13</v>
@@ -1769,16 +1769,16 @@
         <v>16.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BF5" t="n">
         <v>9</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-12 13:38:45</t>
+          <t>2026-05-12 15:58:19</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-12 13:38:45</t>
+          <t>2026-05-12 15:58:19</t>
         </is>
       </c>
     </row>
@@ -2151,16 +2151,16 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O7" t="n">
         <v>1.22</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="R7" t="n">
         <v>1.24</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-12 13:38:45</t>
+          <t>2026-05-12 15:58:19</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="O8" t="n">
         <v>1.01</v>
@@ -2414,13 +2414,13 @@
         <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.02</v>
+        <v>1.31</v>
       </c>
       <c r="R8" t="n">
         <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-12 13:38:45</t>
+          <t>2026-05-12 15:58:19</t>
         </is>
       </c>
     </row>
@@ -2659,13 +2659,13 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="O9" t="n">
         <v>1.09</v>
       </c>
       <c r="P9" t="n">
-        <v>1.25</v>
+        <v>3.9</v>
       </c>
       <c r="Q9" t="n">
         <v>1.09</v>
@@ -2674,7 +2674,7 @@
         <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="T9" t="n">
         <v>1.11</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-12 13:38:45</t>
+          <t>2026-05-12 15:58:19</t>
         </is>
       </c>
     </row>
@@ -2913,16 +2913,16 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="O10" t="n">
         <v>1.2</v>
       </c>
       <c r="P10" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="R10" t="n">
         <v>1.24</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-12 13:38:45</t>
+          <t>2026-05-12 15:58:19</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-12 13:38:45</t>
+          <t>2026-05-12 15:58:19</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3463,7 @@
         <v>40</v>
       </c>
       <c r="AB12" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AC12" t="n">
         <v>11.5</v>
@@ -3505,7 +3505,7 @@
         <v>12.5</v>
       </c>
       <c r="AP12" t="n">
-        <v>9.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="AQ12" t="n">
         <v>14.5</v>
@@ -3514,7 +3514,7 @@
         <v>17.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.6</v>
+        <v>28</v>
       </c>
       <c r="AT12" t="n">
         <v>14</v>
@@ -3556,13 +3556,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BG12" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BH12" t="n">
         <v>5</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BJ12" t="n">
         <v>8.199999999999999</v>
@@ -3574,7 +3574,7 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BN12" t="n">
         <v>6.4</v>
@@ -3586,13 +3586,13 @@
         <v>16.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BR12" t="n">
         <v>22</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT12" t="n">
         <v>6.6</v>
@@ -3604,23 +3604,23 @@
         <v>17.5</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BX12" t="n">
         <v>22</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ12" t="n">
         <v>13</v>
       </c>
       <c r="CA12" t="n">
-        <v>9.4</v>
+        <v>6.8</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-12 13:38:45</t>
+          <t>2026-05-12 15:58:19</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="G13" t="n">
         <v>2.34</v>
@@ -3666,7 +3666,7 @@
         <v>3.3</v>
       </c>
       <c r="K13" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -3690,7 +3690,7 @@
         <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>2.82</v>
+        <v>2.66</v>
       </c>
       <c r="T13" t="n">
         <v>1.11</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-12 13:38:45</t>
+          <t>2026-05-12 15:58:19</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
         <v>5.2</v>
       </c>
       <c r="I14" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J14" t="n">
         <v>3.6</v>
@@ -3926,7 +3926,7 @@
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N14" t="n">
         <v>3.45</v>
@@ -3938,13 +3938,13 @@
         <v>1.84</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="R14" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S14" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="T14" t="n">
         <v>1.9</v>
@@ -3956,22 +3956,22 @@
         <v>1.2</v>
       </c>
       <c r="W14" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z14" t="n">
         <v>50</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC14" t="n">
         <v>10</v>
@@ -3986,13 +3986,13 @@
         <v>12</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ14" t="n">
         <v>22</v>
@@ -4007,22 +4007,22 @@
         <v>150</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.59</v>
+        <v>10.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.59</v>
+        <v>13</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.54</v>
+        <v>4.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.59</v>
+        <v>5</v>
       </c>
       <c r="AT14" t="n">
         <v>6.2</v>
@@ -4034,19 +4034,19 @@
         <v>16.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.56</v>
+        <v>4.9</v>
       </c>
       <c r="AX14" t="n">
         <v>8</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.59</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.59</v>
+        <v>18.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.59</v>
+        <v>4.9</v>
       </c>
       <c r="BB14" t="n">
         <v>14</v>
@@ -4055,16 +4055,16 @@
         <v>15</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.53</v>
+        <v>4.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.57</v>
+        <v>4.9</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.59</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.59</v>
+        <v>4.9</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-12 13:38:45</t>
+          <t>2026-05-12 15:58:19</t>
         </is>
       </c>
     </row>
@@ -4183,28 +4183,28 @@
         <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="O15" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="P15" t="n">
         <v>2.12</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R15" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="V15" t="n">
         <v>1.2</v>
@@ -4294,7 +4294,7 @@
         <v>10</v>
       </c>
       <c r="AY15" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AZ15" t="n">
         <v>16.5</v>
@@ -4324,19 +4324,19 @@
         <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="BJ15" t="n">
         <v>14.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>6.2</v>
+        <v>1.66</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>21</v>
+        <v>1.87</v>
       </c>
       <c r="BN15" t="n">
         <v>6.2</v>
@@ -4348,13 +4348,13 @@
         <v>17</v>
       </c>
       <c r="BQ15" t="n">
-        <v>7.2</v>
+        <v>1.69</v>
       </c>
       <c r="BR15" t="n">
         <v>36</v>
       </c>
       <c r="BS15" t="n">
-        <v>14.5</v>
+        <v>1.78</v>
       </c>
       <c r="BT15" t="n">
         <v>12.5</v>
@@ -4366,13 +4366,13 @@
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>21</v>
+        <v>1.81</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>21</v>
+        <v>1.82</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-12 13:38:45</t>
+          <t>2026-05-12 15:58:19</t>
         </is>
       </c>
     </row>
@@ -4416,10 +4416,10 @@
         <v>2.24</v>
       </c>
       <c r="G16" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H16" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I16" t="n">
         <v>3.65</v>
@@ -4428,7 +4428,7 @@
         <v>3.55</v>
       </c>
       <c r="K16" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -4464,13 +4464,13 @@
         <v>1.37</v>
       </c>
       <c r="W16" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X16" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z16" t="n">
         <v>25</v>
@@ -4488,7 +4488,7 @@
         <v>15</v>
       </c>
       <c r="AE16" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AF16" t="n">
         <v>14</v>
@@ -4500,16 +4500,16 @@
         <v>17.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>300</v>
+        <v>55</v>
       </c>
       <c r="AJ16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK16" t="n">
         <v>24</v>
       </c>
       <c r="AL16" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM16" t="n">
         <v>95</v>
@@ -4524,10 +4524,10 @@
         <v>13</v>
       </c>
       <c r="AQ16" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS16" t="n">
         <v>44</v>
@@ -4542,43 +4542,43 @@
         <v>13.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AX16" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY16" t="n">
         <v>10</v>
       </c>
       <c r="AZ16" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA16" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="BB16" t="n">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="BC16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD16" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="BE16" t="n">
         <v>36</v>
       </c>
       <c r="BF16" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BH16" t="n">
         <v>3.55</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="BJ16" t="n">
         <v>9.800000000000001</v>
@@ -4590,13 +4590,13 @@
         <v>120</v>
       </c>
       <c r="BM16" t="n">
-        <v>9.800000000000001</v>
+        <v>27</v>
       </c>
       <c r="BN16" t="n">
         <v>5.3</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BP16" t="n">
         <v>17</v>
@@ -4614,16 +4614,16 @@
         <v>7</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BV16" t="n">
         <v>30</v>
       </c>
       <c r="BW16" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BX16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY16" t="n">
         <v>8.6</v>
@@ -4632,11 +4632,11 @@
         <v>27</v>
       </c>
       <c r="CA16" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-12 13:38:45</t>
+          <t>2026-05-12 15:58:19</t>
         </is>
       </c>
     </row>
@@ -4685,212 +4685,212 @@
         <v>4.5</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P17" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BH17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-12 13:38:45</t>
+          <t>2026-05-12 15:58:19</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4930,7 @@
         <v>1.86</v>
       </c>
       <c r="I18" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="J18" t="n">
         <v>3.8</v>
@@ -4939,16 +4939,16 @@
         <v>4.5</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P18" t="n">
         <v>2.3</v>
@@ -4957,194 +4957,194 @@
         <v>1.61</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BH18" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BI18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BK18" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BL18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BN18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BO18" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BP18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BR18" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BS18" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BT18" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BU18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BV18" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BW18" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX18" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BY18" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="CA18" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-12 13:38:45</t>
+          <t>2026-05-12 15:58:19</t>
         </is>
       </c>
     </row>
@@ -5193,16 +5193,16 @@
         <v>7.8</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M19" t="n">
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="P19" t="n">
         <v>3.55</v>
@@ -5211,10 +5211,10 @@
         <v>1.33</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="T19" t="n">
         <v>1.72</v>
@@ -5223,10 +5223,10 @@
         <v>2.22</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="X19" t="n">
         <v>950</v>
@@ -5268,7 +5268,7 @@
         <v>14</v>
       </c>
       <c r="AK19" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AL19" t="n">
         <v>30</v>
@@ -5283,28 +5283,28 @@
         <v>110</v>
       </c>
       <c r="AP19" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="AR19" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT19" t="n">
         <v>12</v>
       </c>
       <c r="AU19" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AV19" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AX19" t="n">
         <v>10.5</v>
@@ -5313,10 +5313,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ19" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BB19" t="n">
         <v>10.5</v>
@@ -5328,77 +5328,77 @@
         <v>20</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BF19" t="n">
         <v>2.98</v>
       </c>
       <c r="BG19" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH19" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BI19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BK19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BL19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN19" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BO19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BP19" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ19" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BR19" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BS19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BT19" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BU19" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BV19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="CA19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-12 13:38:45</t>
+          <t>2026-05-12 15:58:19</t>
         </is>
       </c>
     </row>
@@ -5429,25 +5429,25 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G20" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H20" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I20" t="n">
         <v>3.8</v>
       </c>
       <c r="J20" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K20" t="n">
         <v>4</v>
       </c>
       <c r="L20" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
@@ -5480,16 +5480,16 @@
         <v>1.35</v>
       </c>
       <c r="W20" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="X20" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y20" t="n">
         <v>17</v>
       </c>
       <c r="Z20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA20" t="n">
         <v>75</v>
@@ -5501,13 +5501,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD20" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE20" t="n">
         <v>40</v>
       </c>
       <c r="AF20" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG20" t="n">
         <v>10.5</v>
@@ -5516,70 +5516,70 @@
         <v>16.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AJ20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL20" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM20" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN20" t="n">
         <v>12.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP20" t="n">
         <v>17</v>
       </c>
       <c r="AQ20" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AS20" t="n">
         <v>32</v>
       </c>
       <c r="AT20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU20" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV20" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW20" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AX20" t="n">
         <v>12.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ20" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA20" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BB20" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="BC20" t="n">
         <v>18</v>
       </c>
       <c r="BD20" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="BE20" t="n">
         <v>34</v>
@@ -5591,10 +5591,10 @@
         <v>29</v>
       </c>
       <c r="BH20" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BJ20" t="n">
         <v>9.4</v>
@@ -5606,19 +5606,19 @@
         <v>100</v>
       </c>
       <c r="BM20" t="n">
-        <v>9.4</v>
+        <v>24</v>
       </c>
       <c r="BN20" t="n">
         <v>5.2</v>
       </c>
       <c r="BO20" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BP20" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BQ20" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR20" t="n">
         <v>26</v>
@@ -5636,7 +5636,7 @@
         <v>30</v>
       </c>
       <c r="BW20" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX20" t="n">
         <v>38</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-12 13:38:45</t>
+          <t>2026-05-12 15:58:19</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G21" t="n">
         <v>2.68</v>
@@ -5722,7 +5722,7 @@
         <v>1.42</v>
       </c>
       <c r="S21" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
         <v>1.67</v>
@@ -5737,7 +5737,7 @@
         <v>1.6</v>
       </c>
       <c r="X21" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y21" t="n">
         <v>13.5</v>
@@ -5752,7 +5752,7 @@
         <v>13</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD21" t="n">
         <v>13.5</v>
@@ -5761,7 +5761,7 @@
         <v>32</v>
       </c>
       <c r="AF21" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG21" t="n">
         <v>13</v>
@@ -5800,7 +5800,7 @@
         <v>17.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT21" t="n">
         <v>11</v>
@@ -5812,7 +5812,7 @@
         <v>11</v>
       </c>
       <c r="AW21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX21" t="n">
         <v>15</v>
@@ -5824,19 +5824,19 @@
         <v>13.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB21" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC21" t="n">
         <v>22</v>
       </c>
       <c r="BD21" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE21" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BF21" t="n">
         <v>16</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-12 13:38:45</t>
+          <t>2026-05-12 15:58:19</t>
         </is>
       </c>
     </row>
@@ -5937,76 +5937,76 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="G22" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="H22" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="I22" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="J22" t="n">
+        <v>7</v>
+      </c>
+      <c r="K22" t="n">
         <v>7.4</v>
       </c>
-      <c r="K22" t="n">
-        <v>7.6</v>
-      </c>
       <c r="L22" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M22" t="n">
         <v>1.02</v>
       </c>
       <c r="N22" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="O22" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P22" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="R22" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="S22" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="T22" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U22" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V22" t="n">
         <v>1.08</v>
       </c>
       <c r="W22" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="X22" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Y22" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA22" t="n">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="AB22" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC22" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AD22" t="n">
         <v>44</v>
@@ -6018,52 +6018,52 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AG22" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH22" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ22" t="n">
         <v>11</v>
       </c>
       <c r="AK22" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AL22" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM22" t="n">
         <v>130</v>
       </c>
       <c r="AN22" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AO22" t="n">
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR22" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AS22" t="n">
-        <v>110</v>
+        <v>16.5</v>
       </c>
       <c r="AT22" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AU22" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AV22" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="AW22" t="n">
         <v>44</v>
@@ -6072,34 +6072,34 @@
         <v>8.6</v>
       </c>
       <c r="AY22" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="BA22" t="n">
         <v>40</v>
       </c>
       <c r="BB22" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BC22" t="n">
         <v>11.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BE22" t="n">
         <v>42</v>
       </c>
       <c r="BF22" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="BG22" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BH22" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BI22" t="n">
         <v>3.95</v>
@@ -6108,19 +6108,19 @@
         <v>11.5</v>
       </c>
       <c r="BK22" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL22" t="n">
         <v>120</v>
       </c>
       <c r="BM22" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN22" t="n">
         <v>4.1</v>
       </c>
       <c r="BO22" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BP22" t="n">
         <v>7</v>
@@ -6132,35 +6132,35 @@
         <v>19.5</v>
       </c>
       <c r="BS22" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT22" t="n">
         <v>14.5</v>
       </c>
       <c r="BU22" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BV22" t="n">
         <v>85</v>
       </c>
       <c r="BW22" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BX22" t="n">
         <v>70</v>
       </c>
       <c r="BY22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BZ22" t="n">
         <v>8.4</v>
       </c>
       <c r="CA22" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-12 13:38:45</t>
+          <t>2026-05-12 15:58:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB22"/>
+  <dimension ref="A1:CB23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -881,13 +881,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="O2" t="n">
         <v>1.14</v>
       </c>
       <c r="P2" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Q2" t="n">
         <v>1.14</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-12 15:58:19</t>
+          <t>2026-05-12 18:15:57</t>
         </is>
       </c>
     </row>
@@ -1135,13 +1135,13 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="O3" t="n">
         <v>1.17</v>
       </c>
       <c r="P3" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Q3" t="n">
         <v>1.16</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-12 15:58:19</t>
+          <t>2026-05-12 18:15:57</t>
         </is>
       </c>
     </row>
@@ -1389,13 +1389,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="O4" t="n">
         <v>1.16</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q4" t="n">
         <v>1.16</v>
@@ -1404,7 +1404,7 @@
         <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-12 15:58:19</t>
+          <t>2026-05-12 18:15:57</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="G5" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="H5" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1643,16 +1643,16 @@
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P5" t="n">
         <v>1.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
         <v>1.32</v>
@@ -1664,40 +1664,40 @@
         <v>1.92</v>
       </c>
       <c r="U5" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V5" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W5" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="X5" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z5" t="n">
         <v>55</v>
       </c>
       <c r="AA5" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC5" t="n">
         <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE5" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="AF5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG5" t="n">
         <v>12</v>
@@ -1706,7 +1706,7 @@
         <v>25</v>
       </c>
       <c r="AI5" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AJ5" t="n">
         <v>21</v>
@@ -1718,13 +1718,13 @@
         <v>48</v>
       </c>
       <c r="AM5" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN5" t="n">
         <v>14.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AP5" t="n">
         <v>10</v>
@@ -1733,10 +1733,10 @@
         <v>13</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.5</v>
+        <v>34</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AT5" t="n">
         <v>7</v>
@@ -1745,13 +1745,13 @@
         <v>7.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY5" t="n">
         <v>8.800000000000001</v>
@@ -1760,64 +1760,64 @@
         <v>18.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="BC5" t="n">
         <v>16.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BF5" t="n">
         <v>9</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BJ5" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BN5" t="n">
         <v>5.9</v>
       </c>
       <c r="BO5" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BP5" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="BR5" t="n">
         <v>44</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="BT5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BU5" t="n">
         <v>1.58</v>
@@ -1826,23 +1826,23 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="BZ5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-12 15:58:19</t>
+          <t>2026-05-12 18:15:57</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-12 15:58:19</t>
+          <t>2026-05-12 18:15:57</t>
         </is>
       </c>
     </row>
@@ -2151,13 +2151,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="O7" t="n">
         <v>1.22</v>
       </c>
       <c r="P7" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Q7" t="n">
         <v>1.22</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-12 15:58:19</t>
+          <t>2026-05-12 18:15:57</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-12 15:58:19</t>
+          <t>2026-05-12 18:15:57</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2665,7 @@
         <v>1.09</v>
       </c>
       <c r="P9" t="n">
-        <v>3.9</v>
+        <v>1.25</v>
       </c>
       <c r="Q9" t="n">
         <v>1.09</v>
@@ -2800,55 +2800,55 @@
         <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN9" t="n">
         <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-12 15:58:19</t>
+          <t>2026-05-12 18:15:57</t>
         </is>
       </c>
     </row>
@@ -2913,13 +2913,13 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="O10" t="n">
         <v>1.2</v>
       </c>
       <c r="P10" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Q10" t="n">
         <v>1.19</v>
@@ -3054,55 +3054,55 @@
         <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN10" t="n">
         <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-12 15:58:19</t>
+          <t>2026-05-12 18:15:57</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
         <v>2.2</v>
       </c>
       <c r="H11" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I11" t="n">
         <v>3.5</v>
@@ -3185,7 +3185,7 @@
         <v>2</v>
       </c>
       <c r="T11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="U11" t="n">
         <v>2.98</v>
@@ -3218,7 +3218,7 @@
         <v>22</v>
       </c>
       <c r="AE11" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AF11" t="n">
         <v>28</v>
@@ -3251,34 +3251,34 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AQ11" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AV11" t="n">
         <v>11</v>
       </c>
       <c r="AW11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AX11" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AZ11" t="n">
         <v>10</v>
@@ -3287,7 +3287,7 @@
         <v>20</v>
       </c>
       <c r="BB11" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="BC11" t="n">
         <v>13</v>
@@ -3299,74 +3299,74 @@
         <v>2.16</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BH11" t="n">
         <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BX11" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-12 15:58:19</t>
+          <t>2026-05-12 18:15:57</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-12 15:58:19</t>
+          <t>2026-05-12 18:15:57</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-12 15:58:19</t>
+          <t>2026-05-12 18:15:57</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
         <v>5.2</v>
       </c>
       <c r="I14" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J14" t="n">
         <v>3.6</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-12 15:58:19</t>
+          <t>2026-05-12 18:15:57</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="G15" t="n">
         <v>1.82</v>
@@ -4168,7 +4168,7 @@
         <v>4.9</v>
       </c>
       <c r="I15" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J15" t="n">
         <v>3.95</v>
@@ -4192,7 +4192,7 @@
         <v>2.12</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R15" t="n">
         <v>1.44</v>
@@ -4267,10 +4267,10 @@
         <v>80</v>
       </c>
       <c r="AP15" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AQ15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR15" t="n">
         <v>3.9</v>
@@ -4279,25 +4279,25 @@
         <v>4.1</v>
       </c>
       <c r="AT15" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU15" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW15" t="n">
         <v>4</v>
       </c>
       <c r="AX15" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AY15" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AZ15" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA15" t="n">
         <v>4</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-12 15:58:19</t>
+          <t>2026-05-12 18:15:57</t>
         </is>
       </c>
     </row>
@@ -4413,40 +4413,40 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G16" t="n">
         <v>2.26</v>
       </c>
       <c r="H16" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I16" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J16" t="n">
         <v>3.55</v>
       </c>
       <c r="K16" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M16" t="n">
         <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="O16" t="n">
         <v>1.33</v>
       </c>
       <c r="P16" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R16" t="n">
         <v>1.37</v>
@@ -4455,7 +4455,7 @@
         <v>3.55</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U16" t="n">
         <v>2.18</v>
@@ -4470,7 +4470,7 @@
         <v>14</v>
       </c>
       <c r="Y16" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z16" t="n">
         <v>25</v>
@@ -4479,7 +4479,7 @@
         <v>70</v>
       </c>
       <c r="AB16" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC16" t="n">
         <v>7.8</v>
@@ -4491,7 +4491,7 @@
         <v>42</v>
       </c>
       <c r="AF16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG16" t="n">
         <v>11</v>
@@ -4536,7 +4536,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV16" t="n">
         <v>13.5</v>
@@ -4560,7 +4560,7 @@
         <v>26</v>
       </c>
       <c r="BC16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD16" t="n">
         <v>34</v>
@@ -4569,7 +4569,7 @@
         <v>36</v>
       </c>
       <c r="BF16" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BG16" t="n">
         <v>36</v>
@@ -4590,7 +4590,7 @@
         <v>120</v>
       </c>
       <c r="BM16" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="BN16" t="n">
         <v>5.3</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-12 15:58:19</t>
+          <t>2026-05-12 18:15:57</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="G17" t="n">
         <v>1.88</v>
@@ -4676,7 +4676,7 @@
         <v>4.4</v>
       </c>
       <c r="I17" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="J17" t="n">
         <v>3.9</v>
@@ -4688,10 +4688,10 @@
         <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>2.04</v>
+        <v>3.9</v>
       </c>
       <c r="O17" t="n">
         <v>1.29</v>
@@ -4700,19 +4700,19 @@
         <v>2.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="R17" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="S17" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="V17" t="n">
         <v>1.27</v>
@@ -4721,176 +4721,176 @@
         <v>2.12</v>
       </c>
       <c r="X17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y17" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE17" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI17" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL17" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.1</v>
+        <v>15</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.1</v>
+        <v>15</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.16</v>
+        <v>4.6</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.16</v>
+        <v>4.9</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.16</v>
+        <v>8</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.16</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.16</v>
+        <v>16</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.14</v>
+        <v>4.7</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.16</v>
+        <v>10</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.16</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.16</v>
+        <v>17</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.14</v>
+        <v>4.7</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.16</v>
+        <v>17</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.16</v>
+        <v>16</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.13</v>
+        <v>4.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.16</v>
+        <v>4.9</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.16</v>
+        <v>8.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.16</v>
+        <v>4.7</v>
       </c>
       <c r="BH17" t="n">
         <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN17" t="n">
         <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ17" t="n">
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-12 15:58:19</t>
+          <t>2026-05-12 18:15:57</t>
         </is>
       </c>
     </row>
@@ -4921,13 +4921,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="G18" t="n">
         <v>4.4</v>
       </c>
       <c r="H18" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="I18" t="n">
         <v>2.04</v>
@@ -4945,7 +4945,7 @@
         <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
         <v>1.21</v>
@@ -4957,13 +4957,13 @@
         <v>1.61</v>
       </c>
       <c r="R18" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S18" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="T18" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U18" t="n">
         <v>2.32</v>
@@ -4975,7 +4975,7 @@
         <v>1.29</v>
       </c>
       <c r="X18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y18" t="n">
         <v>14.5</v>
@@ -4987,10 +4987,10 @@
         <v>26</v>
       </c>
       <c r="AB18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC18" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD18" t="n">
         <v>12.5</v>
@@ -5044,10 +5044,10 @@
         <v>14.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AW18" t="n">
         <v>14</v>
@@ -5065,19 +5065,19 @@
         <v>21</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE18" t="n">
         <v>4.7</v>
       </c>
       <c r="BF18" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BG18" t="n">
         <v>7.6</v>
@@ -5092,31 +5092,31 @@
         <v>9.4</v>
       </c>
       <c r="BK18" t="n">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="BN18" t="n">
         <v>8</v>
       </c>
       <c r="BO18" t="n">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="BP18" t="n">
         <v>30</v>
       </c>
       <c r="BQ18" t="n">
-        <v>21</v>
+        <v>7.4</v>
       </c>
       <c r="BR18" t="n">
         <v>36</v>
       </c>
       <c r="BS18" t="n">
-        <v>25</v>
+        <v>7.8</v>
       </c>
       <c r="BT18" t="n">
         <v>5.2</v>
@@ -5128,23 +5128,23 @@
         <v>13.5</v>
       </c>
       <c r="BW18" t="n">
-        <v>9.800000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="BX18" t="n">
         <v>24</v>
       </c>
       <c r="BY18" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="BZ18" t="n">
         <v>17.5</v>
       </c>
       <c r="CA18" t="n">
-        <v>12.5</v>
+        <v>6.4</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-12 15:58:19</t>
+          <t>2026-05-12 18:15:57</t>
         </is>
       </c>
     </row>
@@ -5193,7 +5193,7 @@
         <v>7.8</v>
       </c>
       <c r="L19" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
         <v>1.01</v>
@@ -5211,7 +5211,7 @@
         <v>1.33</v>
       </c>
       <c r="R19" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="S19" t="n">
         <v>1.84</v>
@@ -5346,13 +5346,13 @@
         <v>15</v>
       </c>
       <c r="BK19" t="n">
-        <v>7</v>
+        <v>2.64</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>21</v>
+        <v>3.2</v>
       </c>
       <c r="BN19" t="n">
         <v>5.9</v>
@@ -5370,25 +5370,25 @@
         <v>24</v>
       </c>
       <c r="BS19" t="n">
-        <v>11</v>
+        <v>2.82</v>
       </c>
       <c r="BT19" t="n">
         <v>18.5</v>
       </c>
       <c r="BU19" t="n">
-        <v>8.4</v>
+        <v>2.72</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>21</v>
+        <v>3.05</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>21</v>
+        <v>3.05</v>
       </c>
       <c r="BZ19" t="n">
         <v>10</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-12 15:58:19</t>
+          <t>2026-05-12 18:15:57</t>
         </is>
       </c>
     </row>
@@ -5429,13 +5429,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G20" t="n">
         <v>2.08</v>
       </c>
       <c r="H20" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I20" t="n">
         <v>3.8</v>
@@ -5465,10 +5465,10 @@
         <v>1.76</v>
       </c>
       <c r="R20" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S20" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T20" t="n">
         <v>1.68</v>
@@ -5498,7 +5498,7 @@
         <v>11.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD20" t="n">
         <v>15</v>
@@ -5513,7 +5513,7 @@
         <v>10.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI20" t="n">
         <v>44</v>
@@ -5543,7 +5543,7 @@
         <v>15.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS20" t="n">
         <v>32</v>
@@ -5561,7 +5561,7 @@
         <v>36</v>
       </c>
       <c r="AX20" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY20" t="n">
         <v>9.800000000000001</v>
@@ -5579,10 +5579,10 @@
         <v>18</v>
       </c>
       <c r="BD20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE20" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="BF20" t="n">
         <v>11</v>
@@ -5594,19 +5594,19 @@
         <v>3.95</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ20" t="n">
         <v>9.4</v>
       </c>
       <c r="BK20" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL20" t="n">
         <v>100</v>
       </c>
       <c r="BM20" t="n">
-        <v>24</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN20" t="n">
         <v>5.2</v>
@@ -5615,7 +5615,7 @@
         <v>4.3</v>
       </c>
       <c r="BP20" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BQ20" t="n">
         <v>6.2</v>
@@ -5624,7 +5624,7 @@
         <v>26</v>
       </c>
       <c r="BS20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT20" t="n">
         <v>7.6</v>
@@ -5642,7 +5642,7 @@
         <v>38</v>
       </c>
       <c r="BY20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ20" t="n">
         <v>21</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-12 15:58:19</t>
+          <t>2026-05-12 18:15:57</t>
         </is>
       </c>
     </row>
@@ -5683,19 +5683,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="G21" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H21" t="n">
         <v>2.86</v>
       </c>
       <c r="I21" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="J21" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K21" t="n">
         <v>3.7</v>
@@ -5731,7 +5731,7 @@
         <v>2.32</v>
       </c>
       <c r="V21" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W21" t="n">
         <v>1.6</v>
@@ -5848,7 +5848,7 @@
         <v>3.85</v>
       </c>
       <c r="BI21" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ21" t="n">
         <v>9.4</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-12 15:58:19</t>
+          <t>2026-05-12 18:15:57</t>
         </is>
       </c>
     </row>
@@ -5949,31 +5949,31 @@
         <v>13</v>
       </c>
       <c r="J22" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="K22" t="n">
         <v>7.4</v>
       </c>
       <c r="L22" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="M22" t="n">
         <v>1.02</v>
       </c>
       <c r="N22" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O22" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P22" t="n">
         <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R22" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="S22" t="n">
         <v>2.16</v>
@@ -5991,37 +5991,37 @@
         <v>4.4</v>
       </c>
       <c r="X22" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y22" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Z22" t="n">
         <v>120</v>
       </c>
       <c r="AA22" t="n">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="AB22" t="n">
         <v>12</v>
       </c>
       <c r="AC22" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AD22" t="n">
         <v>44</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF22" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AG22" t="n">
         <v>11</v>
       </c>
       <c r="AH22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI22" t="n">
         <v>120</v>
@@ -6030,7 +6030,7 @@
         <v>11</v>
       </c>
       <c r="AK22" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AL22" t="n">
         <v>30</v>
@@ -6039,31 +6039,31 @@
         <v>130</v>
       </c>
       <c r="AN22" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AP22" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AQ22" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="AR22" t="n">
         <v>40</v>
       </c>
       <c r="AS22" t="n">
-        <v>16.5</v>
+        <v>55</v>
       </c>
       <c r="AT22" t="n">
         <v>10.5</v>
       </c>
       <c r="AU22" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AV22" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AW22" t="n">
         <v>44</v>
@@ -6072,10 +6072,10 @@
         <v>8.6</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ22" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BA22" t="n">
         <v>40</v>
@@ -6087,40 +6087,40 @@
         <v>11.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="BE22" t="n">
         <v>42</v>
       </c>
       <c r="BF22" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BG22" t="n">
         <v>44</v>
       </c>
       <c r="BH22" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BI22" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BJ22" t="n">
         <v>11.5</v>
       </c>
       <c r="BK22" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL22" t="n">
         <v>120</v>
       </c>
       <c r="BM22" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BN22" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BO22" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BP22" t="n">
         <v>7</v>
@@ -6129,7 +6129,7 @@
         <v>5.3</v>
       </c>
       <c r="BR22" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BS22" t="n">
         <v>9.199999999999999</v>
@@ -6138,7 +6138,7 @@
         <v>14.5</v>
       </c>
       <c r="BU22" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BV22" t="n">
         <v>85</v>
@@ -6153,14 +6153,268 @@
         <v>14</v>
       </c>
       <c r="BZ22" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="CA22" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-12 15:58:19</t>
+          <t>2026-05-12 18:15:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Paraguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Club 2 de Mayo</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>7</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K23" t="n">
+        <v>950</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>2026-05-12 18:15:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-14.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-12 18:15:57</t>
+          <t>2026-05-12 20:32:27</t>
         </is>
       </c>
     </row>
@@ -1135,13 +1135,13 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="O3" t="n">
         <v>1.17</v>
       </c>
       <c r="P3" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Q3" t="n">
         <v>1.16</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-12 18:15:57</t>
+          <t>2026-05-12 20:32:27</t>
         </is>
       </c>
     </row>
@@ -1389,13 +1389,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="O4" t="n">
         <v>1.16</v>
       </c>
       <c r="P4" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Q4" t="n">
         <v>1.16</v>
@@ -1404,7 +1404,7 @@
         <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-12 18:15:57</t>
+          <t>2026-05-12 20:32:27</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G5" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I5" t="n">
         <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1661,7 +1661,7 @@
         <v>3.55</v>
       </c>
       <c r="T5" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U5" t="n">
         <v>1.94</v>
@@ -1670,7 +1670,7 @@
         <v>1.2</v>
       </c>
       <c r="W5" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="X5" t="n">
         <v>16.5</v>
@@ -1682,7 +1682,7 @@
         <v>55</v>
       </c>
       <c r="AA5" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB5" t="n">
         <v>9.4</v>
@@ -1694,7 +1694,7 @@
         <v>25</v>
       </c>
       <c r="AE5" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF5" t="n">
         <v>12.5</v>
@@ -1709,10 +1709,10 @@
         <v>85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL5" t="n">
         <v>48</v>
@@ -1721,10 +1721,10 @@
         <v>150</v>
       </c>
       <c r="AN5" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO5" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP5" t="n">
         <v>10</v>
@@ -1733,22 +1733,22 @@
         <v>13</v>
       </c>
       <c r="AR5" t="n">
-        <v>34</v>
+        <v>4.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AT5" t="n">
         <v>7</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AX5" t="n">
         <v>9.199999999999999</v>
@@ -1757,10 +1757,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BB5" t="n">
         <v>17</v>
@@ -1769,80 +1769,80 @@
         <v>16.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BF5" t="n">
         <v>9</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="BJ5" t="n">
         <v>15</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="BN5" t="n">
         <v>5.9</v>
       </c>
       <c r="BO5" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="BP5" t="n">
         <v>18</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="BR5" t="n">
         <v>44</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="BT5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="BZ5" t="n">
         <v>36</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-12 18:15:57</t>
+          <t>2026-05-12 20:32:27</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="R6" t="n">
         <v>1.24</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-12 18:15:57</t>
+          <t>2026-05-12 20:32:27</t>
         </is>
       </c>
     </row>
@@ -2151,22 +2151,22 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="O7" t="n">
         <v>1.22</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="R7" t="n">
         <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -2235,52 +2235,52 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
         <v>1.01</v>
@@ -2292,55 +2292,55 @@
         <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-12 18:15:57</t>
+          <t>2026-05-12 20:32:27</t>
         </is>
       </c>
     </row>
@@ -2489,52 +2489,52 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2546,55 +2546,55 @@
         <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN8" t="n">
         <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-12 18:15:57</t>
+          <t>2026-05-12 20:32:27</t>
         </is>
       </c>
     </row>
@@ -2743,52 +2743,52 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
         <v>1.01</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-12 18:15:57</t>
+          <t>2026-05-12 20:32:27</t>
         </is>
       </c>
     </row>
@@ -2913,13 +2913,13 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="O10" t="n">
         <v>1.2</v>
       </c>
       <c r="P10" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Q10" t="n">
         <v>1.19</v>
@@ -2997,52 +2997,52 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
         <v>1.01</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-12 18:15:57</t>
+          <t>2026-05-12 20:32:27</t>
         </is>
       </c>
     </row>
@@ -3185,7 +3185,7 @@
         <v>2</v>
       </c>
       <c r="T11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="U11" t="n">
         <v>2.98</v>
@@ -3197,49 +3197,49 @@
         <v>1.83</v>
       </c>
       <c r="X11" t="n">
-        <v>44</v>
+        <v>950</v>
       </c>
       <c r="Y11" t="n">
-        <v>34</v>
+        <v>950</v>
       </c>
       <c r="Z11" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AA11" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AB11" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AC11" t="n">
         <v>14.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE11" t="n">
         <v>36</v>
       </c>
       <c r="AF11" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AG11" t="n">
         <v>15</v>
       </c>
       <c r="AH11" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AJ11" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK11" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL11" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AM11" t="n">
         <v>50</v>
@@ -3248,25 +3248,25 @@
         <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AP11" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AU11" t="n">
         <v>2.16</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>1.96</v>
       </c>
       <c r="AV11" t="n">
         <v>11</v>
@@ -3275,34 +3275,34 @@
         <v>18</v>
       </c>
       <c r="AX11" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.97</v>
+        <v>2.18</v>
       </c>
       <c r="AZ11" t="n">
-        <v>10</v>
+        <v>2.54</v>
       </c>
       <c r="BA11" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="BC11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD11" t="n">
-        <v>16.5</v>
+        <v>2.34</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.16</v>
+        <v>2.42</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.26</v>
+        <v>2.54</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.26</v>
+        <v>9.6</v>
       </c>
       <c r="BH11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-12 18:15:57</t>
+          <t>2026-05-12 20:32:27</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-12 18:15:57</t>
+          <t>2026-05-12 20:32:27</t>
         </is>
       </c>
     </row>
@@ -3660,10 +3660,10 @@
         <v>3.3</v>
       </c>
       <c r="I13" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="J13" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K13" t="n">
         <v>4.3</v>
@@ -3690,7 +3690,7 @@
         <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>2.66</v>
+        <v>2.82</v>
       </c>
       <c r="T13" t="n">
         <v>1.11</v>
@@ -3699,7 +3699,7 @@
         <v>2.28</v>
       </c>
       <c r="V13" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W13" t="n">
         <v>1.74</v>
@@ -3753,64 +3753,64 @@
         <v>90</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AQ13" t="n">
         <v>11</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="AV13" t="n">
         <v>10.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AX13" t="n">
         <v>11</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.54</v>
+        <v>1.78</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.57</v>
+        <v>10.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-12 18:15:57</t>
+          <t>2026-05-12 20:32:27</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="G14" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="H14" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="I14" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3935,55 +3935,55 @@
         <v>1.34</v>
       </c>
       <c r="P14" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R14" t="n">
         <v>1.32</v>
       </c>
       <c r="S14" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T14" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U14" t="n">
         <v>1.9</v>
       </c>
-      <c r="U14" t="n">
-        <v>1.92</v>
-      </c>
       <c r="V14" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W14" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="X14" t="n">
         <v>16</v>
       </c>
       <c r="Y14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z14" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA14" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AB14" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE14" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AF14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG14" t="n">
         <v>12</v>
@@ -3992,10 +3992,10 @@
         <v>25</v>
       </c>
       <c r="AI14" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AJ14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK14" t="n">
         <v>23</v>
@@ -4004,22 +4004,22 @@
         <v>46</v>
       </c>
       <c r="AM14" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO14" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AP14" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS14" t="n">
         <v>5</v>
@@ -4031,37 +4031,37 @@
         <v>6.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW14" t="n">
         <v>4.9</v>
       </c>
       <c r="AX14" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY14" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA14" t="n">
         <v>4.9</v>
       </c>
       <c r="BB14" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BD14" t="n">
         <v>4.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG14" t="n">
         <v>4.9</v>
@@ -4070,65 +4070,65 @@
         <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN14" t="n">
         <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-12 18:15:57</t>
+          <t>2026-05-12 20:32:27</t>
         </is>
       </c>
     </row>
@@ -4162,10 +4162,10 @@
         <v>1.73</v>
       </c>
       <c r="G15" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="H15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I15" t="n">
         <v>6</v>
@@ -4192,7 +4192,7 @@
         <v>2.12</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="R15" t="n">
         <v>1.44</v>
@@ -4282,10 +4282,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV15" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AW15" t="n">
         <v>4</v>
@@ -4297,7 +4297,7 @@
         <v>9</v>
       </c>
       <c r="AZ15" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA15" t="n">
         <v>4</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-12 18:15:57</t>
+          <t>2026-05-12 20:32:27</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
         <v>95</v>
       </c>
       <c r="AN16" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO16" t="n">
         <v>42</v>
@@ -4584,7 +4584,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BL16" t="n">
         <v>120</v>
@@ -4608,7 +4608,7 @@
         <v>32</v>
       </c>
       <c r="BS16" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT16" t="n">
         <v>7</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-12 18:15:57</t>
+          <t>2026-05-12 20:32:27</t>
         </is>
       </c>
     </row>
@@ -4700,7 +4700,7 @@
         <v>2.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="R17" t="n">
         <v>1.39</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-12 18:15:57</t>
+          <t>2026-05-12 20:32:27</t>
         </is>
       </c>
     </row>
@@ -4954,16 +4954,16 @@
         <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="R18" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S18" t="n">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="T18" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="U18" t="n">
         <v>2.32</v>
@@ -5029,7 +5029,7 @@
         <v>11.5</v>
       </c>
       <c r="AP18" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AQ18" t="n">
         <v>9.4</v>
@@ -5044,7 +5044,7 @@
         <v>14.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV18" t="n">
         <v>8.4</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-12 18:15:57</t>
+          <t>2026-05-12 20:32:27</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
         <v>1.32</v>
       </c>
       <c r="H19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I19" t="n">
         <v>12</v>
@@ -5196,7 +5196,7 @@
         <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N19" t="n">
         <v>8</v>
@@ -5208,7 +5208,7 @@
         <v>3.55</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="R19" t="n">
         <v>2.04</v>
@@ -5226,7 +5226,7 @@
         <v>1.09</v>
       </c>
       <c r="W19" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="X19" t="n">
         <v>950</v>
@@ -5283,28 +5283,28 @@
         <v>110</v>
       </c>
       <c r="AP19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AS19" t="n">
         <v>6</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>6.6</v>
       </c>
       <c r="AT19" t="n">
         <v>12</v>
       </c>
       <c r="AU19" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AW19" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AX19" t="n">
         <v>10.5</v>
@@ -5313,10 +5313,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ19" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BA19" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BB19" t="n">
         <v>10.5</v>
@@ -5328,13 +5328,13 @@
         <v>20</v>
       </c>
       <c r="BE19" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BF19" t="n">
         <v>2.98</v>
       </c>
       <c r="BG19" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BH19" t="n">
         <v>7.8</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-12 18:15:57</t>
+          <t>2026-05-12 20:32:27</t>
         </is>
       </c>
     </row>
@@ -5429,22 +5429,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G20" t="n">
         <v>2.08</v>
       </c>
       <c r="H20" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I20" t="n">
         <v>3.8</v>
       </c>
       <c r="J20" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K20" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L20" t="n">
         <v>1.35</v>
@@ -5480,7 +5480,7 @@
         <v>1.35</v>
       </c>
       <c r="W20" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="X20" t="n">
         <v>19.5</v>
@@ -5501,7 +5501,7 @@
         <v>8.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE20" t="n">
         <v>40</v>
@@ -5513,7 +5513,7 @@
         <v>10.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI20" t="n">
         <v>44</v>
@@ -5522,7 +5522,7 @@
         <v>25</v>
       </c>
       <c r="AK20" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL20" t="n">
         <v>30</v>
@@ -5579,7 +5579,7 @@
         <v>18</v>
       </c>
       <c r="BD20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE20" t="n">
         <v>65</v>
@@ -5600,7 +5600,7 @@
         <v>9.4</v>
       </c>
       <c r="BK20" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BL20" t="n">
         <v>100</v>
@@ -5636,7 +5636,7 @@
         <v>30</v>
       </c>
       <c r="BW20" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BX20" t="n">
         <v>38</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-12 18:15:57</t>
+          <t>2026-05-12 20:32:27</t>
         </is>
       </c>
     </row>
@@ -5848,7 +5848,7 @@
         <v>3.85</v>
       </c>
       <c r="BI21" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BJ21" t="n">
         <v>9.4</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-12 18:15:57</t>
+          <t>2026-05-12 20:32:27</t>
         </is>
       </c>
     </row>
@@ -5937,28 +5937,28 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="G22" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="H22" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="I22" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="J22" t="n">
+        <v>7</v>
+      </c>
+      <c r="K22" t="n">
         <v>7.2</v>
       </c>
-      <c r="K22" t="n">
-        <v>7.4</v>
-      </c>
       <c r="L22" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N22" t="n">
         <v>6.8</v>
@@ -5967,16 +5967,16 @@
         <v>1.16</v>
       </c>
       <c r="P22" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R22" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="S22" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="T22" t="n">
         <v>1.89</v>
@@ -5985,40 +5985,40 @@
         <v>2.06</v>
       </c>
       <c r="V22" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W22" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="X22" t="n">
         <v>34</v>
       </c>
       <c r="Y22" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Z22" t="n">
         <v>120</v>
       </c>
       <c r="AA22" t="n">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="AB22" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC22" t="n">
         <v>15.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AE22" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AF22" t="n">
         <v>9.4</v>
       </c>
       <c r="AG22" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH22" t="n">
         <v>28</v>
@@ -6039,16 +6039,16 @@
         <v>130</v>
       </c>
       <c r="AN22" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AO22" t="n">
         <v>160</v>
       </c>
       <c r="AP22" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AQ22" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AR22" t="n">
         <v>40</v>
@@ -6063,7 +6063,7 @@
         <v>14</v>
       </c>
       <c r="AV22" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AW22" t="n">
         <v>44</v>
@@ -6093,13 +6093,13 @@
         <v>42</v>
       </c>
       <c r="BF22" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="BG22" t="n">
         <v>44</v>
       </c>
       <c r="BH22" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BI22" t="n">
         <v>4</v>
@@ -6108,13 +6108,13 @@
         <v>11.5</v>
       </c>
       <c r="BK22" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BL22" t="n">
         <v>120</v>
       </c>
       <c r="BM22" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN22" t="n">
         <v>4</v>
@@ -6123,44 +6123,44 @@
         <v>3.25</v>
       </c>
       <c r="BP22" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BQ22" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BR22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BS22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT22" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BU22" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BV22" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BW22" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BX22" t="n">
         <v>70</v>
       </c>
       <c r="BY22" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BZ22" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CA22" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-12 18:15:57</t>
+          <t>2026-05-12 20:32:27</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-12 18:15:57</t>
+          <t>2026-05-12 20:32:27</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-14.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G2" t="n">
         <v>2.2</v>
@@ -878,157 +878,157 @@
         <v>1.5</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N2" t="n">
         <v>3.05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="P2" t="n">
         <v>1.69</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T2" t="n">
         <v>1.96</v>
       </c>
       <c r="U2" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V2" t="n">
         <v>1.32</v>
       </c>
       <c r="W2" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X2" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Y2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Z2" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AA2" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AB2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>14</v>
+        <v>7.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="AF2" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>27</v>
       </c>
-      <c r="AI2" t="n">
-        <v>400</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>42</v>
-      </c>
       <c r="AK2" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="AL2" t="n">
-        <v>180</v>
+        <v>55</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN2" t="n">
-        <v>110</v>
+        <v>600</v>
       </c>
       <c r="AO2" t="n">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AP2" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS2" t="n">
-        <v>42</v>
+        <v>11.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU2" t="n">
         <v>6.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.9</v>
+        <v>23</v>
       </c>
       <c r="BC2" t="n">
         <v>21</v>
       </c>
       <c r="BD2" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.4</v>
+        <v>12</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="BH2" t="n">
         <v>3</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1046,13 +1046,13 @@
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
@@ -1076,11 +1076,11 @@
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
         <v>3.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="M3" t="n">
         <v>1.1</v>
@@ -1141,22 +1141,22 @@
         <v>1.43</v>
       </c>
       <c r="P3" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R3" t="n">
         <v>1.26</v>
       </c>
       <c r="S3" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="U3" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="V3" t="n">
         <v>1.54</v>
@@ -1165,13 +1165,13 @@
         <v>1.46</v>
       </c>
       <c r="X3" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y3" t="n">
         <v>11</v>
       </c>
       <c r="Z3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA3" t="n">
         <v>50</v>
@@ -1180,7 +1180,7 @@
         <v>12</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD3" t="n">
         <v>15</v>
@@ -1189,19 +1189,19 @@
         <v>40</v>
       </c>
       <c r="AF3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG3" t="n">
         <v>16</v>
       </c>
       <c r="AH3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI3" t="n">
         <v>60</v>
       </c>
       <c r="AJ3" t="n">
-        <v>120</v>
+        <v>340</v>
       </c>
       <c r="AK3" t="n">
         <v>44</v>
@@ -1219,7 +1219,7 @@
         <v>36</v>
       </c>
       <c r="AP3" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AQ3" t="n">
         <v>8.6</v>
@@ -1228,10 +1228,10 @@
         <v>12.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.6</v>
+        <v>18</v>
       </c>
       <c r="AT3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU3" t="n">
         <v>6.2</v>
@@ -1240,7 +1240,7 @@
         <v>11</v>
       </c>
       <c r="AW3" t="n">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="AX3" t="n">
         <v>14.5</v>
@@ -1249,10 +1249,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BB3" t="n">
         <v>36</v>
@@ -1267,28 +1267,28 @@
         <v>26</v>
       </c>
       <c r="BF3" t="n">
-        <v>26</v>
+        <v>6.6</v>
       </c>
       <c r="BG3" t="n">
         <v>5.7</v>
       </c>
       <c r="BH3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK3" t="n">
         <v>3.5</v>
       </c>
-      <c r="BI3" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>3.55</v>
-      </c>
       <c r="BL3" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="BM3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BN3" t="n">
         <v>7</v>
@@ -1297,13 +1297,13 @@
         <v>4.5</v>
       </c>
       <c r="BP3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BR3" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BS3" t="n">
         <v>4.5</v>
@@ -1315,26 +1315,26 @@
         <v>4.2</v>
       </c>
       <c r="BV3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BW3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BX3" t="n">
         <v>48</v>
       </c>
       <c r="BY3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BZ3" t="n">
         <v>46</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -1365,55 +1365,55 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="G4" t="n">
         <v>2.1</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I4" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="J4" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K4" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M4" t="n">
         <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>2.92</v>
+        <v>3.45</v>
       </c>
       <c r="O4" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P4" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="R4" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="S4" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="T4" t="n">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
       <c r="U4" t="n">
-        <v>1.11</v>
+        <v>2.34</v>
       </c>
       <c r="V4" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
         <v>1.9</v>
@@ -1428,37 +1428,37 @@
         <v>500</v>
       </c>
       <c r="AA4" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AC4" t="n">
-        <v>500</v>
+        <v>11</v>
       </c>
       <c r="AD4" t="n">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AE4" t="n">
         <v>500</v>
       </c>
       <c r="AF4" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AG4" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AH4" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AI4" t="n">
         <v>500</v>
       </c>
       <c r="AJ4" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK4" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AL4" t="n">
         <v>500</v>
@@ -1467,128 +1467,128 @@
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AO4" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.55</v>
+        <v>4.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.55</v>
+        <v>6.8</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.04</v>
+        <v>2.88</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -1619,16 +1619,16 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H5" t="n">
         <v>2.58</v>
       </c>
-      <c r="G5" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2.54</v>
-      </c>
       <c r="I5" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="J5" t="n">
         <v>3.55</v>
@@ -1637,28 +1637,28 @@
         <v>4.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="M5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="O5" t="n">
         <v>1.19</v>
       </c>
       <c r="P5" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="R5" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="S5" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="T5" t="n">
         <v>1.53</v>
@@ -1667,13 +1667,13 @@
         <v>2.52</v>
       </c>
       <c r="V5" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="W5" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X5" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="Y5" t="n">
         <v>970</v>
@@ -1685,19 +1685,19 @@
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>30</v>
+        <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>42</v>
+        <v>17.5</v>
       </c>
       <c r="AD5" t="n">
         <v>970</v>
       </c>
       <c r="AE5" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AF5" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AG5" t="n">
         <v>970</v>
@@ -1706,13 +1706,13 @@
         <v>60</v>
       </c>
       <c r="AI5" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AJ5" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AK5" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AL5" t="n">
         <v>75</v>
@@ -1727,16 +1727,16 @@
         <v>55</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AQ5" t="n">
         <v>7.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT5" t="n">
         <v>12</v>
@@ -1748,7 +1748,7 @@
         <v>10</v>
       </c>
       <c r="AW5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AX5" t="n">
         <v>9</v>
@@ -1760,7 +1760,7 @@
         <v>9</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.4</v>
+        <v>12.5</v>
       </c>
       <c r="BB5" t="n">
         <v>16</v>
@@ -1772,77 +1772,77 @@
         <v>16</v>
       </c>
       <c r="BE5" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BF5" t="n">
         <v>10.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH5" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="BJ5" t="n">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="BK5" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="BL5" t="n">
         <v>85</v>
       </c>
       <c r="BM5" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="BN5" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="BP5" t="n">
         <v>970</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR5" t="n">
         <v>28</v>
       </c>
       <c r="BS5" t="n">
-        <v>4.9</v>
+        <v>2.36</v>
       </c>
       <c r="BT5" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.9</v>
+        <v>3.85</v>
       </c>
       <c r="BV5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="BX5" t="n">
         <v>29</v>
       </c>
       <c r="BY5" t="n">
-        <v>5</v>
+        <v>2.36</v>
       </c>
       <c r="BZ5" t="n">
         <v>970</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
         <v>4.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
@@ -1993,7 +1993,7 @@
         <v>8</v>
       </c>
       <c r="AT6" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AU6" t="n">
         <v>5.1</v>
@@ -2005,7 +2005,7 @@
         <v>7.2</v>
       </c>
       <c r="AX6" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY6" t="n">
         <v>7</v>
@@ -2017,13 +2017,13 @@
         <v>7.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BC6" t="n">
         <v>7.2</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE6" t="n">
         <v>8.800000000000001</v>
@@ -2050,7 +2050,7 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>2.88</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN6" t="n">
         <v>6.2</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>4.9</v>
       </c>
       <c r="H7" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="I7" t="n">
         <v>1.95</v>
@@ -2157,16 +2157,16 @@
         <v>1.18</v>
       </c>
       <c r="P7" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R7" t="n">
         <v>1.58</v>
       </c>
       <c r="S7" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="T7" t="n">
         <v>1.58</v>
@@ -2178,7 +2178,7 @@
         <v>2.04</v>
       </c>
       <c r="W7" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X7" t="n">
         <v>27</v>
@@ -2241,10 +2241,10 @@
         <v>5.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS7" t="n">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT7" t="n">
         <v>6.2</v>
@@ -2256,7 +2256,7 @@
         <v>6.2</v>
       </c>
       <c r="AW7" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AX7" t="n">
         <v>6.8</v>
@@ -2268,7 +2268,7 @@
         <v>6.2</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BB7" t="n">
         <v>7.6</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="G8" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I8" t="n">
         <v>5.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K8" t="n">
         <v>5.2</v>
@@ -2411,10 +2411,10 @@
         <v>1.18</v>
       </c>
       <c r="P8" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="R8" t="n">
         <v>1.69</v>
@@ -2429,10 +2429,10 @@
         <v>2.56</v>
       </c>
       <c r="V8" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W8" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="X8" t="n">
         <v>90</v>
@@ -2444,7 +2444,7 @@
         <v>90</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB8" t="n">
         <v>970</v>
@@ -2453,22 +2453,22 @@
         <v>42</v>
       </c>
       <c r="AD8" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE8" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AF8" t="n">
         <v>970</v>
       </c>
       <c r="AG8" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="AH8" t="n">
         <v>60</v>
       </c>
       <c r="AI8" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AJ8" t="n">
         <v>970</v>
@@ -2486,19 +2486,19 @@
         <v>85</v>
       </c>
       <c r="AO8" t="n">
-        <v>50</v>
+        <v>600</v>
       </c>
       <c r="AP8" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.88</v>
+        <v>4.8</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.68</v>
+        <v>4.7</v>
       </c>
       <c r="AT8" t="n">
         <v>7</v>
@@ -2507,10 +2507,10 @@
         <v>8</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="AX8" t="n">
         <v>7</v>
@@ -2522,16 +2522,16 @@
         <v>9</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.6</v>
+        <v>2.86</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC8" t="n">
         <v>9</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.9</v>
+        <v>11</v>
       </c>
       <c r="BE8" t="n">
         <v>2.64</v>
@@ -2543,22 +2543,22 @@
         <v>6.2</v>
       </c>
       <c r="BH8" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="BN8" t="n">
         <v>1000</v>
@@ -2570,31 +2570,31 @@
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -2644,13 +2644,13 @@
         <v>4.6</v>
       </c>
       <c r="I9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J9" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K9" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L9" t="n">
         <v>1.43</v>
@@ -2677,7 +2677,7 @@
         <v>3.7</v>
       </c>
       <c r="T9" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U9" t="n">
         <v>1.98</v>
@@ -2689,10 +2689,10 @@
         <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Z9" t="n">
         <v>46</v>
@@ -2701,13 +2701,13 @@
         <v>150</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE9" t="n">
         <v>85</v>
@@ -2716,19 +2716,19 @@
         <v>14</v>
       </c>
       <c r="AG9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI9" t="n">
         <v>90</v>
       </c>
       <c r="AJ9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL9" t="n">
         <v>48</v>
@@ -2737,7 +2737,7 @@
         <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AO9" t="n">
         <v>110</v>
@@ -2749,10 +2749,10 @@
         <v>13.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="AT9" t="n">
         <v>7.4</v>
@@ -2764,7 +2764,7 @@
         <v>16.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.1</v>
+        <v>29</v>
       </c>
       <c r="AX9" t="n">
         <v>8.6</v>
@@ -2773,92 +2773,92 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BC9" t="n">
         <v>18.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF9" t="n">
         <v>10.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="BJ9" t="n">
         <v>10.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="BP9" t="n">
         <v>13.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BR9" t="n">
         <v>29</v>
       </c>
       <c r="BS9" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BT9" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BZ9" t="n">
         <v>26</v>
       </c>
       <c r="CA9" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -2910,25 +2910,25 @@
         <v>1.25</v>
       </c>
       <c r="M10" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O10" t="n">
         <v>1.18</v>
       </c>
       <c r="P10" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="Q10" t="n">
         <v>1.57</v>
       </c>
       <c r="R10" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S10" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T10" t="n">
         <v>1.57</v>
@@ -2943,19 +2943,19 @@
         <v>2.02</v>
       </c>
       <c r="X10" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Y10" t="n">
         <v>22</v>
       </c>
       <c r="Z10" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA10" t="n">
         <v>80</v>
       </c>
       <c r="AB10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AC10" t="n">
         <v>11</v>
@@ -2964,13 +2964,13 @@
         <v>18</v>
       </c>
       <c r="AE10" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AF10" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AG10" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH10" t="n">
         <v>17</v>
@@ -2979,13 +2979,13 @@
         <v>44</v>
       </c>
       <c r="AJ10" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AK10" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AM10" t="n">
         <v>70</v>
@@ -2997,58 +2997,58 @@
         <v>34</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT10" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AV10" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AW10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC10" t="n">
         <v>6</v>
       </c>
-      <c r="AX10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>5</v>
-      </c>
       <c r="BD10" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH10" t="n">
         <v>5</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>1.44</v>
       </c>
       <c r="G11" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="H11" t="n">
         <v>6</v>
@@ -3158,19 +3158,19 @@
         <v>4.9</v>
       </c>
       <c r="K11" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="M11" t="n">
         <v>1.02</v>
       </c>
       <c r="N11" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="O11" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="P11" t="n">
         <v>2.92</v>
@@ -3305,7 +3305,7 @@
         <v>8.6</v>
       </c>
       <c r="BH11" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BI11" t="n">
         <v>2.88</v>
@@ -3314,59 +3314,59 @@
         <v>11</v>
       </c>
       <c r="BK11" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BL11" t="n">
         <v>85</v>
       </c>
       <c r="BM11" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BN11" t="n">
         <v>5.3</v>
       </c>
       <c r="BO11" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="BP11" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BQ11" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="BR11" t="n">
         <v>20</v>
       </c>
       <c r="BS11" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BT11" t="n">
         <v>12.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BV11" t="n">
         <v>55</v>
       </c>
       <c r="BW11" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BX11" t="n">
         <v>46</v>
       </c>
       <c r="BY11" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BZ11" t="n">
         <v>11</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -3397,19 +3397,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G12" t="n">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="H12" t="n">
         <v>1.92</v>
       </c>
       <c r="I12" t="n">
-        <v>9.199999999999999</v>
+        <v>3.35</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K12" t="n">
         <v>7</v>
@@ -3430,13 +3430,13 @@
         <v>1.42</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="R12" t="n">
         <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -3445,10 +3445,10 @@
         <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X12" t="n">
         <v>950</v>
@@ -3457,10 +3457,10 @@
         <v>950</v>
       </c>
       <c r="Z12" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AA12" t="n">
-        <v>160</v>
+        <v>900</v>
       </c>
       <c r="AB12" t="n">
         <v>950</v>
@@ -3472,85 +3472,85 @@
         <v>950</v>
       </c>
       <c r="AE12" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG12" t="n">
         <v>950</v>
       </c>
       <c r="AH12" t="n">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AI12" t="n">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AJ12" t="n">
-        <v>230</v>
+        <v>900</v>
       </c>
       <c r="AK12" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AL12" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AU12" t="n">
         <v>5.1</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AX12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AY12" t="n">
         <v>1.32</v>
       </c>
-      <c r="AY12" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AZ12" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="BF12" t="n">
         <v>1.55</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G13" t="n">
         <v>5.8</v>
@@ -3684,7 +3684,7 @@
         <v>2.36</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="R13" t="n">
         <v>1.54</v>
@@ -3705,112 +3705,112 @@
         <v>1.2</v>
       </c>
       <c r="X13" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="Y13" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="Z13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA13" t="n">
         <v>26</v>
       </c>
       <c r="AB13" t="n">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="AC13" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="AD13" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AE13" t="n">
         <v>17</v>
       </c>
       <c r="AF13" t="n">
-        <v>55</v>
+        <v>350</v>
       </c>
       <c r="AG13" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AH13" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="AI13" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AJ13" t="n">
         <v>140</v>
       </c>
       <c r="AK13" t="n">
-        <v>70</v>
+        <v>400</v>
       </c>
       <c r="AL13" t="n">
-        <v>65</v>
+        <v>320</v>
       </c>
       <c r="AM13" t="n">
-        <v>100</v>
+        <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>70</v>
+        <v>440</v>
       </c>
       <c r="AO13" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AP13" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AX13" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AY13" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="BH13" t="n">
         <v>4.8</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -3959,13 +3959,13 @@
         <v>1.46</v>
       </c>
       <c r="X14" t="n">
-        <v>950</v>
+        <v>90</v>
       </c>
       <c r="Y14" t="n">
         <v>970</v>
       </c>
       <c r="Z14" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AA14" t="n">
         <v>900</v>
@@ -3980,10 +3980,10 @@
         <v>970</v>
       </c>
       <c r="AE14" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AF14" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AG14" t="n">
         <v>970</v>
@@ -3992,22 +3992,22 @@
         <v>970</v>
       </c>
       <c r="AI14" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AJ14" t="n">
         <v>900</v>
       </c>
       <c r="AK14" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AL14" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AM14" t="n">
-        <v>75</v>
+        <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="AO14" t="n">
         <v>970</v>
@@ -4025,16 +4025,16 @@
         <v>2.32</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AU14" t="n">
         <v>3.15</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="AX14" t="n">
         <v>2.18</v>
@@ -4043,7 +4043,7 @@
         <v>2.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="BA14" t="n">
         <v>2.32</v>
@@ -4052,19 +4052,19 @@
         <v>2.34</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BE14" t="n">
         <v>2.32</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BH14" t="n">
         <v>10</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -4225,7 +4225,7 @@
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC15" t="n">
         <v>1000</v>
@@ -4237,10 +4237,10 @@
         <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH15" t="n">
         <v>1000</v>
@@ -4249,13 +4249,13 @@
         <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM15" t="n">
         <v>1000</v>
@@ -4267,7 +4267,7 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AQ15" t="n">
         <v>4.2</v>
@@ -4279,10 +4279,10 @@
         <v>4.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AV15" t="n">
         <v>4.2</v>
@@ -4291,31 +4291,31 @@
         <v>4.2</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="BA15" t="n">
         <v>4.2</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="BG15" t="n">
         <v>4.2</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
         <v>1.35</v>
       </c>
       <c r="R16" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="S16" t="n">
         <v>1.89</v>
@@ -4467,19 +4467,19 @@
         <v>1.67</v>
       </c>
       <c r="X16" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="Y16" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="Z16" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AA16" t="n">
-        <v>55</v>
+        <v>900</v>
       </c>
       <c r="AB16" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AC16" t="n">
         <v>42</v>
@@ -4488,10 +4488,10 @@
         <v>970</v>
       </c>
       <c r="AE16" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AF16" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AG16" t="n">
         <v>970</v>
@@ -4500,79 +4500,79 @@
         <v>970</v>
       </c>
       <c r="AI16" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AJ16" t="n">
-        <v>38</v>
+        <v>900</v>
       </c>
       <c r="AK16" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AL16" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AM16" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AN16" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AO16" t="n">
         <v>970</v>
       </c>
       <c r="AP16" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AR16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV16" t="n">
         <v>4.5</v>
       </c>
-      <c r="AS16" t="n">
+      <c r="AW16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC16" t="n">
         <v>4.8</v>
       </c>
-      <c r="AT16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY16" t="n">
+      <c r="BD16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BF16" t="n">
         <v>3.9</v>
       </c>
-      <c r="AZ16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BG16" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BH16" t="n">
         <v>6</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -4667,13 +4667,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="G17" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="H17" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="I17" t="n">
         <v>3.35</v>
@@ -4682,7 +4682,7 @@
         <v>3.2</v>
       </c>
       <c r="K17" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
         <v>1.32</v>
@@ -4697,28 +4697,28 @@
         <v>1.3</v>
       </c>
       <c r="P17" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="Q17" t="n">
         <v>1.93</v>
       </c>
       <c r="R17" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>1.05</v>
+        <v>3.05</v>
       </c>
       <c r="T17" t="n">
-        <v>1.11</v>
+        <v>1.74</v>
       </c>
       <c r="U17" t="n">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="V17" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W17" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="X17" t="n">
         <v>970</v>
@@ -4730,7 +4730,7 @@
         <v>42</v>
       </c>
       <c r="AA17" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB17" t="n">
         <v>970</v>
@@ -4745,7 +4745,7 @@
         <v>85</v>
       </c>
       <c r="AF17" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AG17" t="n">
         <v>24</v>
@@ -4754,7 +4754,7 @@
         <v>60</v>
       </c>
       <c r="AI17" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AJ17" t="n">
         <v>900</v>
@@ -4763,25 +4763,25 @@
         <v>75</v>
       </c>
       <c r="AL17" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AO17" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AP17" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AQ17" t="n">
         <v>6.4</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AS17" t="n">
         <v>4.7</v>
@@ -4799,7 +4799,7 @@
         <v>4.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AY17" t="n">
         <v>7</v>
@@ -4820,7 +4820,7 @@
         <v>4.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BF17" t="n">
         <v>4.9</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -4921,22 +4921,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="G18" t="n">
         <v>2.16</v>
       </c>
       <c r="H18" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I18" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="J18" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="K18" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
         <v>1.4</v>
@@ -4969,7 +4969,7 @@
         <v>2.04</v>
       </c>
       <c r="V18" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W18" t="n">
         <v>1.86</v>
@@ -4984,10 +4984,10 @@
         <v>500</v>
       </c>
       <c r="AA18" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB18" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="AC18" t="n">
         <v>42</v>
@@ -5002,43 +5002,43 @@
         <v>970</v>
       </c>
       <c r="AG18" t="n">
+        <v>500</v>
+      </c>
+      <c r="AH18" t="n">
         <v>970</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>950</v>
       </c>
       <c r="AI18" t="n">
         <v>500</v>
       </c>
       <c r="AJ18" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK18" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AL18" t="n">
         <v>500</v>
       </c>
       <c r="AM18" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AO18" t="n">
         <v>500</v>
       </c>
       <c r="AP18" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AR18" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="AT18" t="n">
         <v>5.6</v>
@@ -5047,10 +5047,10 @@
         <v>4.9</v>
       </c>
       <c r="AV18" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="AX18" t="n">
         <v>6.4</v>
@@ -5059,28 +5059,28 @@
         <v>6.2</v>
       </c>
       <c r="AZ18" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="BB18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC18" t="n">
         <v>7</v>
       </c>
-      <c r="BC18" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BD18" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="BF18" t="n">
         <v>3.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BH18" t="n">
         <v>5.6</v>
@@ -5098,7 +5098,7 @@
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>7</v>
+        <v>1.06</v>
       </c>
       <c r="BN18" t="n">
         <v>1000</v>
@@ -5116,7 +5116,7 @@
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>5.4</v>
+        <v>1.73</v>
       </c>
       <c r="BT18" t="n">
         <v>1000</v>
@@ -5128,13 +5128,13 @@
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>6.2</v>
+        <v>2.24</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>6.2</v>
+        <v>1.76</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -5175,10 +5175,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G19" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H19" t="n">
         <v>3.25</v>
@@ -5223,10 +5223,10 @@
         <v>2.34</v>
       </c>
       <c r="V19" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W19" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="X19" t="n">
         <v>22</v>
@@ -5244,19 +5244,19 @@
         <v>13.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD19" t="n">
         <v>16.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AF19" t="n">
         <v>18</v>
       </c>
       <c r="AG19" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH19" t="n">
         <v>18.5</v>
@@ -5271,7 +5271,7 @@
         <v>23</v>
       </c>
       <c r="AL19" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM19" t="n">
         <v>85</v>
@@ -5283,7 +5283,7 @@
         <v>34</v>
       </c>
       <c r="AP19" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ19" t="n">
         <v>11.5</v>
@@ -5292,40 +5292,40 @@
         <v>18.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.7</v>
+        <v>23</v>
       </c>
       <c r="AT19" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AU19" t="n">
         <v>7.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AX19" t="n">
         <v>12</v>
       </c>
       <c r="AY19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ19" t="n">
         <v>12</v>
       </c>
       <c r="BA19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB19" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC19" t="n">
         <v>19.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BE19" t="n">
         <v>19</v>
@@ -5334,7 +5334,7 @@
         <v>11.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BH19" t="n">
         <v>3.8</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -5537,10 +5537,10 @@
         <v>11</v>
       </c>
       <c r="AP20" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="AR20" t="n">
         <v>17.5</v>
@@ -5555,13 +5555,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV20" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AW20" t="n">
         <v>19.5</v>
       </c>
       <c r="AX20" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AY20" t="n">
         <v>12</v>
@@ -5570,16 +5570,16 @@
         <v>11.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BB20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC20" t="n">
         <v>20</v>
       </c>
       <c r="BD20" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BE20" t="n">
         <v>36</v>
@@ -5588,7 +5588,7 @@
         <v>10</v>
       </c>
       <c r="BG20" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH20" t="n">
         <v>5.1</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5698,7 @@
         <v>4.2</v>
       </c>
       <c r="K21" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L21" t="n">
         <v>1.18</v>
@@ -5746,19 +5746,19 @@
         <v>32</v>
       </c>
       <c r="AA21" t="n">
-        <v>440</v>
+        <v>120</v>
       </c>
       <c r="AB21" t="n">
         <v>21</v>
       </c>
       <c r="AC21" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AD21" t="n">
         <v>18</v>
       </c>
       <c r="AE21" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF21" t="n">
         <v>21</v>
@@ -5800,7 +5800,7 @@
         <v>14.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT21" t="n">
         <v>17</v>
@@ -5821,7 +5821,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA21" t="n">
         <v>21</v>
@@ -5836,7 +5836,7 @@
         <v>16</v>
       </c>
       <c r="BE21" t="n">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="BF21" t="n">
         <v>6.4</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -5943,10 +5943,10 @@
         <v>1.82</v>
       </c>
       <c r="H22" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I22" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J22" t="n">
         <v>3.65</v>
@@ -5985,7 +5985,7 @@
         <v>1.9</v>
       </c>
       <c r="V22" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W22" t="n">
         <v>2.22</v>
@@ -6000,7 +6000,7 @@
         <v>55</v>
       </c>
       <c r="AA22" t="n">
-        <v>180</v>
+        <v>700</v>
       </c>
       <c r="AB22" t="n">
         <v>9</v>
@@ -6042,7 +6042,7 @@
         <v>15</v>
       </c>
       <c r="AO22" t="n">
-        <v>440</v>
+        <v>700</v>
       </c>
       <c r="AP22" t="n">
         <v>11.5</v>
@@ -6054,7 +6054,7 @@
         <v>5.3</v>
       </c>
       <c r="AS22" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT22" t="n">
         <v>6.8</v>
@@ -6066,7 +6066,7 @@
         <v>19.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX22" t="n">
         <v>9</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
         <v>1.81</v>
       </c>
       <c r="G23" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
         <v>3.9</v>
@@ -6239,22 +6239,22 @@
         <v>2.08</v>
       </c>
       <c r="V23" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W23" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="X23" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="Y23" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="Z23" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB23" t="n">
         <v>970</v>
@@ -6263,10 +6263,10 @@
         <v>42</v>
       </c>
       <c r="AD23" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AE23" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AF23" t="n">
         <v>970</v>
@@ -6278,16 +6278,16 @@
         <v>60</v>
       </c>
       <c r="AI23" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AJ23" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AK23" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AL23" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AM23" t="n">
         <v>580</v>
@@ -6296,10 +6296,10 @@
         <v>55</v>
       </c>
       <c r="AO23" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AP23" t="n">
-        <v>3.6</v>
+        <v>11</v>
       </c>
       <c r="AQ23" t="n">
         <v>3.55</v>
@@ -6314,7 +6314,7 @@
         <v>3.35</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.2</v>
+        <v>5.4</v>
       </c>
       <c r="AV23" t="n">
         <v>3.5</v>
@@ -6329,7 +6329,7 @@
         <v>3.25</v>
       </c>
       <c r="AZ23" t="n">
-        <v>3.5</v>
+        <v>9.4</v>
       </c>
       <c r="BA23" t="n">
         <v>3.9</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6448,7 @@
         <v>1.43</v>
       </c>
       <c r="G24" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="H24" t="n">
         <v>4.4</v>
@@ -6511,10 +6511,10 @@
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD24" t="n">
         <v>1000</v>
@@ -6523,10 +6523,10 @@
         <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH24" t="n">
         <v>1000</v>
@@ -6535,76 +6535,76 @@
         <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM24" t="n">
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO24" t="n">
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -6705,13 +6705,13 @@
         <v>1.84</v>
       </c>
       <c r="H25" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I25" t="n">
         <v>5.4</v>
       </c>
       <c r="J25" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K25" t="n">
         <v>4.1</v>
@@ -6729,10 +6729,10 @@
         <v>1.3</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R25" t="n">
         <v>1.39</v>
@@ -6741,10 +6741,10 @@
         <v>3.25</v>
       </c>
       <c r="T25" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U25" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V25" t="n">
         <v>1.22</v>
@@ -6768,13 +6768,13 @@
         <v>10.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD25" t="n">
         <v>25</v>
       </c>
       <c r="AE25" t="n">
-        <v>85</v>
+        <v>320</v>
       </c>
       <c r="AF25" t="n">
         <v>13</v>
@@ -6786,13 +6786,13 @@
         <v>24</v>
       </c>
       <c r="AI25" t="n">
-        <v>85</v>
+        <v>320</v>
       </c>
       <c r="AJ25" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AK25" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AL25" t="n">
         <v>44</v>
@@ -6804,7 +6804,7 @@
         <v>13.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>310</v>
+        <v>700</v>
       </c>
       <c r="AP25" t="n">
         <v>13.5</v>
@@ -6816,7 +6816,7 @@
         <v>16</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="AT25" t="n">
         <v>7.6</v>
@@ -6828,7 +6828,7 @@
         <v>15</v>
       </c>
       <c r="AW25" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AX25" t="n">
         <v>9.800000000000001</v>
@@ -6840,7 +6840,7 @@
         <v>14.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BB25" t="n">
         <v>16.5</v>
@@ -6852,13 +6852,13 @@
         <v>16</v>
       </c>
       <c r="BE25" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BG25" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BH25" t="n">
         <v>3.6</v>
@@ -6879,10 +6879,10 @@
         <v>14</v>
       </c>
       <c r="BN25" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO25" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BP25" t="n">
         <v>12</v>
@@ -6894,13 +6894,13 @@
         <v>26</v>
       </c>
       <c r="BS25" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT25" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU25" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -6962,7 +6962,7 @@
         <v>3.2</v>
       </c>
       <c r="I26" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J26" t="n">
         <v>3.4</v>
@@ -6995,10 +6995,10 @@
         <v>3.1</v>
       </c>
       <c r="T26" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="U26" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="V26" t="n">
         <v>1.36</v>
@@ -7010,34 +7010,34 @@
         <v>18.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Z26" t="n">
         <v>29</v>
       </c>
       <c r="AA26" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AB26" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC26" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD26" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AE26" t="n">
         <v>46</v>
       </c>
       <c r="AF26" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG26" t="n">
         <v>13</v>
       </c>
       <c r="AH26" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI26" t="n">
         <v>55</v>
@@ -7070,7 +7070,7 @@
         <v>21</v>
       </c>
       <c r="AS26" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AT26" t="n">
         <v>8.199999999999999</v>
@@ -7082,7 +7082,7 @@
         <v>12.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="AX26" t="n">
         <v>11.5</v>
@@ -7094,16 +7094,16 @@
         <v>12.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BB26" t="n">
-        <v>5.2</v>
+        <v>13</v>
       </c>
       <c r="BC26" t="n">
         <v>19.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>5.2</v>
+        <v>18</v>
       </c>
       <c r="BE26" t="n">
         <v>22</v>
@@ -7112,7 +7112,7 @@
         <v>14.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BH26" t="n">
         <v>4</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -7219,7 +7219,7 @@
         <v>1.85</v>
       </c>
       <c r="J27" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K27" t="n">
         <v>5</v>
@@ -7261,112 +7261,112 @@
         <v>1.21</v>
       </c>
       <c r="X27" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="Y27" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB27" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC27" t="n">
         <v>42</v>
       </c>
       <c r="AD27" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE27" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AF27" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG27" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH27" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK27" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL27" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM27" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO27" t="n">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AU27" t="n">
         <v>5.6</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BF27" t="n">
         <v>1.55</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BH27" t="n">
         <v>4.7</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7476,7 @@
         <v>5.1</v>
       </c>
       <c r="K28" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L28" t="n">
         <v>1.25</v>
@@ -7500,7 +7500,7 @@
         <v>1.54</v>
       </c>
       <c r="S28" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="T28" t="n">
         <v>1.88</v>
@@ -7548,7 +7548,7 @@
         <v>30</v>
       </c>
       <c r="AI28" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AJ28" t="n">
         <v>15</v>
@@ -7620,7 +7620,7 @@
         <v>5</v>
       </c>
       <c r="BG28" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BH28" t="n">
         <v>5</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -7969,7 +7969,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G30" t="n">
         <v>2.26</v>
@@ -7978,10 +7978,10 @@
         <v>3.7</v>
       </c>
       <c r="I30" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J30" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K30" t="n">
         <v>3.75</v>
@@ -8002,7 +8002,7 @@
         <v>1.78</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="R30" t="n">
         <v>1.29</v>
@@ -8011,7 +8011,7 @@
         <v>3.85</v>
       </c>
       <c r="T30" t="n">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="U30" t="n">
         <v>1.99</v>
@@ -8020,13 +8020,13 @@
         <v>1.31</v>
       </c>
       <c r="W30" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X30" t="n">
         <v>15</v>
       </c>
       <c r="Y30" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z30" t="n">
         <v>34</v>
@@ -8050,13 +8050,13 @@
         <v>16</v>
       </c>
       <c r="AG30" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH30" t="n">
         <v>24</v>
       </c>
       <c r="AI30" t="n">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AJ30" t="n">
         <v>34</v>
@@ -8086,7 +8086,7 @@
         <v>20</v>
       </c>
       <c r="AS30" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AT30" t="n">
         <v>6.4</v>
@@ -8098,7 +8098,7 @@
         <v>11.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>5.4</v>
+        <v>36</v>
       </c>
       <c r="AX30" t="n">
         <v>9.6</v>
@@ -8110,7 +8110,7 @@
         <v>14</v>
       </c>
       <c r="BA30" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BB30" t="n">
         <v>20</v>
@@ -8122,7 +8122,7 @@
         <v>20</v>
       </c>
       <c r="BE30" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BF30" t="n">
         <v>14</v>
@@ -8131,22 +8131,22 @@
         <v>10.5</v>
       </c>
       <c r="BH30" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BI30" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BJ30" t="n">
         <v>12</v>
       </c>
       <c r="BK30" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BL30" t="n">
         <v>170</v>
       </c>
       <c r="BM30" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BN30" t="n">
         <v>5.7</v>
@@ -8158,13 +8158,13 @@
         <v>19.5</v>
       </c>
       <c r="BQ30" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BR30" t="n">
         <v>40</v>
       </c>
       <c r="BS30" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BT30" t="n">
         <v>8.4</v>
@@ -8182,7 +8182,7 @@
         <v>60</v>
       </c>
       <c r="BY30" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BZ30" t="n">
         <v>0</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -8241,13 +8241,13 @@
         <v>4.5</v>
       </c>
       <c r="L31" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="M31" t="n">
         <v>1.06</v>
       </c>
       <c r="N31" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O31" t="n">
         <v>1.31</v>
@@ -8259,7 +8259,7 @@
         <v>1.89</v>
       </c>
       <c r="R31" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="S31" t="n">
         <v>3.3</v>
@@ -8280,13 +8280,13 @@
         <v>19</v>
       </c>
       <c r="Y31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z31" t="n">
         <v>50</v>
       </c>
       <c r="AA31" t="n">
-        <v>190</v>
+        <v>700</v>
       </c>
       <c r="AB31" t="n">
         <v>8.4</v>
@@ -8295,7 +8295,7 @@
         <v>11</v>
       </c>
       <c r="AD31" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AE31" t="n">
         <v>90</v>
@@ -8313,7 +8313,7 @@
         <v>100</v>
       </c>
       <c r="AJ31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK31" t="n">
         <v>19</v>
@@ -8325,7 +8325,7 @@
         <v>580</v>
       </c>
       <c r="AN31" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO31" t="n">
         <v>130</v>
@@ -8337,7 +8337,7 @@
         <v>14</v>
       </c>
       <c r="AR31" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AS31" t="n">
         <v>6.6</v>
@@ -8352,7 +8352,7 @@
         <v>16.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX31" t="n">
         <v>7.4</v>
@@ -8373,16 +8373,16 @@
         <v>13</v>
       </c>
       <c r="BD31" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE31" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF31" t="n">
         <v>7.8</v>
       </c>
       <c r="BG31" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH31" t="n">
         <v>4.1</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -8477,13 +8477,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="G32" t="n">
         <v>1.53</v>
       </c>
       <c r="H32" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="I32" t="n">
         <v>6.6</v>
@@ -8510,13 +8510,13 @@
         <v>3.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="R32" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="S32" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="T32" t="n">
         <v>1.48</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -8758,19 +8758,19 @@
         <v>4.5</v>
       </c>
       <c r="O33" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P33" t="n">
         <v>2.52</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="R33" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S33" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="T33" t="n">
         <v>1.57</v>
@@ -8797,7 +8797,7 @@
         <v>900</v>
       </c>
       <c r="AB33" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AC33" t="n">
         <v>12</v>
@@ -8818,13 +8818,13 @@
         <v>26</v>
       </c>
       <c r="AI33" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AJ33" t="n">
         <v>900</v>
       </c>
       <c r="AK33" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AL33" t="n">
         <v>130</v>
@@ -8833,7 +8833,7 @@
         <v>580</v>
       </c>
       <c r="AN33" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AO33" t="n">
         <v>55</v>
@@ -8848,7 +8848,7 @@
         <v>9</v>
       </c>
       <c r="AS33" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AT33" t="n">
         <v>9</v>
@@ -8872,22 +8872,22 @@
         <v>11</v>
       </c>
       <c r="BA33" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BB33" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BC33" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BD33" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BE33" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="BF33" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BG33" t="n">
         <v>8.6</v>
@@ -8896,7 +8896,7 @@
         <v>5</v>
       </c>
       <c r="BI33" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BJ33" t="n">
         <v>970</v>
@@ -8932,7 +8932,7 @@
         <v>6.4</v>
       </c>
       <c r="BU33" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BV33" t="n">
         <v>970</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -9039,16 +9039,16 @@
         <v>1.75</v>
       </c>
       <c r="X34" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="Y34" t="n">
         <v>970</v>
       </c>
       <c r="Z34" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AA34" t="n">
-        <v>70</v>
+        <v>900</v>
       </c>
       <c r="AB34" t="n">
         <v>970</v>
@@ -9060,7 +9060,7 @@
         <v>970</v>
       </c>
       <c r="AE34" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AF34" t="n">
         <v>970</v>
@@ -9072,40 +9072,40 @@
         <v>970</v>
       </c>
       <c r="AI34" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AJ34" t="n">
         <v>900</v>
       </c>
       <c r="AK34" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AL34" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AM34" t="n">
-        <v>75</v>
+        <v>580</v>
       </c>
       <c r="AN34" t="n">
         <v>55</v>
       </c>
       <c r="AO34" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AP34" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AQ34" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AR34" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AS34" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AT34" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AU34" t="n">
         <v>7.2</v>
@@ -9114,37 +9114,37 @@
         <v>9</v>
       </c>
       <c r="AW34" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AX34" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AY34" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ34" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BA34" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BB34" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BC34" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BD34" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BE34" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BF34" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BG34" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BH34" t="n">
         <v>4.6</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -9269,7 +9269,7 @@
         <v>1.38</v>
       </c>
       <c r="P35" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q35" t="n">
         <v>2.2</v>
@@ -9278,10 +9278,10 @@
         <v>1.32</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T35" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U35" t="n">
         <v>2.08</v>
@@ -9305,7 +9305,7 @@
         <v>75</v>
       </c>
       <c r="AB35" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC35" t="n">
         <v>7.2</v>
@@ -9341,7 +9341,7 @@
         <v>110</v>
       </c>
       <c r="AN35" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO35" t="n">
         <v>55</v>
@@ -9389,16 +9389,16 @@
         <v>23</v>
       </c>
       <c r="BD35" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE35" t="n">
+        <v>55</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG35" t="n">
         <v>50</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BG35" t="n">
-        <v>48</v>
       </c>
       <c r="BH35" t="n">
         <v>3.15</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -9496,7 +9496,7 @@
         <v>1.89</v>
       </c>
       <c r="G36" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="H36" t="n">
         <v>4.2</v>
@@ -9532,10 +9532,10 @@
         <v>1.39</v>
       </c>
       <c r="S36" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T36" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U36" t="n">
         <v>2.12</v>
@@ -9550,13 +9550,13 @@
         <v>20</v>
       </c>
       <c r="Y36" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z36" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AA36" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB36" t="n">
         <v>11</v>
@@ -9568,7 +9568,7 @@
         <v>21</v>
       </c>
       <c r="AE36" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF36" t="n">
         <v>15</v>
@@ -9580,7 +9580,7 @@
         <v>23</v>
       </c>
       <c r="AI36" t="n">
-        <v>60</v>
+        <v>320</v>
       </c>
       <c r="AJ36" t="n">
         <v>24</v>
@@ -9610,7 +9610,7 @@
         <v>16</v>
       </c>
       <c r="AS36" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT36" t="n">
         <v>8</v>
@@ -9634,7 +9634,7 @@
         <v>16.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB36" t="n">
         <v>19</v>
@@ -9655,68 +9655,68 @@
         <v>10.5</v>
       </c>
       <c r="BH36" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BI36" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BJ36" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK36" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BL36" t="n">
         <v>1000</v>
       </c>
       <c r="BM36" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BN36" t="n">
         <v>4.7</v>
       </c>
       <c r="BO36" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP36" t="n">
         <v>13</v>
       </c>
       <c r="BQ36" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR36" t="n">
         <v>26</v>
       </c>
       <c r="BS36" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT36" t="n">
         <v>8</v>
       </c>
       <c r="BU36" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BV36" t="n">
         <v>38</v>
       </c>
       <c r="BW36" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX36" t="n">
         <v>1000</v>
       </c>
       <c r="BY36" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ36" t="n">
         <v>22</v>
       </c>
       <c r="CA36" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -9894,7 +9894,7 @@
         <v>6.4</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.98</v>
+        <v>4.4</v>
       </c>
       <c r="BD37" t="n">
         <v>2.14</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -10031,19 +10031,19 @@
         <v>1.28</v>
       </c>
       <c r="P38" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="R38" t="n">
         <v>1.44</v>
       </c>
       <c r="S38" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T38" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U38" t="n">
         <v>2.3</v>
@@ -10061,7 +10061,7 @@
         <v>16</v>
       </c>
       <c r="Z38" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA38" t="n">
         <v>75</v>
@@ -10103,7 +10103,7 @@
         <v>80</v>
       </c>
       <c r="AN38" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AO38" t="n">
         <v>40</v>
@@ -10142,7 +10142,7 @@
         <v>16</v>
       </c>
       <c r="BA38" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB38" t="n">
         <v>23</v>
@@ -10154,7 +10154,7 @@
         <v>29</v>
       </c>
       <c r="BE38" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="BF38" t="n">
         <v>12</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -10255,13 +10255,13 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="G39" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="H39" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="I39" t="n">
         <v>13.5</v>
@@ -10270,7 +10270,7 @@
         <v>7.6</v>
       </c>
       <c r="K39" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
@@ -10306,7 +10306,7 @@
         <v>1.08</v>
       </c>
       <c r="W39" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="X39" t="n">
         <v>950</v>
@@ -10321,7 +10321,7 @@
         <v>420</v>
       </c>
       <c r="AB39" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AC39" t="n">
         <v>970</v>
@@ -10342,7 +10342,7 @@
         <v>950</v>
       </c>
       <c r="AI39" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AJ39" t="n">
         <v>13</v>
@@ -10357,46 +10357,46 @@
         <v>90</v>
       </c>
       <c r="AN39" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AO39" t="n">
         <v>120</v>
       </c>
       <c r="AP39" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AQ39" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AR39" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS39" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV39" t="n">
         <v>8.4</v>
       </c>
-      <c r="AT39" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV39" t="n">
+      <c r="AW39" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ39" t="n">
         <v>7.2</v>
       </c>
-      <c r="AW39" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BA39" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB39" t="n">
         <v>11</v>
@@ -10405,10 +10405,10 @@
         <v>10.5</v>
       </c>
       <c r="BD39" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE39" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF39" t="n">
         <v>2.7</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -10545,13 +10545,13 @@
         <v>1.63</v>
       </c>
       <c r="R40" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S40" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="T40" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="U40" t="n">
         <v>2.2</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -11020,10 +11020,10 @@
         <v>3.8</v>
       </c>
       <c r="G42" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H42" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="I42" t="n">
         <v>2.02</v>
@@ -11035,7 +11035,7 @@
         <v>4.4</v>
       </c>
       <c r="L42" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M42" t="n">
         <v>1.04</v>
@@ -11068,7 +11068,7 @@
         <v>1.98</v>
       </c>
       <c r="W42" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X42" t="n">
         <v>22</v>
@@ -11107,7 +11107,7 @@
         <v>30</v>
       </c>
       <c r="AJ42" t="n">
-        <v>900</v>
+        <v>170</v>
       </c>
       <c r="AK42" t="n">
         <v>100</v>
@@ -11161,13 +11161,13 @@
         <v>7.6</v>
       </c>
       <c r="BB42" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC42" t="n">
-        <v>8.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="BD42" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="BE42" t="n">
         <v>8.6</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -11271,22 +11271,22 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="G43" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="H43" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="I43" t="n">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="J43" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="K43" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="L43" t="n">
         <v>1.01</v>
@@ -11304,7 +11304,7 @@
         <v>1.26</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="R43" t="n">
         <v>1.26</v>
@@ -11319,10 +11319,10 @@
         <v>1.11</v>
       </c>
       <c r="V43" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W43" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="X43" t="n">
         <v>950</v>
@@ -11331,103 +11331,103 @@
         <v>950</v>
       </c>
       <c r="Z43" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AA43" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB43" t="n">
         <v>950</v>
       </c>
       <c r="AC43" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AD43" t="n">
         <v>950</v>
       </c>
       <c r="AE43" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF43" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AG43" t="n">
-        <v>950</v>
+        <v>85</v>
       </c>
       <c r="AH43" t="n">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AI43" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ43" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AK43" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AL43" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AM43" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN43" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AO43" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AQ43" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AU43" t="n">
         <v>1.26</v>
       </c>
-      <c r="AR43" t="n">
+      <c r="AV43" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AX43" t="n">
         <v>1.26</v>
       </c>
-      <c r="AS43" t="n">
+      <c r="AY43" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BF43" t="n">
         <v>1.27</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BB43" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BC43" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BD43" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BE43" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BF43" t="n">
-        <v>1.24</v>
       </c>
       <c r="BG43" t="n">
         <v>1.55</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -11549,28 +11549,28 @@
         <v>1.06</v>
       </c>
       <c r="N44" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="O44" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P44" t="n">
         <v>2.02</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R44" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S44" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T44" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U44" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="V44" t="n">
         <v>1.54</v>
@@ -11579,10 +11579,10 @@
         <v>1.58</v>
       </c>
       <c r="X44" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Y44" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z44" t="n">
         <v>18.5</v>
@@ -11591,7 +11591,7 @@
         <v>44</v>
       </c>
       <c r="AB44" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC44" t="n">
         <v>7.8</v>
@@ -11600,7 +11600,7 @@
         <v>12.5</v>
       </c>
       <c r="AE44" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF44" t="n">
         <v>17.5</v>
@@ -11627,16 +11627,16 @@
         <v>80</v>
       </c>
       <c r="AN44" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO44" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AP44" t="n">
         <v>14</v>
       </c>
       <c r="AQ44" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR44" t="n">
         <v>17.5</v>
@@ -11657,7 +11657,7 @@
         <v>27</v>
       </c>
       <c r="AX44" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AY44" t="n">
         <v>11</v>
@@ -11669,25 +11669,25 @@
         <v>34</v>
       </c>
       <c r="BB44" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BC44" t="n">
         <v>25</v>
       </c>
       <c r="BD44" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE44" t="n">
         <v>28</v>
       </c>
       <c r="BF44" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG44" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BH44" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BI44" t="n">
         <v>2.98</v>
@@ -11696,7 +11696,7 @@
         <v>9.4</v>
       </c>
       <c r="BK44" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL44" t="n">
         <v>1000</v>
@@ -11714,13 +11714,13 @@
         <v>20</v>
       </c>
       <c r="BQ44" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR44" t="n">
         <v>32</v>
       </c>
       <c r="BS44" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT44" t="n">
         <v>6.2</v>
@@ -11732,13 +11732,13 @@
         <v>22</v>
       </c>
       <c r="BW44" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX44" t="n">
         <v>34</v>
       </c>
       <c r="BY44" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ44" t="n">
         <v>0</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -11779,10 +11779,10 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="G45" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="H45" t="n">
         <v>11</v>
@@ -11815,7 +11815,7 @@
         <v>1.55</v>
       </c>
       <c r="R45" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="S45" t="n">
         <v>2.4</v>
@@ -11830,13 +11830,13 @@
         <v>1.09</v>
       </c>
       <c r="W45" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="X45" t="n">
         <v>30</v>
       </c>
       <c r="Y45" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Z45" t="n">
         <v>110</v>
@@ -11845,7 +11845,7 @@
         <v>530</v>
       </c>
       <c r="AB45" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC45" t="n">
         <v>14.5</v>
@@ -11869,7 +11869,7 @@
         <v>130</v>
       </c>
       <c r="AJ45" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AK45" t="n">
         <v>13</v>
@@ -11893,19 +11893,19 @@
         <v>36</v>
       </c>
       <c r="AR45" t="n">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="AS45" t="n">
         <v>120</v>
       </c>
       <c r="AT45" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU45" t="n">
         <v>13.5</v>
       </c>
       <c r="AV45" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AW45" t="n">
         <v>44</v>
@@ -11923,7 +11923,7 @@
         <v>40</v>
       </c>
       <c r="BB45" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC45" t="n">
         <v>12.5</v>
@@ -11947,16 +11947,16 @@
         <v>4.1</v>
       </c>
       <c r="BJ45" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK45" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BL45" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="BM45" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN45" t="n">
         <v>3.9</v>
@@ -11968,41 +11968,41 @@
         <v>7.2</v>
       </c>
       <c r="BQ45" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BR45" t="n">
         <v>21</v>
       </c>
       <c r="BS45" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BT45" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BU45" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BV45" t="n">
+        <v>95</v>
+      </c>
+      <c r="BW45" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BX45" t="n">
+        <v>80</v>
+      </c>
+      <c r="BY45" t="n">
         <v>14</v>
-      </c>
-      <c r="BU45" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BV45" t="n">
-        <v>90</v>
-      </c>
-      <c r="BW45" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BX45" t="n">
-        <v>75</v>
-      </c>
-      <c r="BY45" t="n">
-        <v>15.5</v>
       </c>
       <c r="BZ45" t="n">
         <v>10</v>
       </c>
       <c r="CA45" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -12036,13 +12036,13 @@
         <v>1.82</v>
       </c>
       <c r="G46" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="H46" t="n">
         <v>4.8</v>
       </c>
       <c r="I46" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J46" t="n">
         <v>3.5</v>
@@ -12084,7 +12084,7 @@
         <v>1.22</v>
       </c>
       <c r="W46" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X46" t="n">
         <v>13.5</v>
@@ -12129,7 +12129,7 @@
         <v>23</v>
       </c>
       <c r="AL46" t="n">
-        <v>190</v>
+        <v>110</v>
       </c>
       <c r="AM46" t="n">
         <v>580</v>
@@ -12150,7 +12150,7 @@
         <v>14.5</v>
       </c>
       <c r="AS46" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT46" t="n">
         <v>6.2</v>
@@ -12183,10 +12183,10 @@
         <v>18</v>
       </c>
       <c r="BD46" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE46" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF46" t="n">
         <v>11.5</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -12287,19 +12287,19 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G47" t="n">
         <v>3.65</v>
       </c>
       <c r="H47" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="I47" t="n">
         <v>2.7</v>
       </c>
       <c r="J47" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="K47" t="n">
         <v>3.35</v>
@@ -12308,31 +12308,31 @@
         <v>1.48</v>
       </c>
       <c r="M47" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N47" t="n">
-        <v>2.46</v>
+        <v>2.26</v>
       </c>
       <c r="O47" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="P47" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="R47" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="S47" t="n">
-        <v>1.05</v>
+        <v>2.62</v>
       </c>
       <c r="T47" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="U47" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V47" t="n">
         <v>1.59</v>
@@ -12344,109 +12344,109 @@
         <v>9.6</v>
       </c>
       <c r="Y47" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="Z47" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AA47" t="n">
-        <v>48</v>
+        <v>220</v>
       </c>
       <c r="AB47" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC47" t="n">
         <v>7.4</v>
       </c>
       <c r="AD47" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE47" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AF47" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AG47" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AH47" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI47" t="n">
-        <v>70</v>
+        <v>450</v>
       </c>
       <c r="AJ47" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AK47" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="AL47" t="n">
-        <v>85</v>
+        <v>450</v>
       </c>
       <c r="AM47" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AN47" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AO47" t="n">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="AP47" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="AQ47" t="n">
-        <v>3.65</v>
+        <v>4.9</v>
       </c>
       <c r="AR47" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU47" t="n">
         <v>4.4</v>
       </c>
-      <c r="AS47" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AU47" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AV47" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="AW47" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="AX47" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="AY47" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="AZ47" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BA47" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="BB47" t="n">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="BC47" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="BD47" t="n">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="BE47" t="n">
-        <v>5.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF47" t="n">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="BG47" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BH47" t="n">
         <v>3.1</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -12571,13 +12571,13 @@
         <v>1.14</v>
       </c>
       <c r="P48" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.14</v>
+        <v>1.45</v>
       </c>
       <c r="R48" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="S48" t="n">
         <v>1.8</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G49" t="n">
         <v>1.99</v>
@@ -12819,7 +12819,7 @@
         <v>1.01</v>
       </c>
       <c r="N49" t="n">
-        <v>1.1</v>
+        <v>1.53</v>
       </c>
       <c r="O49" t="n">
         <v>1.11</v>
@@ -12843,7 +12843,7 @@
         <v>1.11</v>
       </c>
       <c r="V49" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="W49" t="n">
         <v>2</v>
@@ -12876,7 +12876,7 @@
         <v>1000</v>
       </c>
       <c r="AG49" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AH49" t="n">
         <v>1000</v>
@@ -12903,58 +12903,58 @@
         <v>1000</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AS49" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AT49" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AU49" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AV49" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AW49" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AX49" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AY49" t="n">
         <v>1.01</v>
       </c>
       <c r="AZ49" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BA49" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BB49" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BC49" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BD49" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BE49" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BG49" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BH49" t="n">
         <v>1000</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -13049,22 +13049,22 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="G50" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="H50" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I50" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="J50" t="n">
         <v>3.05</v>
       </c>
       <c r="K50" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="L50" t="n">
         <v>1.01</v>
@@ -13088,73 +13088,73 @@
         <v>1.13</v>
       </c>
       <c r="S50" t="n">
-        <v>2.96</v>
+        <v>2.46</v>
       </c>
       <c r="T50" t="n">
-        <v>2.1</v>
+        <v>1.11</v>
       </c>
       <c r="U50" t="n">
-        <v>1.74</v>
+        <v>1.11</v>
       </c>
       <c r="V50" t="n">
         <v>1.24</v>
       </c>
       <c r="W50" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="X50" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Y50" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z50" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA50" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB50" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC50" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD50" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE50" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF50" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG50" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH50" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI50" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ50" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AK50" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL50" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM50" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AN50" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AO50" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AP50" t="n">
         <v>1.01</v>
@@ -13211,55 +13211,55 @@
         <v>1.01</v>
       </c>
       <c r="BH50" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI50" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BJ50" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK50" t="n">
         <v>1.01</v>
       </c>
       <c r="BL50" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="BM50" t="n">
         <v>1.01</v>
       </c>
       <c r="BN50" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO50" t="n">
         <v>1.01</v>
       </c>
       <c r="BP50" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BQ50" t="n">
         <v>1.01</v>
       </c>
       <c r="BR50" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS50" t="n">
         <v>1.01</v>
       </c>
       <c r="BT50" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BU50" t="n">
         <v>1.01</v>
       </c>
       <c r="BV50" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW50" t="n">
         <v>1.01</v>
       </c>
       <c r="BX50" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BY50" t="n">
         <v>1.01</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>
@@ -13303,22 +13303,22 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G51" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H51" t="n">
         <v>3.7</v>
       </c>
       <c r="I51" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="J51" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K51" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L51" t="n">
         <v>1.3</v>
@@ -13336,133 +13336,133 @@
         <v>2.14</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R51" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T51" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U51" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V51" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W51" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="X51" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Y51" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z51" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA51" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AB51" t="n">
         <v>13</v>
       </c>
       <c r="AC51" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD51" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE51" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF51" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG51" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH51" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI51" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ51" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK51" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL51" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM51" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN51" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO51" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AP51" t="n">
         <v>14.5</v>
       </c>
       <c r="AQ51" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR51" t="n">
-        <v>4.7</v>
+        <v>25</v>
       </c>
       <c r="AS51" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AT51" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AU51" t="n">
         <v>7.8</v>
       </c>
       <c r="AV51" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW51" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="AX51" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY51" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ51" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA51" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BB51" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC51" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD51" t="n">
-        <v>4.9</v>
+        <v>28</v>
       </c>
       <c r="BE51" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="BF51" t="n">
         <v>11.5</v>
       </c>
       <c r="BG51" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="BH51" t="n">
         <v>3.75</v>
@@ -13474,13 +13474,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK51" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BL51" t="n">
         <v>1000</v>
       </c>
       <c r="BM51" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BN51" t="n">
         <v>5</v>
@@ -13492,41 +13492,41 @@
         <v>14.5</v>
       </c>
       <c r="BQ51" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR51" t="n">
         <v>26</v>
       </c>
       <c r="BS51" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT51" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU51" t="n">
         <v>5.4</v>
       </c>
       <c r="BV51" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BW51" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX51" t="n">
         <v>38</v>
       </c>
       <c r="BY51" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ51" t="n">
         <v>21</v>
       </c>
       <c r="CA51" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-05-13 19:57:10</t>
+          <t>2026-05-13 22:15:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-14.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G2" t="n">
         <v>2.2</v>
@@ -866,13 +866,13 @@
         <v>3.85</v>
       </c>
       <c r="I2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J2" t="n">
         <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L2" t="n">
         <v>1.5</v>
@@ -887,16 +887,16 @@
         <v>1.44</v>
       </c>
       <c r="P2" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q2" t="n">
         <v>2.26</v>
       </c>
       <c r="R2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S2" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T2" t="n">
         <v>1.96</v>
@@ -905,7 +905,7 @@
         <v>1.85</v>
       </c>
       <c r="V2" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W2" t="n">
         <v>1.84</v>
@@ -914,10 +914,10 @@
         <v>13</v>
       </c>
       <c r="Y2" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="Z2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AA2" t="n">
         <v>500</v>
@@ -929,10 +929,10 @@
         <v>7.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF2" t="n">
         <v>12.5</v>
@@ -944,19 +944,19 @@
         <v>23</v>
       </c>
       <c r="AI2" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AJ2" t="n">
         <v>27</v>
       </c>
       <c r="AK2" t="n">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="AL2" t="n">
         <v>55</v>
       </c>
       <c r="AM2" t="n">
-        <v>170</v>
+        <v>580</v>
       </c>
       <c r="AN2" t="n">
         <v>600</v>
@@ -974,22 +974,22 @@
         <v>20</v>
       </c>
       <c r="AS2" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AT2" t="n">
         <v>7.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
         <v>13</v>
       </c>
       <c r="AW2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX2" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>11</v>
       </c>
       <c r="AY2" t="n">
         <v>9</v>
@@ -998,25 +998,25 @@
         <v>16.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BB2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC2" t="n">
         <v>23</v>
       </c>
-      <c r="BC2" t="n">
-        <v>21</v>
-      </c>
       <c r="BD2" t="n">
-        <v>10.5</v>
+        <v>22</v>
       </c>
       <c r="BE2" t="n">
         <v>12</v>
       </c>
       <c r="BF2" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BG2" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH2" t="n">
         <v>3</v>
@@ -1028,19 +1028,19 @@
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BN2" t="n">
         <v>4.6</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
@@ -1052,25 +1052,25 @@
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="H3" t="n">
         <v>2.7</v>
@@ -1126,34 +1126,34 @@
         <v>3.05</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L3" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="P3" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="U3" t="n">
         <v>1.98</v>
@@ -1162,13 +1162,13 @@
         <v>1.54</v>
       </c>
       <c r="W3" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X3" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z3" t="n">
         <v>21</v>
@@ -1195,7 +1195,7 @@
         <v>16</v>
       </c>
       <c r="AH3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI3" t="n">
         <v>60</v>
@@ -1213,16 +1213,16 @@
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>44</v>
+        <v>600</v>
       </c>
       <c r="AO3" t="n">
-        <v>36</v>
+        <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR3" t="n">
         <v>12.5</v>
@@ -1249,10 +1249,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BB3" t="n">
         <v>36</v>
@@ -1270,13 +1270,13 @@
         <v>6.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.7</v>
+        <v>30</v>
       </c>
       <c r="BH3" t="n">
         <v>3.45</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BJ3" t="n">
         <v>12.5</v>
@@ -1288,7 +1288,7 @@
         <v>190</v>
       </c>
       <c r="BM3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BN3" t="n">
         <v>7</v>
@@ -1306,7 +1306,7 @@
         <v>55</v>
       </c>
       <c r="BS3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BT3" t="n">
         <v>6.6</v>
@@ -1321,20 +1321,20 @@
         <v>4.1</v>
       </c>
       <c r="BX3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BY3" t="n">
         <v>4.4</v>
       </c>
       <c r="BZ3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="CA3" t="n">
         <v>4.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="I4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K4" t="n">
         <v>4.6</v>
@@ -1389,73 +1389,73 @@
         <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>3.45</v>
+        <v>5.4</v>
       </c>
       <c r="O4" t="n">
         <v>1.18</v>
       </c>
       <c r="P4" t="n">
-        <v>2.34</v>
+        <v>2.52</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="S4" t="n">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="T4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="U4" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V4" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="W4" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X4" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="Y4" t="n">
         <v>500</v>
       </c>
       <c r="Z4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA4" t="n">
         <v>500</v>
       </c>
-      <c r="AA4" t="n">
-        <v>900</v>
-      </c>
       <c r="AB4" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="AC4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AD4" t="n">
         <v>170</v>
       </c>
       <c r="AE4" t="n">
-        <v>500</v>
+        <v>340</v>
       </c>
       <c r="AF4" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AG4" t="n">
-        <v>36</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AH4" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AI4" t="n">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="AJ4" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AK4" t="n">
         <v>130</v>
@@ -1467,64 +1467,64 @@
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>55</v>
+        <v>9.6</v>
       </c>
       <c r="AO4" t="n">
         <v>600</v>
       </c>
       <c r="AP4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV4" t="n">
         <v>6.8</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS4" t="n">
+      <c r="AW4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>12</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF4" t="n">
         <v>8</v>
       </c>
-      <c r="AT4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BG4" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH4" t="n">
         <v>5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -1619,25 +1619,25 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="H5" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="I5" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="J5" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K5" t="n">
         <v>4.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="M5" t="n">
         <v>1.04</v>
@@ -1667,10 +1667,10 @@
         <v>2.52</v>
       </c>
       <c r="V5" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="W5" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="X5" t="n">
         <v>500</v>
@@ -1727,7 +1727,7 @@
         <v>55</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="AQ5" t="n">
         <v>7.6</v>
@@ -1772,13 +1772,13 @@
         <v>16</v>
       </c>
       <c r="BE5" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF5" t="n">
         <v>10.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH5" t="n">
         <v>4.5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -1891,13 +1891,13 @@
         <v>4.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="O6" t="n">
         <v>1.24</v>
@@ -1909,7 +1909,7 @@
         <v>1.72</v>
       </c>
       <c r="R6" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S6" t="n">
         <v>2.8</v>
@@ -1918,10 +1918,10 @@
         <v>1.62</v>
       </c>
       <c r="U6" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V6" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W6" t="n">
         <v>1.53</v>
@@ -1936,7 +1936,7 @@
         <v>21</v>
       </c>
       <c r="AA6" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="AB6" t="n">
         <v>14</v>
@@ -1963,7 +1963,7 @@
         <v>36</v>
       </c>
       <c r="AJ6" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AK6" t="n">
         <v>28</v>
@@ -1978,61 +1978,61 @@
         <v>19.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AP6" t="n">
-        <v>6.6</v>
+        <v>16.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.8</v>
+        <v>17</v>
       </c>
       <c r="AS6" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.2</v>
+        <v>13.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>9.199999999999999</v>
+        <v>17</v>
       </c>
       <c r="AY6" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.8</v>
+        <v>16.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.6</v>
+        <v>16</v>
       </c>
       <c r="BC6" t="n">
-        <v>7.2</v>
+        <v>13.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>8.199999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.6</v>
+        <v>16</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.6</v>
+        <v>16.5</v>
       </c>
       <c r="BH6" t="n">
         <v>3.95</v>
@@ -2044,19 +2044,19 @@
         <v>9</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BN6" t="n">
         <v>6.2</v>
       </c>
       <c r="BO6" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BP6" t="n">
         <v>19.5</v>
@@ -2074,7 +2074,7 @@
         <v>6.2</v>
       </c>
       <c r="BU6" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="BV6" t="n">
         <v>19.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
         <v>4.9</v>
@@ -2151,22 +2151,22 @@
         <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="O7" t="n">
         <v>1.18</v>
       </c>
       <c r="P7" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R7" t="n">
         <v>1.58</v>
       </c>
       <c r="S7" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T7" t="n">
         <v>1.58</v>
@@ -2178,7 +2178,7 @@
         <v>2.04</v>
       </c>
       <c r="W7" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X7" t="n">
         <v>27</v>
@@ -2211,7 +2211,7 @@
         <v>19</v>
       </c>
       <c r="AH7" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI7" t="n">
         <v>28</v>
@@ -2235,43 +2235,43 @@
         <v>8.6</v>
       </c>
       <c r="AP7" t="n">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="AQ7" t="n">
         <v>5.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.199999999999999</v>
+        <v>17</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.2</v>
+        <v>18.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.1</v>
+        <v>8.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AW7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BB7" t="n">
         <v>7.4</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>7.6</v>
       </c>
       <c r="BC7" t="n">
         <v>7</v>
@@ -2280,7 +2280,7 @@
         <v>7</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF7" t="n">
         <v>6.6</v>
@@ -2292,7 +2292,7 @@
         <v>4.7</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="BJ7" t="n">
         <v>9.4</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="G8" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="H8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
         <v>5.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="K8" t="n">
         <v>5.2</v>
@@ -2405,43 +2405,43 @@
         <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="O8" t="n">
         <v>1.18</v>
       </c>
       <c r="P8" t="n">
-        <v>2.74</v>
+        <v>2.58</v>
       </c>
       <c r="Q8" t="n">
         <v>1.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="S8" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="T8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U8" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="V8" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W8" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="X8" t="n">
-        <v>90</v>
+        <v>950</v>
       </c>
       <c r="Y8" t="n">
         <v>950</v>
       </c>
       <c r="Z8" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AA8" t="n">
         <v>900</v>
@@ -2456,7 +2456,7 @@
         <v>970</v>
       </c>
       <c r="AE8" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AF8" t="n">
         <v>970</v>
@@ -2468,7 +2468,7 @@
         <v>60</v>
       </c>
       <c r="AI8" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AJ8" t="n">
         <v>970</v>
@@ -2477,10 +2477,10 @@
         <v>970</v>
       </c>
       <c r="AL8" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AM8" t="n">
-        <v>70</v>
+        <v>580</v>
       </c>
       <c r="AN8" t="n">
         <v>85</v>
@@ -2489,28 +2489,28 @@
         <v>600</v>
       </c>
       <c r="AP8" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AT8" t="n">
         <v>7</v>
       </c>
       <c r="AU8" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="AV8" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.68</v>
+        <v>2.42</v>
       </c>
       <c r="AX8" t="n">
         <v>7</v>
@@ -2522,7 +2522,7 @@
         <v>9</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="BB8" t="n">
         <v>7.6</v>
@@ -2534,67 +2534,67 @@
         <v>11</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.64</v>
+        <v>2.3</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.9</v>
+        <v>4.6</v>
       </c>
       <c r="BG8" t="n">
         <v>6.2</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>13</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU8" t="n">
         <v>5.1</v>
       </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>3.1</v>
-      </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.11</v>
+        <v>1.69</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.11</v>
+        <v>1.77</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>1.87</v>
       </c>
       <c r="G9" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H9" t="n">
         <v>4.6</v>
@@ -2674,10 +2674,10 @@
         <v>1.31</v>
       </c>
       <c r="S9" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="T9" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U9" t="n">
         <v>1.98</v>
@@ -2686,7 +2686,7 @@
         <v>1.24</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X9" t="n">
         <v>13.5</v>
@@ -2713,7 +2713,7 @@
         <v>85</v>
       </c>
       <c r="AF9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG9" t="n">
         <v>12</v>
@@ -2749,10 +2749,10 @@
         <v>13.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>16.5</v>
+        <v>26</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AT9" t="n">
         <v>7.4</v>
@@ -2764,19 +2764,19 @@
         <v>16.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AX9" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AY9" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB9" t="n">
         <v>19</v>
@@ -2788,13 +2788,13 @@
         <v>34</v>
       </c>
       <c r="BE9" t="n">
-        <v>7.2</v>
+        <v>28</v>
       </c>
       <c r="BF9" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.6</v>
+        <v>26</v>
       </c>
       <c r="BH9" t="n">
         <v>3.3</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -2913,7 +2913,7 @@
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="O10" t="n">
         <v>1.18</v>
@@ -3009,7 +3009,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AU10" t="n">
         <v>5.1</v>
@@ -3021,13 +3021,13 @@
         <v>7.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AY10" t="n">
         <v>6.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BA10" t="n">
         <v>7.6</v>
@@ -3036,7 +3036,7 @@
         <v>6.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BD10" t="n">
         <v>6.8</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
         <v>1.51</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="I11" t="n">
         <v>7.4</v>
@@ -3158,7 +3158,7 @@
         <v>4.9</v>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L11" t="n">
         <v>1.19</v>
@@ -3167,7 +3167,7 @@
         <v>1.02</v>
       </c>
       <c r="N11" t="n">
-        <v>3.85</v>
+        <v>7.2</v>
       </c>
       <c r="O11" t="n">
         <v>1.13</v>
@@ -3176,16 +3176,16 @@
         <v>2.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="R11" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="S11" t="n">
         <v>1.9</v>
       </c>
       <c r="T11" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U11" t="n">
         <v>2.3</v>
@@ -3236,10 +3236,10 @@
         <v>15.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM11" t="n">
         <v>260</v>
@@ -3251,28 +3251,28 @@
         <v>330</v>
       </c>
       <c r="AP11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="AR11" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU11" t="n">
         <v>7</v>
       </c>
       <c r="AV11" t="n">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="AW11" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AX11" t="n">
         <v>6.4</v>
@@ -3281,92 +3281,92 @@
         <v>6.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>6.8</v>
+        <v>16</v>
       </c>
       <c r="BA11" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB11" t="n">
         <v>6.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BD11" t="n">
         <v>7.4</v>
       </c>
       <c r="BE11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BG11" t="n">
         <v>9</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>8.6</v>
       </c>
       <c r="BH11" t="n">
         <v>6.2</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BJ11" t="n">
         <v>11</v>
       </c>
       <c r="BK11" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BL11" t="n">
         <v>85</v>
       </c>
       <c r="BM11" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BN11" t="n">
         <v>5.3</v>
       </c>
       <c r="BO11" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="BP11" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BQ11" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BR11" t="n">
         <v>20</v>
       </c>
       <c r="BS11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BT11" t="n">
         <v>12.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BV11" t="n">
         <v>55</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BX11" t="n">
         <v>46</v>
       </c>
       <c r="BY11" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BZ11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CA11" t="n">
         <v>3.6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -3397,220 +3397,220 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="G12" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="H12" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="I12" t="n">
-        <v>3.35</v>
+        <v>2.84</v>
       </c>
       <c r="J12" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="K12" t="n">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M12" t="n">
         <v>1.02</v>
       </c>
       <c r="N12" t="n">
-        <v>1.42</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P12" t="n">
-        <v>1.42</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.18</v>
+        <v>1.54</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="S12" t="n">
-        <v>1.05</v>
+        <v>2.22</v>
       </c>
       <c r="T12" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="U12" t="n">
-        <v>1.11</v>
+        <v>2.42</v>
       </c>
       <c r="V12" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="W12" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="X12" t="n">
-        <v>950</v>
+        <v>26</v>
       </c>
       <c r="Y12" t="n">
-        <v>950</v>
+        <v>17</v>
       </c>
       <c r="Z12" t="n">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="AA12" t="n">
-        <v>900</v>
+        <v>40</v>
       </c>
       <c r="AB12" t="n">
-        <v>950</v>
+        <v>18</v>
       </c>
       <c r="AC12" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="AD12" t="n">
-        <v>950</v>
+        <v>14</v>
       </c>
       <c r="AE12" t="n">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="AF12" t="n">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AG12" t="n">
-        <v>950</v>
+        <v>14.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>60</v>
+        <v>16.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AJ12" t="n">
-        <v>900</v>
+        <v>44</v>
       </c>
       <c r="AK12" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AL12" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AM12" t="n">
-        <v>580</v>
+        <v>65</v>
       </c>
       <c r="AN12" t="n">
-        <v>600</v>
+        <v>18</v>
       </c>
       <c r="AO12" t="n">
-        <v>600</v>
+        <v>16</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.33</v>
+        <v>5.1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.31</v>
+        <v>4.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.33</v>
+        <v>4.9</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.34</v>
+        <v>5.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.32</v>
+        <v>4.7</v>
       </c>
       <c r="AU12" t="n">
         <v>5.1</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.32</v>
+        <v>4.3</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.34</v>
+        <v>5.1</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.34</v>
+        <v>5</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.32</v>
+        <v>4.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.28</v>
+        <v>5.1</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.34</v>
+        <v>5.3</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.35</v>
+        <v>5.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.34</v>
+        <v>5.2</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.35</v>
+        <v>5.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.34</v>
+        <v>5.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.55</v>
+        <v>4.7</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.55</v>
+        <v>4.5</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BL12" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BP12" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BR12" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BV12" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -3651,37 +3651,37 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="I13" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="J13" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="K13" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L13" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="M13" t="n">
         <v>1.03</v>
       </c>
       <c r="N13" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
         <v>1.2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
         <v>1.58</v>
@@ -3690,7 +3690,7 @@
         <v>1.54</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="T13" t="n">
         <v>1.71</v>
@@ -3699,7 +3699,7 @@
         <v>2.16</v>
       </c>
       <c r="V13" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="W13" t="n">
         <v>1.2</v>
@@ -3714,7 +3714,7 @@
         <v>19.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AB13" t="n">
         <v>70</v>
@@ -3726,13 +3726,13 @@
         <v>15</v>
       </c>
       <c r="AE13" t="n">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="AF13" t="n">
         <v>350</v>
       </c>
       <c r="AG13" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AH13" t="n">
         <v>44</v>
@@ -3753,64 +3753,64 @@
         <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>440</v>
+        <v>600</v>
       </c>
       <c r="AO13" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="AR13" t="n">
         <v>5.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>4.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AX13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>6.4</v>
       </c>
-      <c r="AY13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BA13" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BC13" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BD13" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BF13" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BH13" t="n">
         <v>4.8</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -3908,43 +3908,43 @@
         <v>2.66</v>
       </c>
       <c r="G14" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="H14" t="n">
         <v>2.36</v>
       </c>
       <c r="I14" t="n">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K14" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="M14" t="n">
         <v>1.04</v>
       </c>
       <c r="N14" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="O14" t="n">
         <v>1.21</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="R14" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="T14" t="n">
         <v>1.56</v>
@@ -3953,10 +3953,10 @@
         <v>2.4</v>
       </c>
       <c r="V14" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W14" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="X14" t="n">
         <v>90</v>
@@ -4010,64 +4010,64 @@
         <v>500</v>
       </c>
       <c r="AO14" t="n">
-        <v>970</v>
+        <v>600</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.34</v>
+        <v>3.45</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2.46</v>
+        <v>5.1</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.22</v>
+        <v>4.4</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.32</v>
+        <v>2.56</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.36</v>
+        <v>5</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.15</v>
+        <v>7</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.36</v>
+        <v>5</v>
       </c>
       <c r="AX14" t="n">
-        <v>2.18</v>
+        <v>3.05</v>
       </c>
       <c r="AY14" t="n">
-        <v>2.6</v>
+        <v>3.95</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.32</v>
+        <v>5</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.32</v>
+        <v>2.54</v>
       </c>
       <c r="BB14" t="n">
-        <v>2.34</v>
+        <v>6.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.4</v>
+        <v>5.9</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.26</v>
+        <v>3.7</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.32</v>
+        <v>3.3</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.24</v>
+        <v>2.98</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="BH14" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BI14" t="n">
         <v>2.92</v>
@@ -4082,7 +4082,7 @@
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="BN14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -4159,97 +4159,97 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="G15" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="H15" t="n">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="I15" t="n">
-        <v>14</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K15" t="n">
-        <v>18</v>
+        <v>7.6</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M15" t="n">
         <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>2.82</v>
+        <v>6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="P15" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.11</v>
+        <v>1.39</v>
       </c>
       <c r="R15" t="n">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="S15" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="T15" t="n">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="U15" t="n">
-        <v>1.11</v>
+        <v>2.24</v>
       </c>
       <c r="V15" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="W15" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="X15" t="n">
         <v>950</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AA15" t="n">
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
+        <v>80</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD15" t="n">
         <v>950</v>
       </c>
-      <c r="AC15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1000</v>
-      </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AF15" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH15" t="n">
         <v>950</v>
       </c>
-      <c r="AH15" t="n">
-        <v>1000</v>
-      </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ15" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AK15" t="n">
         <v>500</v>
@@ -4258,19 +4258,19 @@
         <v>500</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN15" t="n">
-        <v>29</v>
+        <v>4.4</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.17</v>
+        <v>6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AR15" t="n">
         <v>4.2</v>
@@ -4279,100 +4279,100 @@
         <v>4.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.15</v>
+        <v>5.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.18</v>
+        <v>4.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="AW15" t="n">
         <v>4.2</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.18</v>
+        <v>5.8</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.15</v>
+        <v>4.9</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.18</v>
+        <v>5.6</v>
       </c>
       <c r="BA15" t="n">
         <v>4.2</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.18</v>
+        <v>5.3</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.16</v>
+        <v>5.7</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.18</v>
+        <v>5.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.18</v>
+        <v>6</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.33</v>
+        <v>3.7</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="BH15" t="n">
         <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BJ15" t="n">
         <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.04</v>
+        <v>1.6</v>
       </c>
       <c r="BN15" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.04</v>
+        <v>1.63</v>
       </c>
       <c r="BT15" t="n">
         <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.04</v>
+        <v>1.58</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.04</v>
+        <v>1.57</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -4437,16 +4437,16 @@
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>1.1</v>
+        <v>6.2</v>
       </c>
       <c r="O16" t="n">
         <v>1.13</v>
       </c>
       <c r="P16" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="R16" t="n">
         <v>1.73</v>
@@ -4515,7 +4515,7 @@
         <v>500</v>
       </c>
       <c r="AN16" t="n">
-        <v>55</v>
+        <v>10.5</v>
       </c>
       <c r="AO16" t="n">
         <v>970</v>
@@ -4533,10 +4533,10 @@
         <v>5.6</v>
       </c>
       <c r="AT16" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AU16" t="n">
-        <v>4.1</v>
+        <v>9</v>
       </c>
       <c r="AV16" t="n">
         <v>4.5</v>
@@ -4545,28 +4545,28 @@
         <v>5.2</v>
       </c>
       <c r="AX16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AY16" t="n">
-        <v>4.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
         <v>4.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB16" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BD16" t="n">
         <v>5.1</v>
       </c>
       <c r="BE16" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="BF16" t="n">
         <v>3.9</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -4667,25 +4667,25 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="G17" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="H17" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="I17" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K17" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L17" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="M17" t="n">
         <v>1.07</v>
@@ -4694,19 +4694,19 @@
         <v>3.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P17" t="n">
         <v>1.86</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="R17" t="n">
         <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T17" t="n">
         <v>1.74</v>
@@ -4736,16 +4736,16 @@
         <v>970</v>
       </c>
       <c r="AC17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AD17" t="n">
         <v>970</v>
       </c>
       <c r="AE17" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AF17" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG17" t="n">
         <v>24</v>
@@ -4769,22 +4769,22 @@
         <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO17" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP17" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="AQ17" t="n">
         <v>6.4</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="AT17" t="n">
         <v>6.4</v>
@@ -4796,31 +4796,31 @@
         <v>7</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AX17" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="AY17" t="n">
         <v>7</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.1</v>
+        <v>9</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="BF17" t="n">
         <v>4.9</v>
@@ -4829,58 +4829,58 @@
         <v>5.5</v>
       </c>
       <c r="BH17" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.04</v>
+        <v>2.68</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.04</v>
+        <v>1.52</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="BN17" t="n">
         <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.04</v>
+        <v>1.89</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="G18" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H18" t="n">
         <v>3.75</v>
@@ -4933,10 +4933,10 @@
         <v>4.5</v>
       </c>
       <c r="J18" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L18" t="n">
         <v>1.4</v>
@@ -4966,16 +4966,16 @@
         <v>1.8</v>
       </c>
       <c r="U18" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V18" t="n">
         <v>1.28</v>
       </c>
       <c r="W18" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="X18" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="Y18" t="n">
         <v>970</v>
@@ -5026,7 +5026,7 @@
         <v>55</v>
       </c>
       <c r="AO18" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP18" t="n">
         <v>6</v>
@@ -5038,7 +5038,7 @@
         <v>3</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.66</v>
+        <v>2.86</v>
       </c>
       <c r="AT18" t="n">
         <v>5.6</v>
@@ -5047,10 +5047,10 @@
         <v>4.9</v>
       </c>
       <c r="AV18" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="AX18" t="n">
         <v>6.4</v>
@@ -5059,31 +5059,31 @@
         <v>6.2</v>
       </c>
       <c r="AZ18" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.66</v>
+        <v>2.86</v>
       </c>
       <c r="BB18" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.64</v>
+        <v>2.84</v>
       </c>
       <c r="BF18" t="n">
         <v>3.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="BH18" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BI18" t="n">
         <v>2.78</v>
@@ -5092,49 +5092,49 @@
         <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.56</v>
+        <v>5.3</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS18" t="n">
         <v>1.06</v>
       </c>
-      <c r="BN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>1.73</v>
-      </c>
       <c r="BT18" t="n">
         <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>2.24</v>
+        <v>1.07</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.76</v>
+        <v>1.07</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -5175,13 +5175,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="G19" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H19" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I19" t="n">
         <v>3.5</v>
@@ -5205,28 +5205,28 @@
         <v>1.25</v>
       </c>
       <c r="P19" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q19" t="n">
         <v>1.77</v>
       </c>
       <c r="R19" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S19" t="n">
         <v>2.96</v>
       </c>
       <c r="T19" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U19" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V19" t="n">
         <v>1.4</v>
       </c>
       <c r="W19" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="X19" t="n">
         <v>22</v>
@@ -5238,7 +5238,7 @@
         <v>28</v>
       </c>
       <c r="AA19" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB19" t="n">
         <v>13.5</v>
@@ -5259,7 +5259,7 @@
         <v>11</v>
       </c>
       <c r="AH19" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI19" t="n">
         <v>48</v>
@@ -5286,10 +5286,10 @@
         <v>16.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AR19" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AS19" t="n">
         <v>23</v>
@@ -5301,25 +5301,25 @@
         <v>7.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW19" t="n">
         <v>16.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AY19" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ19" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA19" t="n">
         <v>21</v>
       </c>
       <c r="BB19" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="BC19" t="n">
         <v>19.5</v>
@@ -5331,28 +5331,28 @@
         <v>19</v>
       </c>
       <c r="BF19" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BH19" t="n">
         <v>3.8</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BJ19" t="n">
         <v>9</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BN19" t="n">
         <v>5.4</v>
@@ -5364,13 +5364,13 @@
         <v>16</v>
       </c>
       <c r="BQ19" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BR19" t="n">
         <v>27</v>
       </c>
       <c r="BS19" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT19" t="n">
         <v>6.6</v>
@@ -5379,26 +5379,26 @@
         <v>5.2</v>
       </c>
       <c r="BV19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BW19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BX19" t="n">
         <v>34</v>
       </c>
       <c r="BY19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CA19" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -5456,25 +5456,25 @@
         <v>7</v>
       </c>
       <c r="O20" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P20" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R20" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="S20" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="T20" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="U20" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="V20" t="n">
         <v>1.62</v>
@@ -5486,16 +5486,16 @@
         <v>34</v>
       </c>
       <c r="Y20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z20" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="AA20" t="n">
         <v>38</v>
       </c>
       <c r="AB20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC20" t="n">
         <v>11.5</v>
@@ -5528,7 +5528,7 @@
         <v>27</v>
       </c>
       <c r="AM20" t="n">
-        <v>200</v>
+        <v>44</v>
       </c>
       <c r="AN20" t="n">
         <v>12</v>
@@ -5537,19 +5537,19 @@
         <v>11</v>
       </c>
       <c r="AP20" t="n">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="AQ20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR20" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AS20" t="n">
         <v>18</v>
       </c>
       <c r="AT20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU20" t="n">
         <v>9.800000000000001</v>
@@ -5582,31 +5582,31 @@
         <v>15</v>
       </c>
       <c r="BE20" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="BF20" t="n">
         <v>10</v>
       </c>
       <c r="BG20" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH20" t="n">
         <v>5.1</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="BJ20" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BK20" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN20" t="n">
         <v>6.6</v>
@@ -5618,31 +5618,31 @@
         <v>17</v>
       </c>
       <c r="BQ20" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="BR20" t="n">
         <v>22</v>
       </c>
       <c r="BS20" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT20" t="n">
         <v>6.4</v>
       </c>
       <c r="BU20" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BV20" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BW20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX20" t="n">
         <v>22</v>
       </c>
       <c r="BY20" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ20" t="n">
         <v>12.5</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
         <v>4.6</v>
       </c>
       <c r="L21" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="M21" t="n">
         <v>1.02</v>
@@ -5713,13 +5713,13 @@
         <v>1.13</v>
       </c>
       <c r="P21" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q21" t="n">
         <v>1.38</v>
       </c>
       <c r="R21" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="S21" t="n">
         <v>1.92</v>
@@ -5728,7 +5728,7 @@
         <v>1.43</v>
       </c>
       <c r="U21" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="V21" t="n">
         <v>1.41</v>
@@ -5767,7 +5767,7 @@
         <v>14</v>
       </c>
       <c r="AH21" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI21" t="n">
         <v>30</v>
@@ -5800,7 +5800,7 @@
         <v>14.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT21" t="n">
         <v>17</v>
@@ -5854,59 +5854,59 @@
         <v>8.6</v>
       </c>
       <c r="BK21" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BL21" t="n">
         <v>55</v>
       </c>
       <c r="BM21" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN21" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP21" t="n">
         <v>14</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BR21" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BS21" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BT21" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BU21" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV21" t="n">
         <v>21</v>
       </c>
       <c r="BW21" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BX21" t="n">
         <v>24</v>
       </c>
       <c r="BY21" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BZ21" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CA21" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -5937,28 +5937,28 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="G22" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="H22" t="n">
         <v>5.3</v>
       </c>
       <c r="I22" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J22" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K22" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L22" t="n">
         <v>1.43</v>
       </c>
       <c r="M22" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N22" t="n">
         <v>3.4</v>
@@ -5967,7 +5967,7 @@
         <v>1.38</v>
       </c>
       <c r="P22" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q22" t="n">
         <v>2.1</v>
@@ -5976,19 +5976,19 @@
         <v>1.32</v>
       </c>
       <c r="S22" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T22" t="n">
         <v>1.94</v>
       </c>
       <c r="U22" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="V22" t="n">
         <v>1.2</v>
       </c>
       <c r="W22" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="X22" t="n">
         <v>15.5</v>
@@ -6003,13 +6003,13 @@
         <v>700</v>
       </c>
       <c r="AB22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC22" t="n">
         <v>10</v>
       </c>
       <c r="AD22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE22" t="n">
         <v>100</v>
@@ -6051,10 +6051,10 @@
         <v>15</v>
       </c>
       <c r="AR22" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AS22" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AT22" t="n">
         <v>6.8</v>
@@ -6066,7 +6066,7 @@
         <v>19.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AX22" t="n">
         <v>9</v>
@@ -6078,7 +6078,7 @@
         <v>19</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BB22" t="n">
         <v>16</v>
@@ -6090,31 +6090,31 @@
         <v>20</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BF22" t="n">
         <v>11</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BH22" t="n">
         <v>3.3</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BJ22" t="n">
         <v>11</v>
       </c>
       <c r="BK22" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN22" t="n">
         <v>4.3</v>
@@ -6126,41 +6126,41 @@
         <v>12.5</v>
       </c>
       <c r="BQ22" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR22" t="n">
         <v>29</v>
       </c>
       <c r="BS22" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT22" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU22" t="n">
         <v>5.6</v>
       </c>
       <c r="BV22" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ22" t="n">
         <v>25</v>
       </c>
       <c r="CA22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -6182,229 +6182,229 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Austria Wien (A)</t>
+          <t>SK Sturm Graz II</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>KSV 1919</t>
+          <t>Rapid Vienna (Am)</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.81</v>
+        <v>2.18</v>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="H23" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="I23" t="n">
-        <v>5.4</v>
+        <v>3.75</v>
       </c>
       <c r="J23" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="K23" t="n">
-        <v>5.2</v>
+        <v>3.85</v>
       </c>
       <c r="L23" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="M23" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="O23" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="P23" t="n">
-        <v>2.06</v>
+        <v>1.88</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.56</v>
+        <v>1.92</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="S23" t="n">
-        <v>2.4</v>
+        <v>3.45</v>
       </c>
       <c r="T23" t="n">
-        <v>1.54</v>
+        <v>1.74</v>
       </c>
       <c r="U23" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V23" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="W23" t="n">
-        <v>1.99</v>
+        <v>1.71</v>
       </c>
       <c r="X23" t="n">
-        <v>500</v>
+        <v>15</v>
       </c>
       <c r="Y23" t="n">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="Z23" t="n">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AA23" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AB23" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AC23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL23" t="n">
         <v>42</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>500</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>500</v>
       </c>
       <c r="AM23" t="n">
         <v>580</v>
       </c>
       <c r="AN23" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="AO23" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AP23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ23" t="n">
         <v>11</v>
       </c>
-      <c r="AQ23" t="n">
-        <v>3.55</v>
-      </c>
       <c r="AR23" t="n">
-        <v>3.85</v>
+        <v>21</v>
       </c>
       <c r="AS23" t="n">
-        <v>4</v>
+        <v>8.4</v>
       </c>
       <c r="AT23" t="n">
-        <v>3.35</v>
+        <v>8.6</v>
       </c>
       <c r="AU23" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>3.9</v>
+        <v>29</v>
       </c>
       <c r="AX23" t="n">
-        <v>3.45</v>
+        <v>11.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>3.25</v>
+        <v>9.4</v>
       </c>
       <c r="AZ23" t="n">
-        <v>9.4</v>
+        <v>14.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>3.9</v>
+        <v>34</v>
       </c>
       <c r="BB23" t="n">
-        <v>3.6</v>
+        <v>13</v>
       </c>
       <c r="BC23" t="n">
-        <v>3.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD23" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>22</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>30</v>
+      </c>
+      <c r="BH23" t="n">
         <v>3.75</v>
       </c>
-      <c r="BE23" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BH23" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BI23" t="n">
-        <v>3.15</v>
+        <v>2.78</v>
       </c>
       <c r="BJ23" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="BK23" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL23" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM23" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN23" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BO23" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="BP23" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="BQ23" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR23" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="BS23" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT23" t="n">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="BU23" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BV23" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="BW23" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX23" t="n">
         <v>46</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ23" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -6445,19 +6445,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="G24" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="H24" t="n">
-        <v>4.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I24" t="n">
         <v>990</v>
       </c>
       <c r="J24" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K24" t="n">
         <v>6.2</v>
@@ -6478,13 +6478,13 @@
         <v>1.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="R24" t="n">
         <v>1.12</v>
       </c>
       <c r="S24" t="n">
-        <v>1.05</v>
+        <v>5.5</v>
       </c>
       <c r="T24" t="n">
         <v>1.11</v>
@@ -6493,10 +6493,10 @@
         <v>1.11</v>
       </c>
       <c r="V24" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W24" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -6547,58 +6547,58 @@
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AO24" t="n">
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BC24" t="n">
         <v>1.1</v>
       </c>
-      <c r="AQ24" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>1.09</v>
-      </c>
       <c r="BD24" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="BF24" t="n">
         <v>1.08</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="G25" t="n">
         <v>1.84</v>
@@ -6708,43 +6708,43 @@
         <v>5</v>
       </c>
       <c r="I25" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J25" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N25" t="n">
         <v>3.7</v>
       </c>
-      <c r="K25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L25" t="n">
+      <c r="O25" t="n">
         <v>1.31</v>
       </c>
-      <c r="M25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.3</v>
-      </c>
       <c r="P25" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="R25" t="n">
         <v>1.39</v>
       </c>
       <c r="S25" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="T25" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="U25" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
         <v>1.22</v>
@@ -6765,10 +6765,10 @@
         <v>900</v>
       </c>
       <c r="AB25" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC25" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD25" t="n">
         <v>25</v>
@@ -6789,10 +6789,10 @@
         <v>320</v>
       </c>
       <c r="AJ25" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AK25" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AL25" t="n">
         <v>44</v>
@@ -6807,7 +6807,7 @@
         <v>700</v>
       </c>
       <c r="AP25" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ25" t="n">
         <v>15.5</v>
@@ -6816,103 +6816,103 @@
         <v>16</v>
       </c>
       <c r="AS25" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AT25" t="n">
         <v>7.6</v>
       </c>
       <c r="AU25" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV25" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AX25" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY25" t="n">
         <v>9</v>
       </c>
       <c r="AZ25" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BA25" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BB25" t="n">
         <v>16.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="BD25" t="n">
         <v>16</v>
       </c>
       <c r="BE25" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BF25" t="n">
         <v>10</v>
       </c>
       <c r="BG25" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BH25" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BI25" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="BJ25" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK25" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN25" t="n">
         <v>4.4</v>
       </c>
       <c r="BO25" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BP25" t="n">
         <v>12</v>
       </c>
       <c r="BQ25" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BS25" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BT25" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU25" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>55</v>
+      </c>
+      <c r="BY25" t="n">
         <v>11.5</v>
-      </c>
-      <c r="BX25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY25" t="n">
-        <v>12</v>
       </c>
       <c r="BZ25" t="n">
         <v>0</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -6944,229 +6944,229 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SK Sturm Graz II</t>
+          <t>Austria Wien (A)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rapid Vienna (Am)</t>
+          <t>KSV 1919</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.14</v>
+        <v>1.78</v>
       </c>
       <c r="G26" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I26" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K26" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S26" t="n">
         <v>2.4</v>
       </c>
-      <c r="H26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I26" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="J26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K26" t="n">
+      <c r="T26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="X26" t="n">
+        <v>500</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>500</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>500</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>500</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>600</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ26" t="n">
         <v>4</v>
       </c>
-      <c r="L26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="U26" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="X26" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>20</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>42</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>11</v>
-      </c>
       <c r="AR26" t="n">
-        <v>21</v>
+        <v>4.1</v>
       </c>
       <c r="AS26" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="AT26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU26" t="n">
         <v>7.2</v>
       </c>
       <c r="AV26" t="n">
-        <v>12.5</v>
+        <v>4.1</v>
       </c>
       <c r="AW26" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="AX26" t="n">
-        <v>11.5</v>
+        <v>3.85</v>
       </c>
       <c r="AY26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ26" t="n">
         <v>9.4</v>
       </c>
-      <c r="AZ26" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BA26" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="BB26" t="n">
-        <v>13</v>
+        <v>4.1</v>
       </c>
       <c r="BC26" t="n">
-        <v>19.5</v>
+        <v>4.1</v>
       </c>
       <c r="BD26" t="n">
-        <v>18</v>
+        <v>4.2</v>
       </c>
       <c r="BE26" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="BF26" t="n">
-        <v>14.5</v>
+        <v>3.55</v>
       </c>
       <c r="BG26" t="n">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
       <c r="BH26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>970</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>110</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>970</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BU26" t="n">
         <v>4</v>
       </c>
-      <c r="BI26" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BJ26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL26" t="n">
-        <v>120</v>
-      </c>
-      <c r="BM26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN26" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BO26" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP26" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BQ26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR26" t="n">
-        <v>32</v>
-      </c>
-      <c r="BS26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT26" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BU26" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BV26" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BW26" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BX26" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BZ26" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -7210,55 +7210,55 @@
         <v>4.5</v>
       </c>
       <c r="G27" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="H27" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="I27" t="n">
         <v>1.85</v>
       </c>
       <c r="J27" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="K27" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M27" t="n">
         <v>1.04</v>
       </c>
       <c r="N27" t="n">
-        <v>2.28</v>
+        <v>4.7</v>
       </c>
       <c r="O27" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P27" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="Q27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R27" t="n">
         <v>1.56</v>
       </c>
-      <c r="R27" t="n">
-        <v>1.5</v>
-      </c>
       <c r="S27" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="T27" t="n">
-        <v>1.11</v>
+        <v>1.61</v>
       </c>
       <c r="U27" t="n">
-        <v>1.11</v>
+        <v>2.18</v>
       </c>
       <c r="V27" t="n">
         <v>2.16</v>
       </c>
       <c r="W27" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="X27" t="n">
         <v>500</v>
@@ -7270,7 +7270,7 @@
         <v>500</v>
       </c>
       <c r="AA27" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AB27" t="n">
         <v>500</v>
@@ -7282,7 +7282,7 @@
         <v>500</v>
       </c>
       <c r="AE27" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AF27" t="n">
         <v>500</v>
@@ -7309,118 +7309,118 @@
         <v>580</v>
       </c>
       <c r="AN27" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO27" t="n">
-        <v>200</v>
+        <v>55</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.36</v>
+        <v>6.8</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.33</v>
+        <v>2.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.35</v>
+        <v>2.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.37</v>
+        <v>2.34</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.37</v>
+        <v>2.16</v>
       </c>
       <c r="AU27" t="n">
         <v>5.6</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.33</v>
+        <v>2.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.35</v>
+        <v>2.5</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.37</v>
+        <v>2.26</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.37</v>
+        <v>2.3</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.31</v>
+        <v>9</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.37</v>
+        <v>2.2</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.38</v>
+        <v>2.02</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.38</v>
+        <v>2.04</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.38</v>
+        <v>2.04</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.38</v>
+        <v>2.06</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.55</v>
+        <v>1.99</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.35</v>
+        <v>6</v>
       </c>
       <c r="BH27" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BI27" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="BJ27" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="BK27" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BL27" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BM27" t="n">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="BN27" t="n">
         <v>970</v>
       </c>
       <c r="BO27" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BP27" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BQ27" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BR27" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BS27" t="n">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="BT27" t="n">
-        <v>970</v>
+        <v>4.9</v>
       </c>
       <c r="BU27" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BV27" t="n">
         <v>970</v>
       </c>
       <c r="BW27" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BX27" t="n">
         <v>25</v>
       </c>
       <c r="BY27" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BZ27" t="n">
         <v>0</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -7461,25 +7461,25 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="G28" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H28" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="I28" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="J28" t="n">
         <v>5.1</v>
       </c>
       <c r="K28" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="L28" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="M28" t="n">
         <v>1.04</v>
@@ -7488,31 +7488,31 @@
         <v>5</v>
       </c>
       <c r="O28" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P28" t="n">
         <v>2.36</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R28" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S28" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="T28" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="U28" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="V28" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W28" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="X28" t="n">
         <v>29</v>
@@ -7527,7 +7527,7 @@
         <v>320</v>
       </c>
       <c r="AB28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC28" t="n">
         <v>14.5</v>
@@ -7539,10 +7539,10 @@
         <v>150</v>
       </c>
       <c r="AF28" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH28" t="n">
         <v>30</v>
@@ -7551,10 +7551,10 @@
         <v>260</v>
       </c>
       <c r="AJ28" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK28" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL28" t="n">
         <v>40</v>
@@ -7563,46 +7563,46 @@
         <v>150</v>
       </c>
       <c r="AN28" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AO28" t="n">
         <v>170</v>
       </c>
       <c r="AP28" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AQ28" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AR28" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AS28" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="AT28" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AU28" t="n">
         <v>10.5</v>
       </c>
       <c r="AV28" t="n">
-        <v>4.2</v>
+        <v>27</v>
       </c>
       <c r="AW28" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="AX28" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY28" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AZ28" t="n">
         <v>17.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BB28" t="n">
         <v>10.5</v>
@@ -7611,70 +7611,70 @@
         <v>12.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.3</v>
+        <v>23</v>
       </c>
       <c r="BE28" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BF28" t="n">
         <v>5</v>
       </c>
       <c r="BG28" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="BH28" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BI28" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BJ28" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK28" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="BL28" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="BM28" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BN28" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="BO28" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="BP28" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BQ28" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="BR28" t="n">
         <v>27</v>
       </c>
       <c r="BS28" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BT28" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BU28" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="BV28" t="n">
+        <v>85</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BX28" t="n">
         <v>80</v>
       </c>
-      <c r="BW28" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BX28" t="n">
-        <v>75</v>
-      </c>
       <c r="BY28" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BZ28" t="n">
         <v>0</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -7715,16 +7715,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="G29" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H29" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I29" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J29" t="n">
         <v>4.1</v>
@@ -7733,7 +7733,7 @@
         <v>4.7</v>
       </c>
       <c r="L29" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="M29" t="n">
         <v>1.04</v>
@@ -7751,13 +7751,13 @@
         <v>1.63</v>
       </c>
       <c r="R29" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S29" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T29" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U29" t="n">
         <v>2.24</v>
@@ -7766,7 +7766,7 @@
         <v>1.22</v>
       </c>
       <c r="W29" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X29" t="n">
         <v>26</v>
@@ -7787,7 +7787,7 @@
         <v>12</v>
       </c>
       <c r="AD29" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE29" t="n">
         <v>70</v>
@@ -7805,7 +7805,7 @@
         <v>60</v>
       </c>
       <c r="AJ29" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AK29" t="n">
         <v>19.5</v>
@@ -7820,7 +7820,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AO29" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP29" t="n">
         <v>19</v>
@@ -7829,10 +7829,10 @@
         <v>19</v>
       </c>
       <c r="AR29" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AT29" t="n">
         <v>9.800000000000001</v>
@@ -7844,7 +7844,7 @@
         <v>17.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AX29" t="n">
         <v>10.5</v>
@@ -7856,7 +7856,7 @@
         <v>15.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BB29" t="n">
         <v>15.5</v>
@@ -7865,7 +7865,7 @@
         <v>14.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BE29" t="n">
         <v>22</v>
@@ -7874,61 +7874,61 @@
         <v>7</v>
       </c>
       <c r="BG29" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BH29" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BI29" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="BJ29" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BK29" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BL29" t="n">
         <v>110</v>
       </c>
       <c r="BM29" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN29" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BO29" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="BP29" t="n">
         <v>12.5</v>
       </c>
       <c r="BQ29" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BR29" t="n">
         <v>25</v>
       </c>
       <c r="BS29" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BT29" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU29" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV29" t="n">
         <v>44</v>
       </c>
       <c r="BW29" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BX29" t="n">
         <v>48</v>
       </c>
       <c r="BY29" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BZ29" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -7987,7 +7987,7 @@
         <v>3.75</v>
       </c>
       <c r="L30" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="M30" t="n">
         <v>1.08</v>
@@ -7999,7 +7999,7 @@
         <v>1.37</v>
       </c>
       <c r="P30" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q30" t="n">
         <v>2.08</v>
@@ -8011,13 +8011,13 @@
         <v>3.85</v>
       </c>
       <c r="T30" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="U30" t="n">
         <v>1.99</v>
       </c>
       <c r="V30" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W30" t="n">
         <v>1.8</v>
@@ -8035,10 +8035,10 @@
         <v>500</v>
       </c>
       <c r="AB30" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC30" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD30" t="n">
         <v>20</v>
@@ -8047,7 +8047,7 @@
         <v>65</v>
       </c>
       <c r="AF30" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG30" t="n">
         <v>12.5</v>
@@ -8077,7 +8077,7 @@
         <v>160</v>
       </c>
       <c r="AP30" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AQ30" t="n">
         <v>9.6</v>
@@ -8086,16 +8086,16 @@
         <v>20</v>
       </c>
       <c r="AS30" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="AT30" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU30" t="n">
         <v>6.8</v>
       </c>
       <c r="AV30" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AW30" t="n">
         <v>36</v>
@@ -8104,13 +8104,13 @@
         <v>9.6</v>
       </c>
       <c r="AY30" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AZ30" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BB30" t="n">
         <v>20</v>
@@ -8122,7 +8122,7 @@
         <v>20</v>
       </c>
       <c r="BE30" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BF30" t="n">
         <v>14</v>
@@ -8131,22 +8131,22 @@
         <v>10.5</v>
       </c>
       <c r="BH30" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BI30" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="BJ30" t="n">
         <v>12</v>
       </c>
       <c r="BK30" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BL30" t="n">
         <v>170</v>
       </c>
       <c r="BM30" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BN30" t="n">
         <v>5.7</v>
@@ -8158,13 +8158,13 @@
         <v>19.5</v>
       </c>
       <c r="BQ30" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BR30" t="n">
         <v>40</v>
       </c>
       <c r="BS30" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BT30" t="n">
         <v>8.4</v>
@@ -8182,7 +8182,7 @@
         <v>60</v>
       </c>
       <c r="BY30" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BZ30" t="n">
         <v>0</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -8241,7 +8241,7 @@
         <v>4.5</v>
       </c>
       <c r="L31" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="M31" t="n">
         <v>1.06</v>
@@ -8256,7 +8256,7 @@
         <v>1.94</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R31" t="n">
         <v>1.35</v>
@@ -8313,7 +8313,7 @@
         <v>100</v>
       </c>
       <c r="AJ31" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AK31" t="n">
         <v>19</v>
@@ -8337,13 +8337,13 @@
         <v>14</v>
       </c>
       <c r="AR31" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AS31" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU31" t="n">
         <v>8.199999999999999</v>
@@ -8352,37 +8352,37 @@
         <v>16.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AX31" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AY31" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB31" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BC31" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BE31" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BF31" t="n">
         <v>7.8</v>
       </c>
       <c r="BG31" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH31" t="n">
         <v>4.1</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -8477,10 +8477,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="G32" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="H32" t="n">
         <v>5.8</v>
@@ -8489,46 +8489,46 @@
         <v>6.6</v>
       </c>
       <c r="J32" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="K32" t="n">
         <v>6</v>
       </c>
       <c r="L32" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="M32" t="n">
         <v>1.02</v>
       </c>
       <c r="N32" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="O32" t="n">
         <v>1.13</v>
       </c>
       <c r="P32" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="R32" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="S32" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="T32" t="n">
         <v>1.48</v>
       </c>
       <c r="U32" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V32" t="n">
         <v>1.18</v>
       </c>
       <c r="W32" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="X32" t="n">
         <v>95</v>
@@ -8558,7 +8558,7 @@
         <v>14</v>
       </c>
       <c r="AG32" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH32" t="n">
         <v>19.5</v>
@@ -8567,34 +8567,34 @@
         <v>250</v>
       </c>
       <c r="AJ32" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AK32" t="n">
         <v>15</v>
       </c>
       <c r="AL32" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="AM32" t="n">
         <v>250</v>
       </c>
       <c r="AN32" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AO32" t="n">
         <v>120</v>
       </c>
       <c r="AP32" t="n">
-        <v>6.4</v>
+        <v>17</v>
       </c>
       <c r="AQ32" t="n">
-        <v>6.2</v>
+        <v>17</v>
       </c>
       <c r="AR32" t="n">
-        <v>6.4</v>
+        <v>23</v>
       </c>
       <c r="AS32" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT32" t="n">
         <v>12.5</v>
@@ -8603,10 +8603,10 @@
         <v>10</v>
       </c>
       <c r="AV32" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW32" t="n">
-        <v>6.4</v>
+        <v>28</v>
       </c>
       <c r="AX32" t="n">
         <v>11.5</v>
@@ -8615,34 +8615,34 @@
         <v>9.4</v>
       </c>
       <c r="AZ32" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BA32" t="n">
-        <v>6.4</v>
+        <v>23</v>
       </c>
       <c r="BB32" t="n">
         <v>13.5</v>
       </c>
       <c r="BC32" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BD32" t="n">
         <v>17.5</v>
       </c>
       <c r="BE32" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BF32" t="n">
         <v>4.2</v>
       </c>
       <c r="BG32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BH32" t="n">
         <v>6.4</v>
       </c>
-      <c r="BH32" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BI32" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BJ32" t="n">
         <v>11.5</v>
@@ -8651,7 +8651,7 @@
         <v>3.25</v>
       </c>
       <c r="BL32" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BM32" t="n">
         <v>4.3</v>
@@ -8660,7 +8660,7 @@
         <v>5.6</v>
       </c>
       <c r="BO32" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP32" t="n">
         <v>11</v>
@@ -8669,10 +8669,10 @@
         <v>3.2</v>
       </c>
       <c r="BR32" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BS32" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BT32" t="n">
         <v>12.5</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -8988,7 +8988,7 @@
         <v>2.06</v>
       </c>
       <c r="G34" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H34" t="n">
         <v>3.05</v>
@@ -8997,7 +8997,7 @@
         <v>3.75</v>
       </c>
       <c r="J34" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="K34" t="n">
         <v>4.2</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
         <v>2.26</v>
       </c>
       <c r="G35" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H35" t="n">
         <v>3.9</v>
@@ -9263,10 +9263,10 @@
         <v>1.09</v>
       </c>
       <c r="N35" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O35" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P35" t="n">
         <v>1.81</v>
@@ -9275,10 +9275,10 @@
         <v>2.2</v>
       </c>
       <c r="R35" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S35" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T35" t="n">
         <v>1.89</v>
@@ -9290,7 +9290,7 @@
         <v>1.33</v>
       </c>
       <c r="W35" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="X35" t="n">
         <v>11.5</v>
@@ -9305,10 +9305,10 @@
         <v>75</v>
       </c>
       <c r="AB35" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC35" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD35" t="n">
         <v>16</v>
@@ -9326,7 +9326,7 @@
         <v>18</v>
       </c>
       <c r="AI35" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ35" t="n">
         <v>28</v>
@@ -9344,7 +9344,7 @@
         <v>21</v>
       </c>
       <c r="AO35" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP35" t="n">
         <v>10.5</v>
@@ -9392,10 +9392,10 @@
         <v>40</v>
       </c>
       <c r="BE35" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="BF35" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BG35" t="n">
         <v>50</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -9502,10 +9502,10 @@
         <v>4.2</v>
       </c>
       <c r="I36" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J36" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K36" t="n">
         <v>4.3</v>
@@ -9517,10 +9517,10 @@
         <v>1.06</v>
       </c>
       <c r="N36" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O36" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P36" t="n">
         <v>2.02</v>
@@ -9535,13 +9535,13 @@
         <v>3.25</v>
       </c>
       <c r="T36" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U36" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V36" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W36" t="n">
         <v>2.04</v>
@@ -9550,10 +9550,10 @@
         <v>20</v>
       </c>
       <c r="Y36" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z36" t="n">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="AA36" t="n">
         <v>110</v>
@@ -9565,7 +9565,7 @@
         <v>11.5</v>
       </c>
       <c r="AD36" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE36" t="n">
         <v>55</v>
@@ -9580,7 +9580,7 @@
         <v>23</v>
       </c>
       <c r="AI36" t="n">
-        <v>320</v>
+        <v>160</v>
       </c>
       <c r="AJ36" t="n">
         <v>24</v>
@@ -9592,7 +9592,7 @@
         <v>40</v>
       </c>
       <c r="AM36" t="n">
-        <v>120</v>
+        <v>580</v>
       </c>
       <c r="AN36" t="n">
         <v>13</v>
@@ -9610,7 +9610,7 @@
         <v>16</v>
       </c>
       <c r="AS36" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AT36" t="n">
         <v>8</v>
@@ -9619,7 +9619,7 @@
         <v>8</v>
       </c>
       <c r="AV36" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW36" t="n">
         <v>5.2</v>
@@ -9637,7 +9637,7 @@
         <v>5.2</v>
       </c>
       <c r="BB36" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BC36" t="n">
         <v>17.5</v>
@@ -9679,25 +9679,25 @@
         <v>3.6</v>
       </c>
       <c r="BP36" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BQ36" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR36" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BS36" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT36" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU36" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BV36" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BW36" t="n">
         <v>11</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -10007,10 +10007,10 @@
         <v>2.08</v>
       </c>
       <c r="H38" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I38" t="n">
         <v>3.9</v>
-      </c>
-      <c r="I38" t="n">
-        <v>3.95</v>
       </c>
       <c r="J38" t="n">
         <v>3.85</v>
@@ -10025,19 +10025,19 @@
         <v>1.06</v>
       </c>
       <c r="N38" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O38" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P38" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="R38" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S38" t="n">
         <v>3.1</v>
@@ -10046,19 +10046,19 @@
         <v>1.73</v>
       </c>
       <c r="U38" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V38" t="n">
         <v>1.34</v>
       </c>
       <c r="W38" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="X38" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y38" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z38" t="n">
         <v>28</v>
@@ -10073,25 +10073,25 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD38" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE38" t="n">
         <v>42</v>
       </c>
       <c r="AF38" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG38" t="n">
         <v>10.5</v>
       </c>
       <c r="AH38" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI38" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ38" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK38" t="n">
         <v>20</v>
@@ -10100,7 +10100,7 @@
         <v>32</v>
       </c>
       <c r="AM38" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN38" t="n">
         <v>13.5</v>
@@ -10109,7 +10109,7 @@
         <v>40</v>
       </c>
       <c r="AP38" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ38" t="n">
         <v>14.5</v>
@@ -10130,7 +10130,7 @@
         <v>14.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AX38" t="n">
         <v>12.5</v>
@@ -10139,10 +10139,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ38" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BB38" t="n">
         <v>23</v>
@@ -10154,13 +10154,13 @@
         <v>29</v>
       </c>
       <c r="BE38" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BF38" t="n">
         <v>12</v>
       </c>
       <c r="BG38" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BH38" t="n">
         <v>3.65</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -10255,22 +10255,22 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="G39" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="H39" t="n">
         <v>12</v>
       </c>
       <c r="I39" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="J39" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="K39" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
@@ -10279,34 +10279,34 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O39" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P39" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="R39" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="S39" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="T39" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="U39" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="V39" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W39" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="X39" t="n">
         <v>950</v>
@@ -10321,19 +10321,19 @@
         <v>420</v>
       </c>
       <c r="AB39" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="AC39" t="n">
         <v>970</v>
       </c>
       <c r="AD39" t="n">
-        <v>55</v>
+        <v>950</v>
       </c>
       <c r="AE39" t="n">
         <v>150</v>
       </c>
       <c r="AF39" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG39" t="n">
         <v>12.5</v>
@@ -10345,76 +10345,76 @@
         <v>200</v>
       </c>
       <c r="AJ39" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AK39" t="n">
         <v>13</v>
       </c>
       <c r="AL39" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM39" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN39" t="n">
         <v>3.25</v>
       </c>
       <c r="AO39" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AP39" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ39" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AR39" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AS39" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT39" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU39" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV39" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AW39" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AX39" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY39" t="n">
         <v>11</v>
       </c>
       <c r="AZ39" t="n">
-        <v>7.2</v>
+        <v>22</v>
       </c>
       <c r="BA39" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB39" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BC39" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BG39" t="n">
         <v>10.5</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BG39" t="n">
-        <v>15</v>
       </c>
       <c r="BH39" t="n">
         <v>1000</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -11017,7 +11017,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="G42" t="n">
         <v>4.2</v>
@@ -11029,7 +11029,7 @@
         <v>2.02</v>
       </c>
       <c r="J42" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K42" t="n">
         <v>4.4</v>
@@ -11053,7 +11053,7 @@
         <v>1.64</v>
       </c>
       <c r="R42" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S42" t="n">
         <v>2.6</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -11280,10 +11280,10 @@
         <v>3.3</v>
       </c>
       <c r="I43" t="n">
-        <v>20</v>
+        <v>6.8</v>
       </c>
       <c r="J43" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="K43" t="n">
         <v>7</v>
@@ -11319,7 +11319,7 @@
         <v>1.11</v>
       </c>
       <c r="V43" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W43" t="n">
         <v>2.12</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -11543,34 +11543,34 @@
         <v>3.65</v>
       </c>
       <c r="L44" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="M44" t="n">
         <v>1.06</v>
       </c>
       <c r="N44" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O44" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P44" t="n">
         <v>2.02</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="R44" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S44" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T44" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U44" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V44" t="n">
         <v>1.54</v>
@@ -11579,10 +11579,10 @@
         <v>1.58</v>
       </c>
       <c r="X44" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y44" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z44" t="n">
         <v>18.5</v>
@@ -11624,16 +11624,16 @@
         <v>38</v>
       </c>
       <c r="AM44" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN44" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO44" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP44" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ44" t="n">
         <v>11</v>
@@ -11642,7 +11642,7 @@
         <v>17.5</v>
       </c>
       <c r="AS44" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AT44" t="n">
         <v>11</v>
@@ -11675,19 +11675,19 @@
         <v>25</v>
       </c>
       <c r="BD44" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE44" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="BF44" t="n">
         <v>21</v>
       </c>
       <c r="BG44" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BH44" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BI44" t="n">
         <v>2.98</v>
@@ -11696,49 +11696,49 @@
         <v>9.4</v>
       </c>
       <c r="BK44" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL44" t="n">
         <v>1000</v>
       </c>
       <c r="BM44" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN44" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BO44" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BP44" t="n">
         <v>20</v>
       </c>
       <c r="BQ44" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BR44" t="n">
         <v>32</v>
       </c>
       <c r="BS44" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT44" t="n">
         <v>6.2</v>
       </c>
       <c r="BU44" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BV44" t="n">
         <v>22</v>
       </c>
       <c r="BW44" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BX44" t="n">
         <v>34</v>
       </c>
       <c r="BY44" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ44" t="n">
         <v>0</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -11785,19 +11785,19 @@
         <v>1.32</v>
       </c>
       <c r="H45" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="I45" t="n">
         <v>12</v>
       </c>
       <c r="J45" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K45" t="n">
         <v>6.6</v>
       </c>
-      <c r="K45" t="n">
-        <v>6.8</v>
-      </c>
       <c r="L45" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M45" t="n">
         <v>1.03</v>
@@ -11806,7 +11806,7 @@
         <v>6.2</v>
       </c>
       <c r="O45" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P45" t="n">
         <v>2.74</v>
@@ -11833,7 +11833,7 @@
         <v>4.1</v>
       </c>
       <c r="X45" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y45" t="n">
         <v>42</v>
@@ -11851,7 +11851,7 @@
         <v>14.5</v>
       </c>
       <c r="AD45" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AE45" t="n">
         <v>170</v>
@@ -11863,7 +11863,7 @@
         <v>10.5</v>
       </c>
       <c r="AH45" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI45" t="n">
         <v>130</v>
@@ -11878,22 +11878,22 @@
         <v>32</v>
       </c>
       <c r="AM45" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN45" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AO45" t="n">
         <v>180</v>
       </c>
       <c r="AP45" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ45" t="n">
         <v>36</v>
       </c>
       <c r="AR45" t="n">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="AS45" t="n">
         <v>120</v>
@@ -11917,10 +11917,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ45" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BA45" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="BB45" t="n">
         <v>10</v>
@@ -11950,13 +11950,13 @@
         <v>12</v>
       </c>
       <c r="BK45" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BL45" t="n">
         <v>140</v>
       </c>
       <c r="BM45" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BN45" t="n">
         <v>3.9</v>
@@ -11974,35 +11974,35 @@
         <v>21</v>
       </c>
       <c r="BS45" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT45" t="n">
         <v>14.5</v>
       </c>
       <c r="BU45" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV45" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BW45" t="n">
+        <v>15</v>
+      </c>
+      <c r="BX45" t="n">
+        <v>75</v>
+      </c>
+      <c r="BY45" t="n">
         <v>14.5</v>
       </c>
-      <c r="BX45" t="n">
-        <v>80</v>
-      </c>
-      <c r="BY45" t="n">
-        <v>14</v>
-      </c>
       <c r="BZ45" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA45" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -12042,7 +12042,7 @@
         <v>4.8</v>
       </c>
       <c r="I46" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J46" t="n">
         <v>3.5</v>
@@ -12087,7 +12087,7 @@
         <v>2.06</v>
       </c>
       <c r="X46" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y46" t="n">
         <v>16.5</v>
@@ -12138,7 +12138,7 @@
         <v>16</v>
       </c>
       <c r="AO46" t="n">
-        <v>480</v>
+        <v>700</v>
       </c>
       <c r="AP46" t="n">
         <v>9.6</v>
@@ -12150,10 +12150,10 @@
         <v>14.5</v>
       </c>
       <c r="AS46" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT46" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AU46" t="n">
         <v>7</v>
@@ -12162,7 +12162,7 @@
         <v>15</v>
       </c>
       <c r="AW46" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX46" t="n">
         <v>8.4</v>
@@ -12174,7 +12174,7 @@
         <v>18</v>
       </c>
       <c r="BA46" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB46" t="n">
         <v>16</v>
@@ -12183,16 +12183,16 @@
         <v>18</v>
       </c>
       <c r="BD46" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE46" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BE46" t="n">
-        <v>8.6</v>
       </c>
       <c r="BF46" t="n">
         <v>11.5</v>
       </c>
       <c r="BG46" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH46" t="n">
         <v>3.3</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -12308,13 +12308,13 @@
         <v>1.48</v>
       </c>
       <c r="M47" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N47" t="n">
-        <v>2.26</v>
+        <v>2.46</v>
       </c>
       <c r="O47" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="P47" t="n">
         <v>1.44</v>
@@ -12350,7 +12350,7 @@
         <v>16.5</v>
       </c>
       <c r="AA47" t="n">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="AB47" t="n">
         <v>10.5</v>
@@ -12395,13 +12395,13 @@
         <v>110</v>
       </c>
       <c r="AP47" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AQ47" t="n">
         <v>4.9</v>
       </c>
       <c r="AR47" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AS47" t="n">
         <v>7.2</v>
@@ -12413,19 +12413,19 @@
         <v>4.4</v>
       </c>
       <c r="AV47" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AW47" t="n">
         <v>7</v>
       </c>
       <c r="AX47" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY47" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AZ47" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA47" t="n">
         <v>7.6</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -12565,13 +12565,13 @@
         <v>1.01</v>
       </c>
       <c r="N48" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="O48" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P48" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q48" t="n">
         <v>1.45</v>
@@ -12580,7 +12580,7 @@
         <v>1.46</v>
       </c>
       <c r="S48" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="T48" t="n">
         <v>1.11</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -12798,7 +12798,7 @@
         <v>1.87</v>
       </c>
       <c r="G49" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="H49" t="n">
         <v>3.3</v>
@@ -12807,7 +12807,7 @@
         <v>990</v>
       </c>
       <c r="J49" t="n">
-        <v>2.04</v>
+        <v>1.1</v>
       </c>
       <c r="K49" t="n">
         <v>5.1</v>
@@ -12828,13 +12828,13 @@
         <v>1.33</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="R49" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S49" t="n">
-        <v>1.05</v>
+        <v>1.31</v>
       </c>
       <c r="T49" t="n">
         <v>1.11</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -13049,22 +13049,22 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="G50" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="H50" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="I50" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="J50" t="n">
         <v>3.05</v>
       </c>
       <c r="K50" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="L50" t="n">
         <v>1.01</v>
@@ -13076,7 +13076,7 @@
         <v>2.28</v>
       </c>
       <c r="O50" t="n">
-        <v>1.46</v>
+        <v>1.02</v>
       </c>
       <c r="P50" t="n">
         <v>1.5</v>
@@ -13088,178 +13088,178 @@
         <v>1.13</v>
       </c>
       <c r="S50" t="n">
-        <v>2.46</v>
+        <v>1.05</v>
       </c>
       <c r="T50" t="n">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="U50" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="V50" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W50" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="X50" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y50" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z50" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA50" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB50" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC50" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD50" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE50" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF50" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG50" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH50" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI50" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ50" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK50" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL50" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM50" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN50" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO50" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT50" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AU50" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV50" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AW50" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AX50" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AY50" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ50" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA50" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BC50" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD50" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF50" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BG50" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BH50" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI50" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BJ50" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK50" t="n">
         <v>1.01</v>
       </c>
       <c r="BL50" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="BM50" t="n">
         <v>1.01</v>
       </c>
       <c r="BN50" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO50" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BP50" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ50" t="n">
         <v>1.01</v>
       </c>
       <c r="BR50" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS50" t="n">
         <v>1.01</v>
       </c>
       <c r="BT50" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU50" t="n">
         <v>1.01</v>
       </c>
       <c r="BV50" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW50" t="n">
         <v>1.01</v>
       </c>
       <c r="BX50" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BY50" t="n">
         <v>1.01</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>
@@ -13303,19 +13303,19 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G51" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H51" t="n">
         <v>3.7</v>
       </c>
       <c r="I51" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J51" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K51" t="n">
         <v>3.85</v>
@@ -13333,7 +13333,7 @@
         <v>1.27</v>
       </c>
       <c r="P51" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q51" t="n">
         <v>1.83</v>
@@ -13351,10 +13351,10 @@
         <v>2.28</v>
       </c>
       <c r="V51" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W51" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X51" t="n">
         <v>18</v>
@@ -13399,7 +13399,7 @@
         <v>24</v>
       </c>
       <c r="AL51" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM51" t="n">
         <v>90</v>
@@ -13420,16 +13420,16 @@
         <v>25</v>
       </c>
       <c r="AS51" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT51" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AU51" t="n">
         <v>7.8</v>
       </c>
       <c r="AV51" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW51" t="n">
         <v>34</v>
@@ -13453,7 +13453,7 @@
         <v>18.5</v>
       </c>
       <c r="BD51" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE51" t="n">
         <v>7.2</v>
@@ -13462,13 +13462,13 @@
         <v>11.5</v>
       </c>
       <c r="BG51" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH51" t="n">
         <v>3.75</v>
       </c>
       <c r="BI51" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="BJ51" t="n">
         <v>9.199999999999999</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-05-13 22:15:14</t>
+          <t>2026-05-14 00:34:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-14.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-14 20:18:30</t>
+          <t>2026-05-14 22:52:28</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,36 +1097,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Tigres FC Zipaquira</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Envigado</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.75</v>
+        <v>1.22</v>
       </c>
       <c r="G3" t="n">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="H3" t="n">
-        <v>3.45</v>
+        <v>1.46</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5</v>
+        <v>950</v>
       </c>
       <c r="J3" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="K3" t="n">
-        <v>2.24</v>
+        <v>6.6</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1141,16 +1141,16 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2</v>
+        <v>2.68</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -1159,10 +1159,10 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="W3" t="n">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1180,97 +1180,97 @@
         <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
         <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>8.800000000000001</v>
+        <v>560</v>
       </c>
       <c r="AI3" t="n">
-        <v>40</v>
+        <v>930</v>
       </c>
       <c r="AJ3" t="n">
         <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>25</v>
+        <v>670</v>
       </c>
       <c r="AL3" t="n">
-        <v>40</v>
+        <v>990</v>
       </c>
       <c r="AM3" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
         <v>1000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AR3" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AS3" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AT3" t="n">
         <v>1000</v>
       </c>
       <c r="AU3" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="AV3" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>19</v>
+        <v>5.5</v>
       </c>
       <c r="AX3" t="n">
         <v>1000</v>
       </c>
       <c r="AY3" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>8</v>
+        <v>2.84</v>
       </c>
       <c r="BA3" t="n">
-        <v>32</v>
+        <v>5.5</v>
       </c>
       <c r="BB3" t="n">
         <v>1000</v>
       </c>
       <c r="BC3" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>100</v>
+        <v>2.84</v>
       </c>
       <c r="BF3" t="n">
-        <v>55</v>
+        <v>2.26</v>
       </c>
       <c r="BG3" t="n">
-        <v>29</v>
+        <v>5.5</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-14 20:18:30</t>
+          <t>2026-05-14 22:52:28</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,251 +1351,251 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>21:45:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Quindio</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Internacional de Palmira</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.16</v>
+        <v>2.46</v>
       </c>
       <c r="G4" t="n">
-        <v>2.26</v>
+        <v>2.68</v>
       </c>
       <c r="H4" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="I4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="L4" t="n">
         <v>3.45</v>
       </c>
-      <c r="J4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="S4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V4" t="n">
         <v>1.26</v>
       </c>
-      <c r="M4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="W4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>260</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>990</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>380</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>180</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>6.6</v>
       </c>
-      <c r="O4" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="X4" t="n">
-        <v>29</v>
-      </c>
-      <c r="Y4" t="n">
+      <c r="AR4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>130</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV4" t="n">
         <v>26</v>
       </c>
-      <c r="Z4" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA4" t="n">
+      <c r="AW4" t="n">
+        <v>130</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>55</v>
       </c>
-      <c r="AB4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>48</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>46</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BA4" t="n">
-        <v>28</v>
+        <v>270</v>
       </c>
       <c r="BB4" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="BC4" t="n">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="BD4" t="n">
-        <v>21</v>
+        <v>220</v>
       </c>
       <c r="BE4" t="n">
-        <v>38</v>
+        <v>520</v>
       </c>
       <c r="BF4" t="n">
-        <v>8.4</v>
+        <v>90</v>
       </c>
       <c r="BG4" t="n">
-        <v>15</v>
+        <v>270</v>
       </c>
       <c r="BH4" t="n">
-        <v>5.7</v>
+        <v>1.43</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.3</v>
+        <v>1.14</v>
       </c>
       <c r="BJ4" t="n">
-        <v>8.4</v>
+        <v>970</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL4" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.9</v>
+        <v>13</v>
       </c>
       <c r="BO4" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BP4" t="n">
-        <v>15</v>
+        <v>490</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BR4" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BT4" t="n">
-        <v>7.2</v>
+        <v>23</v>
       </c>
       <c r="BU4" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="BV4" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="BX4" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="BZ4" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-14 20:18:30</t>
+          <t>2026-05-14 22:52:28</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Mexican Liga MX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,498 +1605,244 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21:45:00</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Quindio</t>
+          <t>Pachuca</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Internacional de Palmira</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.77</v>
+        <v>2.04</v>
       </c>
       <c r="G5" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="H5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="X5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>210</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>270</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>110</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>95</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>32</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>130</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>85</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>75</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>30</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>160</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>60</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>44</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO5" t="n">
         <v>5.4</v>
       </c>
-      <c r="I5" t="n">
-        <v>6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="X5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>200</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>170</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG5" t="n">
+      <c r="BP5" t="n">
+        <v>75</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>55</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>570</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>190</v>
+      </c>
+      <c r="BT5" t="n">
         <v>11</v>
       </c>
-      <c r="AH5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>170</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR5" t="n">
+      <c r="BU5" t="n">
         <v>9.4</v>
       </c>
-      <c r="AS5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>980</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>7</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>36</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BV5" t="n">
-        <v>980</v>
+        <v>280</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.4</v>
+        <v>50</v>
       </c>
       <c r="BX5" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-14 20:18:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Mexican Liga MX</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>22:00:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Pachuca</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Pumas UNAM</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="X6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>26</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>70</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>13</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>38</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>110</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>16</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>8</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>28</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>11</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>32</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>40</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>24</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>2026-05-14 20:18:30</t>
+          <t>2026-05-14 22:52:28</t>
         </is>
       </c>
     </row>
